--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -14,6 +14,7 @@
     <x:sheet name="December 2025" sheetId="12" r:id="rId12"/>
     <x:sheet name="January 2026" sheetId="13" r:id="rId13"/>
     <x:sheet name="February 2026" sheetId="14" r:id="rId14"/>
+    <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -575,6 +576,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1317-596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>none Prk.San francisco, San jose, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110622F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1359-531</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -895,7 +908,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -967,6 +980,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -1292,6 +1308,1257 @@
     </a:fmtScheme>
   </a:themeElements>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28">
+      <x:c r="A3" s="2" t="s"/>
+      <x:c r="B3" s="2">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s"/>
+      <x:c r="D3" s="2" t="s"/>
+      <x:c r="E3" s="2" t="s"/>
+      <x:c r="F3" s="2" t="s"/>
+      <x:c r="G3" s="2" t="s"/>
+      <x:c r="H3" s="2" t="s"/>
+      <x:c r="I3" s="2" t="s"/>
+      <x:c r="J3" s="2" t="s"/>
+      <x:c r="K3" s="2" t="s"/>
+      <x:c r="L3" s="2" t="s"/>
+      <x:c r="M3" s="2" t="s"/>
+      <x:c r="N3" s="2" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28">
+      <x:c r="A4" s="2" t="s"/>
+      <x:c r="B4" s="2" t="s"/>
+      <x:c r="C4" s="2" t="s"/>
+      <x:c r="D4" s="2" t="s"/>
+      <x:c r="E4" s="2" t="s"/>
+      <x:c r="F4" s="2" t="s"/>
+      <x:c r="G4" s="2" t="s"/>
+      <x:c r="H4" s="2" t="s"/>
+      <x:c r="I4" s="2" t="s"/>
+      <x:c r="J4" s="2" t="s"/>
+      <x:c r="K4" s="2" t="s"/>
+      <x:c r="L4" s="2" t="s"/>
+      <x:c r="M4" s="2" t="s"/>
+      <x:c r="N4" s="2" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A5" s="3" t="s"/>
+      <x:c r="B5" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="s"/>
+      <x:c r="O5" s="6" t="s"/>
+      <x:c r="P5" s="6" t="s"/>
+      <x:c r="Q5" s="6" t="s"/>
+      <x:c r="R5" s="6" t="s"/>
+      <x:c r="S5" s="6" t="s"/>
+      <x:c r="T5" s="6" t="s"/>
+      <x:c r="U5" s="6" t="s"/>
+      <x:c r="V5" s="6" t="s"/>
+      <x:c r="W5" s="6" t="s"/>
+      <x:c r="X5" s="6" t="s"/>
+      <x:c r="Y5" s="6" t="s"/>
+      <x:c r="Z5" s="6" t="s"/>
+      <x:c r="AA5" s="6" t="s"/>
+      <x:c r="AB5" s="6" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A6" s="7" t="s"/>
+      <x:c r="B6" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H6" s="12">
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="n">
+        <x:v>1216168</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L6" s="12">
+        <x:v>46092.1400231481</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="s"/>
+      <x:c r="O6" s="9" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="7" t="s"/>
+      <x:c r="B7" s="8" t="s"/>
+      <x:c r="C7" s="8" t="s"/>
+      <x:c r="D7" s="8" t="s"/>
+      <x:c r="E7" s="8" t="s"/>
+      <x:c r="F7" s="8" t="s"/>
+      <x:c r="G7" s="8" t="s"/>
+      <x:c r="H7" s="8" t="s"/>
+      <x:c r="I7" s="8" t="s"/>
+      <x:c r="J7" s="8" t="s"/>
+      <x:c r="K7" s="8" t="s"/>
+      <x:c r="L7" s="8" t="s"/>
+      <x:c r="M7" s="8" t="s"/>
+      <x:c r="N7" s="7" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="s"/>
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="17" t="s"/>
+      <x:c r="F9" s="17" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B10" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="19" t="s"/>
+      <x:c r="D10" s="19" t="s"/>
+      <x:c r="E10" s="19" t="s"/>
+      <x:c r="F10" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B11" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="22" t="s"/>
+      <x:c r="D11" s="22" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B12" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="s"/>
+      <x:c r="D12" s="25" t="s"/>
+      <x:c r="E12" s="25" t="s"/>
+      <x:c r="F12" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="6">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B9:F9"/>
+    <x:mergeCell ref="B10:E10"/>
+    <x:mergeCell ref="B11:E11"/>
+    <x:mergeCell ref="B12:E12"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -576,6 +576,75 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1317-596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZ CELLPHONE AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>km. 5 lantawan drive, pasonanca, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIX-06868-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1384-689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Diplahan, Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110624G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1294-762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-110613A-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1293-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110615E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1292-941</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Guipos, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110618E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1289-791</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB-GADGETZ CELLPHONE STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Dumalinao, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110616G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1295-381</x:t>
   </x:si>
   <x:si>
     <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
@@ -908,7 +977,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -980,9 +1049,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -1459,13 +1525,13 @@
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
         <x:v>182</x:v>
       </x:c>
       <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
         <x:v>183</x:v>
@@ -1477,19 +1543,19 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46076.318900463</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46074</x:v>
+        <x:v>46088.1798263889</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46088.179837963</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216179</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
-        <x:v>3780</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2393865741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>35</x:v>
@@ -1497,72 +1563,291 @@
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46046.1343634259</x:v>
+      </x:c>
+      <x:c r="I7" s="13">
+        <x:v>45917</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>1216183</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46093.2878703704</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s"/>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="17" t="s"/>
-      <x:c r="F9" s="17" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="s"/>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="19" t="s"/>
-      <x:c r="F10" s="20" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="21" t="s">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
-        <x:v>1</x:v>
+      <x:c r="C8" s="27" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D8" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="27" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F8" s="27" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G8" s="27" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H8" s="29">
+        <x:v>46046.1309027778</x:v>
+      </x:c>
+      <x:c r="I8" s="30">
+        <x:v>46021</x:v>
+      </x:c>
+      <x:c r="J8" s="28" t="n">
+        <x:v>1216181</x:v>
+      </x:c>
+      <x:c r="K8" s="31" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L8" s="32">
+        <x:v>46093.273287037</x:v>
+      </x:c>
+      <x:c r="M8" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="27" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="27" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F9" s="27" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G9" s="27" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H9" s="29">
+        <x:v>46046.1237615741</x:v>
+      </x:c>
+      <x:c r="I9" s="30">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J9" s="28" t="n">
+        <x:v>1216180</x:v>
+      </x:c>
+      <x:c r="K9" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L9" s="32">
+        <x:v>46093.2636342593</x:v>
+      </x:c>
+      <x:c r="M9" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
+        <x:v>46046.1140856482</x:v>
+      </x:c>
+      <x:c r="I10" s="30">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J10" s="28" t="n">
+        <x:v>1216182</x:v>
+      </x:c>
+      <x:c r="K10" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L10" s="32">
+        <x:v>46093.2825231481</x:v>
+      </x:c>
+      <x:c r="M10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I11" s="30">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J11" s="28" t="n">
+        <x:v>1216184</x:v>
+      </x:c>
+      <x:c r="K11" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L11" s="32">
+        <x:v>46093.2926041667</x:v>
+      </x:c>
+      <x:c r="M11" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I12" s="30">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J12" s="28" t="n">
+        <x:v>1216168</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L12" s="32">
+        <x:v>46092.1400231481</x:v>
+      </x:c>
+      <x:c r="M12" s="27" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s"/>
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="17" t="s"/>
+      <x:c r="F15" s="17" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="19" t="s"/>
+      <x:c r="F16" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="21" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2538,13 +2823,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -657,6 +657,39 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1359-531</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AILYN G. PANIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PURON NANGKA, TENIAPAN, San Pablo, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06923-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1389-850</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERLINDA G. PANES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUROK NANGKA, TENIAPAN, San Pablo, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06918-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1388-689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JORELYN P. SOLES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06912-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1387-457</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1793,65 +1826,180 @@
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s"/>
+      <x:c r="E13" s="27" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
+        <x:v>46090.2854050926</x:v>
+      </x:c>
+      <x:c r="I13" s="29">
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L13" s="32">
+        <x:v>46094.0865740741</x:v>
+      </x:c>
+      <x:c r="M13" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="27" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H14" s="29">
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I14" s="29">
+        <x:v>46090.2541203704</x:v>
+      </x:c>
+      <x:c r="J14" s="28" t="n">
+        <x:v>1216185</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L14" s="32">
+        <x:v>46094.0818981481</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="27" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F15" s="27" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H15" s="29">
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I15" s="29">
+        <x:v>46090.2349305556</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="n">
+        <x:v>1216187</x:v>
+      </x:c>
+      <x:c r="K15" s="31" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L15" s="32">
+        <x:v>46094.0939351852</x:v>
+      </x:c>
+      <x:c r="M15" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C15" s="16" t="s"/>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="17" t="s"/>
-      <x:c r="F15" s="17" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="18" t="s">
+      <x:c r="C18" s="16" t="s"/>
+      <x:c r="D18" s="16" t="s"/>
+      <x:c r="E18" s="17" t="s"/>
+      <x:c r="F18" s="17" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="19" t="s"/>
-      <x:c r="D16" s="19" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="20" t="s">
+      <x:c r="C19" s="19" t="s"/>
+      <x:c r="D19" s="19" t="s"/>
+      <x:c r="E19" s="19" t="s"/>
+      <x:c r="F19" s="20" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="21" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="23" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="24" t="s">
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="22" t="s"/>
+      <x:c r="F22" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="s"/>
-      <x:c r="D19" s="25" t="s"/>
-      <x:c r="E19" s="25" t="s"/>
-      <x:c r="F19" s="26" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2823,14 +2971,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -588,6 +588,30 @@
   </x:si>
   <x:si>
     <x:t>61-3-2026-1384-689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DES APPLIANCE PLAZA INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESTIMO BLDG. POBLACION, BAYBAY, Liloy, Zamboanga Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0620H-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1366-828</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEARL'S ONLINE SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ariosa Street, San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06359-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1357-656</x:t>
   </x:si>
   <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
@@ -1599,7 +1623,7 @@
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
       <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
         <x:v>186</x:v>
@@ -1617,34 +1641,34 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46046.1343634259</x:v>
+        <x:v>46077.2833680556</x:v>
       </x:c>
       <x:c r="I7" s="13">
-        <x:v>45917</x:v>
+        <x:v>46097</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1217027</x:v>
       </x:c>
       <x:c r="K7" s="14" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46094.1366782407</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
-        <x:v>35</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C8" s="27" t="s">
         <x:v>190</x:v>
       </x:c>
       <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="27" t="s">
         <x:v>191</x:v>
@@ -1656,19 +1680,19 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H8" s="29">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>46021</x:v>
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I8" s="29">
+        <x:v>46076.2633680556</x:v>
       </x:c>
       <x:c r="J8" s="28" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216188</x:v>
       </x:c>
       <x:c r="K8" s="31" t="n">
-        <x:v>5280</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L8" s="32">
-        <x:v>46093.273287037</x:v>
+        <x:v>46094.1562731481</x:v>
       </x:c>
       <x:c r="M8" s="27" t="s">
         <x:v>35</x:v>
@@ -1679,34 +1703,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C9" s="27" t="s">
-        <x:v>190</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D9" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="27" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F9" s="27" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="G9" s="27" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H9" s="29">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I9" s="30">
-        <x:v>45991</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J9" s="28" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K9" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M9" s="27" t="s">
         <x:v>35</x:v>
@@ -1717,34 +1741,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="27" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D10" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="27" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F10" s="27" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G10" s="27" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H10" s="29">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>46024</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J10" s="28" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M10" s="27" t="s">
         <x:v>35</x:v>
@@ -1755,7 +1779,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="27" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D11" s="28" t="s">
         <x:v>15</x:v>
@@ -1770,19 +1794,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H11" s="29">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>45883</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J11" s="28" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M11" s="27" t="s">
         <x:v>35</x:v>
@@ -1808,19 +1832,19 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="H12" s="29">
-        <x:v>46076.318900463</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46074</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J12" s="28" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M12" s="27" t="s">
         <x:v>35</x:v>
@@ -1828,12 +1852,14 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="27" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s"/>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E13" s="27" t="s">
         <x:v>210</x:v>
       </x:c>
@@ -1844,19 +1870,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H13" s="29">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I13" s="29">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J13" s="28" t="s">
-        <x:v>212</x:v>
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="n">
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
-        <x:v>426</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M13" s="27" t="s">
         <x:v>35</x:v>
@@ -1864,12 +1890,14 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="27" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E14" s="27" t="s">
         <x:v>214</x:v>
       </x:c>
@@ -1880,19 +1908,19 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="H14" s="29">
-        <x:v>46090.2540972222</x:v>
-      </x:c>
-      <x:c r="I14" s="29">
-        <x:v>46090.2541203704</x:v>
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I14" s="30">
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J14" s="28" t="n">
-        <x:v>1216185</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
-        <x:v>426</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M14" s="27" t="s">
         <x:v>35</x:v>
@@ -1907,103 +1935,193 @@
       </x:c>
       <x:c r="D15" s="28" t="s"/>
       <x:c r="E15" s="27" t="s">
-        <x:v>214</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F15" s="27" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G15" s="27" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H15" s="29">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I15" s="29">
-        <x:v>46090.2349305556</x:v>
-      </x:c>
-      <x:c r="J15" s="28" t="n">
-        <x:v>1216187</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="s">
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M15" s="27" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="27" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F16" s="27" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H16" s="29">
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I16" s="29">
+        <x:v>46090.2541203704</x:v>
+      </x:c>
+      <x:c r="J16" s="28" t="n">
+        <x:v>1216185</x:v>
+      </x:c>
+      <x:c r="K16" s="31" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L16" s="32">
+        <x:v>46094.0818981481</x:v>
+      </x:c>
+      <x:c r="M16" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="27" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F17" s="27" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G17" s="27" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H17" s="29">
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I17" s="29">
+        <x:v>46090.2349305556</x:v>
+      </x:c>
+      <x:c r="J17" s="28" t="n">
+        <x:v>1216187</x:v>
+      </x:c>
+      <x:c r="K17" s="31" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L17" s="32">
+        <x:v>46094.0939351852</x:v>
+      </x:c>
+      <x:c r="M17" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C18" s="16" t="s"/>
-      <x:c r="D18" s="16" t="s"/>
-      <x:c r="E18" s="17" t="s"/>
-      <x:c r="F18" s="17" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="18" t="s">
+      <x:c r="C20" s="16" t="s"/>
+      <x:c r="D20" s="16" t="s"/>
+      <x:c r="E20" s="17" t="s"/>
+      <x:c r="F20" s="17" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C19" s="19" t="s"/>
-      <x:c r="D19" s="19" t="s"/>
-      <x:c r="E19" s="19" t="s"/>
-      <x:c r="F19" s="20" t="s">
+      <x:c r="C21" s="19" t="s"/>
+      <x:c r="D21" s="19" t="s"/>
+      <x:c r="E21" s="19" t="s"/>
+      <x:c r="F21" s="20" t="s">
         <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="21" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="22" t="s"/>
       <x:c r="D22" s="22" t="s"/>
       <x:c r="E22" s="22" t="s"/>
       <x:c r="F22" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="s"/>
+      <x:c r="D23" s="22" t="s"/>
+      <x:c r="E23" s="22" t="s"/>
+      <x:c r="F23" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="21" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="s"/>
+      <x:c r="D24" s="22" t="s"/>
+      <x:c r="E24" s="22" t="s"/>
+      <x:c r="F24" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C26" s="22" t="s"/>
+      <x:c r="D26" s="22" t="s"/>
+      <x:c r="E26" s="22" t="s"/>
+      <x:c r="F26" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2971,15 +3089,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="228">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -602,6 +602,18 @@
     <x:t>61-2-2026-1366-828</x:t>
   </x:si>
   <x:si>
+    <x:t>HIGH-SPEED MOTORCYCLE PARTS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Purok Pines 2, Sanito, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06354-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1355-880</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEARL'S ONLINE SHOP</x:t>
   </x:si>
   <x:si>
@@ -612,6 +624,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1357-656</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SLIM BX ELECTRONICS AND TELECOMMUNICATION PARTS AND EQUIPMENT RETAILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vicencio Sagun Street, Brgy San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06389-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1360-023</x:t>
   </x:si>
   <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
@@ -1680,19 +1704,19 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H8" s="29">
-        <x:v>46076.2633564815</x:v>
+        <x:v>46076.245</x:v>
       </x:c>
       <x:c r="I8" s="29">
-        <x:v>46076.2633680556</x:v>
+        <x:v>46076.2450115741</x:v>
       </x:c>
       <x:c r="J8" s="28" t="n">
-        <x:v>1216188</x:v>
+        <x:v>1216190</x:v>
       </x:c>
       <x:c r="K8" s="31" t="n">
-        <x:v>4530</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="32">
-        <x:v>46094.1562731481</x:v>
+        <x:v>46094.1710416667</x:v>
       </x:c>
       <x:c r="M8" s="27" t="s">
         <x:v>35</x:v>
@@ -1700,13 +1724,13 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C9" s="27" t="s">
         <x:v>194</x:v>
       </x:c>
       <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="27" t="s">
         <x:v>195</x:v>
@@ -1718,19 +1742,19 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="H9" s="29">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>45917</x:v>
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I9" s="29">
+        <x:v>46076.2633680556</x:v>
       </x:c>
       <x:c r="J9" s="28" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216188</x:v>
       </x:c>
       <x:c r="K9" s="31" t="n">
-        <x:v>3780</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L9" s="32">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46094.1562731481</x:v>
       </x:c>
       <x:c r="M9" s="27" t="s">
         <x:v>35</x:v>
@@ -1738,13 +1762,13 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C10" s="27" t="s">
         <x:v>198</x:v>
       </x:c>
       <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E10" s="27" t="s">
         <x:v>199</x:v>
@@ -1756,19 +1780,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H10" s="29">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>46021</x:v>
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I10" s="29">
+        <x:v>46076.3755439815</x:v>
       </x:c>
       <x:c r="J10" s="28" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216189</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
-        <x:v>5280</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>46093.273287037</x:v>
+        <x:v>46094.1653935185</x:v>
       </x:c>
       <x:c r="M10" s="27" t="s">
         <x:v>35</x:v>
@@ -1779,34 +1803,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C11" s="27" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D11" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="27" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F11" s="27" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G11" s="27" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H11" s="29">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>45991</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J11" s="28" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M11" s="27" t="s">
         <x:v>35</x:v>
@@ -1817,34 +1841,34 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C12" s="27" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D12" s="28" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="27" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="F12" s="27" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="G12" s="27" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H12" s="29">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I12" s="30">
-        <x:v>46024</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J12" s="28" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K12" s="31" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L12" s="32">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M12" s="27" t="s">
         <x:v>35</x:v>
@@ -1855,7 +1879,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="27" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D13" s="28" t="s">
         <x:v>15</x:v>
@@ -1870,19 +1894,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H13" s="29">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I13" s="30">
-        <x:v>45883</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J13" s="28" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K13" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L13" s="32">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M13" s="27" t="s">
         <x:v>35</x:v>
@@ -1908,19 +1932,19 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="H14" s="29">
-        <x:v>46076.318900463</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I14" s="30">
-        <x:v>46074</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J14" s="28" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K14" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="32">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M14" s="27" t="s">
         <x:v>35</x:v>
@@ -1928,12 +1952,14 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="27" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E15" s="27" t="s">
         <x:v>218</x:v>
       </x:c>
@@ -1944,19 +1970,19 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="H15" s="29">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I15" s="29">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J15" s="28" t="s">
-        <x:v>220</x:v>
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="n">
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K15" s="31" t="n">
-        <x:v>426</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L15" s="32">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M15" s="27" t="s">
         <x:v>35</x:v>
@@ -1964,12 +1990,14 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="27" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E16" s="27" t="s">
         <x:v>222</x:v>
       </x:c>
@@ -1980,19 +2008,19 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="H16" s="29">
-        <x:v>46090.2540972222</x:v>
-      </x:c>
-      <x:c r="I16" s="29">
-        <x:v>46090.2541203704</x:v>
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J16" s="28" t="n">
-        <x:v>1216185</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K16" s="31" t="n">
-        <x:v>426</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="32">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M16" s="27" t="s">
         <x:v>35</x:v>
@@ -2007,80 +2035,130 @@
       </x:c>
       <x:c r="D17" s="28" t="s"/>
       <x:c r="E17" s="27" t="s">
-        <x:v>222</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="F17" s="27" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G17" s="27" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H17" s="29">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I17" s="29">
-        <x:v>46090.2349305556</x:v>
-      </x:c>
-      <x:c r="J17" s="28" t="n">
-        <x:v>1216187</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J17" s="28" t="s">
+        <x:v>228</x:v>
       </x:c>
       <x:c r="K17" s="31" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L17" s="32">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M17" s="27" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="27" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F18" s="27" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G18" s="27" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H18" s="29">
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I18" s="29">
+        <x:v>46090.2541203704</x:v>
+      </x:c>
+      <x:c r="J18" s="28" t="n">
+        <x:v>1216185</x:v>
+      </x:c>
+      <x:c r="K18" s="31" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L18" s="32">
+        <x:v>46094.0818981481</x:v>
+      </x:c>
+      <x:c r="M18" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="27" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F19" s="27" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G19" s="27" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H19" s="29">
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I19" s="29">
+        <x:v>46090.2349305556</x:v>
+      </x:c>
+      <x:c r="J19" s="28" t="n">
+        <x:v>1216187</x:v>
+      </x:c>
+      <x:c r="K19" s="31" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L19" s="32">
+        <x:v>46094.0939351852</x:v>
+      </x:c>
+      <x:c r="M19" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C20" s="16" t="s"/>
-      <x:c r="D20" s="16" t="s"/>
-      <x:c r="E20" s="17" t="s"/>
-      <x:c r="F20" s="17" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="18" t="s">
+      <x:c r="C22" s="16" t="s"/>
+      <x:c r="D22" s="16" t="s"/>
+      <x:c r="E22" s="17" t="s"/>
+      <x:c r="F22" s="17" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="18" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C21" s="19" t="s"/>
-      <x:c r="D21" s="19" t="s"/>
-      <x:c r="E21" s="19" t="s"/>
-      <x:c r="F21" s="20" t="s">
+      <x:c r="C23" s="19" t="s"/>
+      <x:c r="D23" s="19" t="s"/>
+      <x:c r="E23" s="19" t="s"/>
+      <x:c r="F23" s="20" t="s">
         <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="21" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="21" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="23" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="21" t="s">
-        <x:v>105</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C24" s="22" t="s"/>
       <x:c r="D24" s="22" t="s"/>
@@ -2091,18 +2169,18 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C25" s="22" t="s"/>
       <x:c r="D25" s="22" t="s"/>
       <x:c r="E25" s="22" t="s"/>
       <x:c r="F25" s="23" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="21" t="s">
-        <x:v>20</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C26" s="22" t="s"/>
       <x:c r="D26" s="22" t="s"/>
@@ -2111,19 +2189,39 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="24" t="s">
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="s"/>
+      <x:c r="D27" s="22" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="23" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C28" s="22" t="s"/>
+      <x:c r="D28" s="22" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B29" s="24" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3092,14 +3190,14 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B22:F22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -185,16 +185,16 @@
     <x:t>Alexander Tomales</x:t>
   </x:si>
   <x:si>
+    <x:t>MP-ROIX-01008-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-8-2025-1095</x:t>
+  </x:si>
+  <x:si>
     <x:t>MP-ROIX-01007-25</x:t>
   </x:si>
   <x:si>
     <x:t>61-8-2025-1093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MP-ROIX-01008-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-8-2025-1095</x:t>
   </x:si>
   <x:si>
     <x:t>VALIANT ELECTRONICS SUPPLY</x:t>
@@ -4819,19 +4819,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="29">
-        <x:v>45875.2324652778</x:v>
+        <x:v>45875.361724537</x:v>
       </x:c>
       <x:c r="I10" s="30">
-        <x:v>45903</x:v>
+        <x:v>45921</x:v>
       </x:c>
       <x:c r="J10" s="28" t="n">
-        <x:v>1215852</x:v>
+        <x:v>1215851</x:v>
       </x:c>
       <x:c r="K10" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="32">
-        <x:v>45876.2319791667</x:v>
+        <x:v>45876.2230902778</x:v>
       </x:c>
       <x:c r="M10" s="27" t="s">
         <x:v>35</x:v>
@@ -4857,19 +4857,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="29">
-        <x:v>45875.361724537</x:v>
+        <x:v>45875.2324652778</x:v>
       </x:c>
       <x:c r="I11" s="30">
-        <x:v>45921</x:v>
+        <x:v>45903</x:v>
       </x:c>
       <x:c r="J11" s="28" t="n">
-        <x:v>1215851</x:v>
+        <x:v>1215852</x:v>
       </x:c>
       <x:c r="K11" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="32">
-        <x:v>45876.2230902778</x:v>
+        <x:v>45876.2319791667</x:v>
       </x:c>
       <x:c r="M11" s="27" t="s">
         <x:v>35</x:v>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -17,58 +17,22 @@
     <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="236">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -602,6 +566,18 @@
     <x:t>61-2-2026-1366-828</x:t>
   </x:si>
   <x:si>
+    <x:t>COMPRO COMPUTER SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Datoc Street, Gatas District, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06365-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1358-112</x:t>
+  </x:si>
+  <x:si>
     <x:t>HIGH-SPEED MOTORCYCLE PARTS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -614,6 +590,18 @@
     <x:t>61-2-2026-1355-880</x:t>
   </x:si>
   <x:si>
+    <x:t>PCCP COMPUTER REPAIR SERVICES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Sabado Street, San Francisco District, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06357-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1356-022</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEARL'S ONLINE SHOP</x:t>
   </x:si>
   <x:si>
@@ -705,6 +693,27 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1359-531</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Service Center Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATOC ST., GATAS DISTRICT, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPSCP-ROIX-06500-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1374-436</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SABADO ST., SAN FRANCISCO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPSCP-ROIX-06499-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1373-524</x:t>
   </x:si>
   <x:si>
     <x:t>AILYN G. PANIS</x:t>
@@ -747,7 +756,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -774,12 +783,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -790,16 +793,30 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -823,7 +840,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -852,6 +869,17 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
@@ -866,17 +894,6 @@
       <x:left style="thin">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="thin">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -1058,7 +1075,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1069,76 +1086,91 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
@@ -1146,114 +1178,127 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1516,717 +1561,851 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46088.1798263889</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>46088.179837963</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216179</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46093.2393865741</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46077.2833680556</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1217027</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46094.1366782407</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
+        <x:v>46076.2809953704</x:v>
+      </x:c>
+      <x:c r="I8" s="34">
+        <x:v>46076.2810185185</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="n">
+        <x:v>1216194</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46097.2411111111</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="33" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E9" s="33" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F9" s="33" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G9" s="33" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H9" s="34">
+        <x:v>46076.245</x:v>
+      </x:c>
+      <x:c r="I9" s="34">
+        <x:v>46076.2450115741</x:v>
+      </x:c>
+      <x:c r="J9" s="33" t="n">
+        <x:v>1216190</x:v>
+      </x:c>
+      <x:c r="K9" s="36" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>46094.1710416667</x:v>
+      </x:c>
+      <x:c r="M9" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>46076.2578009259</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>46076.2578240741</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1216197</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>46097.2583912037</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I11" s="13">
+        <x:v>46076.2633680556</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1216188</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>46094.1562731481</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I12" s="13">
+        <x:v>46076.3755439815</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1216189</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="16">
+        <x:v>46094.1653935185</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C13" s="11" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>46046.1343634259</x:v>
+      </x:c>
+      <x:c r="I13" s="14">
+        <x:v>45917</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1216183</x:v>
+      </x:c>
+      <x:c r="K13" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L13" s="16">
+        <x:v>46093.2878703704</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>46046.1309027778</x:v>
+      </x:c>
+      <x:c r="I14" s="14">
+        <x:v>46021</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1216181</x:v>
+      </x:c>
+      <x:c r="K14" s="15" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L14" s="16">
+        <x:v>46093.273287037</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>46046.1237615741</x:v>
+      </x:c>
+      <x:c r="I15" s="14">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1216180</x:v>
+      </x:c>
+      <x:c r="K15" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L15" s="16">
+        <x:v>46093.2636342593</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>46046.1140856482</x:v>
+      </x:c>
+      <x:c r="I16" s="14">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>1216182</x:v>
+      </x:c>
+      <x:c r="K16" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L16" s="16">
+        <x:v>46093.2825231481</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I17" s="14">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>1216184</x:v>
+      </x:c>
+      <x:c r="K17" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L17" s="16">
+        <x:v>46093.2926041667</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I18" s="14">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="n">
+        <x:v>1216168</x:v>
+      </x:c>
+      <x:c r="K18" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="16">
+        <x:v>46092.1400231481</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>46079.2852546296</x:v>
+      </x:c>
+      <x:c r="I19" s="13">
+        <x:v>46079.2852662037</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="n">
+        <x:v>1216195</x:v>
+      </x:c>
+      <x:c r="K19" s="15" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L19" s="16">
+        <x:v>46097.2459143518</x:v>
+      </x:c>
+      <x:c r="M19" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="11" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>46079.2747222222</x:v>
+      </x:c>
+      <x:c r="I20" s="13">
+        <x:v>46079.2747453704</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="n">
+        <x:v>1216196</x:v>
+      </x:c>
+      <x:c r="K20" s="15" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L20" s="16">
+        <x:v>46097.2536342593</x:v>
+      </x:c>
+      <x:c r="M20" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="s"/>
+      <x:c r="E21" s="11" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>46090.2854050926</x:v>
+      </x:c>
+      <x:c r="I21" s="13">
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="K21" s="15" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L21" s="16">
+        <x:v>46094.0865740741</x:v>
+      </x:c>
+      <x:c r="M21" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="s"/>
+      <x:c r="E22" s="11" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F22" s="11" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I22" s="13">
+        <x:v>46090.2541203704</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="n">
+        <x:v>1216185</x:v>
+      </x:c>
+      <x:c r="K22" s="15" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L22" s="16">
+        <x:v>46094.0818981481</x:v>
+      </x:c>
+      <x:c r="M22" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="s"/>
+      <x:c r="E23" s="11" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F23" s="11" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I23" s="13">
+        <x:v>46090.2349305556</x:v>
+      </x:c>
+      <x:c r="J23" s="12" t="n">
+        <x:v>1216187</x:v>
+      </x:c>
+      <x:c r="K23" s="15" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L23" s="16">
+        <x:v>46094.0939351852</x:v>
+      </x:c>
+      <x:c r="M23" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C26" s="21" t="s"/>
+      <x:c r="D26" s="21" t="s"/>
+      <x:c r="E26" s="22" t="s"/>
+      <x:c r="F26" s="22" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B27" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="24" t="s"/>
+      <x:c r="D27" s="24" t="s"/>
+      <x:c r="E27" s="24" t="s"/>
+      <x:c r="F27" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46088.1798263889</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>46088.179837963</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216179</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46093.2393865741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46077.2833680556</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1217027</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46094.1366782407</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>46076.245</x:v>
-      </x:c>
-      <x:c r="I8" s="29">
-        <x:v>46076.2450115741</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1216190</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>46094.1710416667</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>46076.2633564815</x:v>
-      </x:c>
-      <x:c r="I9" s="29">
-        <x:v>46076.2633680556</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1216188</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>46094.1562731481</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>46076.3755324074</x:v>
-      </x:c>
-      <x:c r="I10" s="29">
-        <x:v>46076.3755439815</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1216189</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>46094.1653935185</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G11" s="27" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H11" s="29">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>45917</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:v>1216183</x:v>
-      </x:c>
-      <x:c r="K11" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L11" s="32">
-        <x:v>46093.2878703704</x:v>
-      </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D12" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="27" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F12" s="27" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G12" s="27" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H12" s="29">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I12" s="30">
-        <x:v>46021</x:v>
-      </x:c>
-      <x:c r="J12" s="28" t="n">
-        <x:v>1216181</x:v>
-      </x:c>
-      <x:c r="K12" s="31" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L12" s="32">
-        <x:v>46093.273287037</x:v>
-      </x:c>
-      <x:c r="M12" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="27" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D13" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="27" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F13" s="27" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G13" s="27" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H13" s="29">
-        <x:v>46046.1237615741</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J13" s="28" t="n">
-        <x:v>1216180</x:v>
-      </x:c>
-      <x:c r="K13" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L13" s="32">
-        <x:v>46093.2636342593</x:v>
-      </x:c>
-      <x:c r="M13" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D14" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="27" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F14" s="27" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G14" s="27" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H14" s="29">
-        <x:v>46046.1140856482</x:v>
-      </x:c>
-      <x:c r="I14" s="30">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J14" s="28" t="n">
-        <x:v>1216182</x:v>
-      </x:c>
-      <x:c r="K14" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="32">
-        <x:v>46093.2825231481</x:v>
-      </x:c>
-      <x:c r="M14" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D15" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="27" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F15" s="27" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G15" s="27" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H15" s="29">
-        <x:v>46048.0974768518</x:v>
-      </x:c>
-      <x:c r="I15" s="30">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J15" s="28" t="n">
-        <x:v>1216184</x:v>
-      </x:c>
-      <x:c r="K15" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L15" s="32">
-        <x:v>46093.2926041667</x:v>
-      </x:c>
-      <x:c r="M15" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D16" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="27" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F16" s="27" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G16" s="27" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H16" s="29">
-        <x:v>46076.318900463</x:v>
-      </x:c>
-      <x:c r="I16" s="30">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J16" s="28" t="n">
-        <x:v>1216168</x:v>
-      </x:c>
-      <x:c r="K16" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L16" s="32">
-        <x:v>46092.1400231481</x:v>
-      </x:c>
-      <x:c r="M16" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="27" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F17" s="27" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G17" s="27" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H17" s="29">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I17" s="29">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J17" s="28" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="K17" s="31" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L17" s="32">
-        <x:v>46094.0865740741</x:v>
-      </x:c>
-      <x:c r="M17" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="27" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F18" s="27" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G18" s="27" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H18" s="29">
-        <x:v>46090.2540972222</x:v>
-      </x:c>
-      <x:c r="I18" s="29">
-        <x:v>46090.2541203704</x:v>
-      </x:c>
-      <x:c r="J18" s="28" t="n">
-        <x:v>1216185</x:v>
-      </x:c>
-      <x:c r="K18" s="31" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L18" s="32">
-        <x:v>46094.0818981481</x:v>
-      </x:c>
-      <x:c r="M18" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="27" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F19" s="27" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G19" s="27" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H19" s="29">
-        <x:v>46090.2349189815</x:v>
-      </x:c>
-      <x:c r="I19" s="29">
-        <x:v>46090.2349305556</x:v>
-      </x:c>
-      <x:c r="J19" s="28" t="n">
-        <x:v>1216187</x:v>
-      </x:c>
-      <x:c r="K19" s="31" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L19" s="32">
-        <x:v>46094.0939351852</x:v>
-      </x:c>
-      <x:c r="M19" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C22" s="16" t="s"/>
-      <x:c r="D22" s="16" t="s"/>
-      <x:c r="E22" s="17" t="s"/>
-      <x:c r="F22" s="17" t="s"/>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C23" s="19" t="s"/>
-      <x:c r="D23" s="19" t="s"/>
-      <x:c r="E23" s="19" t="s"/>
-      <x:c r="F23" s="20" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="21" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="22" t="s"/>
-      <x:c r="F24" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="21" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="21" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s"/>
-      <x:c r="D26" s="22" t="s"/>
-      <x:c r="E26" s="22" t="s"/>
-      <x:c r="F26" s="23" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C27" s="22" t="s"/>
-      <x:c r="D27" s="22" t="s"/>
-      <x:c r="E27" s="22" t="s"/>
-      <x:c r="F27" s="23" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C28" s="22" t="s"/>
-      <x:c r="D28" s="22" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="23" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3187,17 +3366,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B26:F26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3273,224 +3453,226 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>45860.0993981482</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1346409</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45860.1449537037</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="C7" s="17" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="D7" s="17" t="s"/>
+      <x:c r="E7" s="17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="F7" s="17" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="G7" s="17" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="H7" s="18">
+        <x:v>45861.1130439815</x:v>
+      </x:c>
+      <x:c r="I7" s="18">
+        <x:v>45861.1130555556</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1346412</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45862.3035648148</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="20" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="22" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B11" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B12" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45860.0993981482</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1346409</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45860.1449537037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45861.1130439815</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>45861.1130555556</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1346412</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45862.3035648148</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -4557,398 +4739,374 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45866.2802893519</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>45866.2803009259</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215849</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45873.1184143519</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45875.2238888889</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215853</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45876.2432986111</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
+        <x:v>45880.1214814815</x:v>
+      </x:c>
+      <x:c r="I8" s="35">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="n">
+        <x:v>1346457</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45881.1618981482</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="33" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="s"/>
+      <x:c r="E9" s="33" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F9" s="33" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G9" s="33" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H9" s="34">
+        <x:v>45873.2195486111</x:v>
+      </x:c>
+      <x:c r="I9" s="34">
+        <x:v>45873.2195601852</x:v>
+      </x:c>
+      <x:c r="J9" s="33" t="n">
+        <x:v>1195700</x:v>
+      </x:c>
+      <x:c r="K9" s="36" t="n">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>45882.1150694444</x:v>
+      </x:c>
+      <x:c r="M9" s="33" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C10" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45866.2802893519</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>45866.2803009259</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215849</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45873.1184143519</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E10" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="G10" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45875.2238888889</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
+      <x:c r="H10" s="13">
+        <x:v>45875.361724537</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215853</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45876.2432986111</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
+      <x:c r="J10" s="12" t="n">
+        <x:v>1215851</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45876.2230902778</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
+      <x:c r="G11" s="11" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45880.1214814815</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s"/>
-      <x:c r="E9" s="27" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>45873.2195486111</x:v>
-      </x:c>
-      <x:c r="I9" s="29">
-        <x:v>45873.2195601852</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1195700</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>2790</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>45882.1150694444</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>45875.361724537</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1215851</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="H11" s="13">
+        <x:v>45875.2324652778</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1215852</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="32">
-        <x:v>45876.2230902778</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G11" s="27" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H11" s="29">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K11" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="16">
         <x:v>45876.2319791667</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="M11" s="11" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s"/>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="17" t="s"/>
-      <x:c r="F14" s="17" t="s"/>
+      <x:c r="B14" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B15" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="B19" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C20" s="25" t="s"/>
-      <x:c r="D20" s="25" t="s"/>
-      <x:c r="E20" s="25" t="s"/>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -6011,436 +6169,412 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45915.355787037</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215901</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45918.2339583333</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45903.3849652778</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45916</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215886</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>3150</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45908.2848958333</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C8" s="33" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E8" s="33" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
+        <x:v>45919.4023032407</x:v>
+      </x:c>
+      <x:c r="I8" s="35">
+        <x:v>45926</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="n">
+        <x:v>1215905</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45925.945150463</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="33" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="33" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F9" s="33" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G9" s="33" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H9" s="34">
+        <x:v>45918.1053935185</x:v>
+      </x:c>
+      <x:c r="I9" s="35">
+        <x:v>45900</x:v>
+      </x:c>
+      <x:c r="J9" s="33" t="n">
+        <x:v>1215910</x:v>
+      </x:c>
+      <x:c r="K9" s="36" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>45929.2194097222</x:v>
+      </x:c>
+      <x:c r="M9" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>45908.2183449074</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45918</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1215894</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45912.1906134259</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>45922.1415393519</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1346550</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>45922.1832523148</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45915.355787037</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215901</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45918.2339583333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45903.3849652778</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45916</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1215886</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>3150</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45908.2848958333</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45919.4023032407</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>45926</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1215905</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>45925.945150463</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
+      <x:c r="C12" s="11" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
+      <x:c r="D12" s="12" t="s"/>
+      <x:c r="E12" s="11" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F9" s="27" t="s">
+      <x:c r="F12" s="11" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G9" s="27" t="s">
+      <x:c r="G12" s="11" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H9" s="29">
-        <x:v>45918.1053935185</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>45900</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1215910</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>45929.2194097222</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>45908.2183449074</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>45918</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1215894</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>45912.1906134259</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G11" s="27" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H11" s="29">
-        <x:v>45922.1415393519</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:v>1346550</x:v>
-      </x:c>
-      <x:c r="K11" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="32">
-        <x:v>45922.1832523148</x:v>
-      </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D12" s="28" t="s"/>
-      <x:c r="E12" s="27" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F12" s="27" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G12" s="27" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="13">
         <x:v>45919.473287037</x:v>
       </x:c>
-      <x:c r="I12" s="29">
+      <x:c r="I12" s="13">
         <x:v>45919.4732986111</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="12" t="n">
         <x:v>1215906</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="15" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="16">
         <x:v>45926.2586111111</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="M12" s="11" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s"/>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="17" t="s"/>
-      <x:c r="F15" s="17" t="s"/>
+      <x:c r="B15" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
     </x:row>
     <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="19" t="s"/>
-      <x:c r="D16" s="19" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B16" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="B17" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="B18" s="26" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="B19" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
+      <x:c r="B20" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C21" s="25" t="s"/>
-      <x:c r="D21" s="25" t="s"/>
-      <x:c r="E21" s="25" t="s"/>
-      <x:c r="F21" s="26" t="n">
+      <x:c r="B21" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7502,260 +7636,249 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45931</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45933.0884375</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45932</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215922</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45936.014837963</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45933.0884375</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45932</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1215922</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45936.014837963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="C7" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s"/>
+      <x:c r="E7" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
         <x:v>45928.9304513889</x:v>
       </x:c>
-      <x:c r="I7" s="12">
+      <x:c r="I7" s="18">
         <x:v>45928.9304861111</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="17" t="n">
         <x:v>1215924</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="18">
         <x:v>45938.0359375</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s"/>
-      <x:c r="E8" s="27" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s"/>
+      <x:c r="E8" s="33" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
         <x:v>45926.4563888889</x:v>
       </x:c>
-      <x:c r="I8" s="29">
+      <x:c r="I8" s="34">
         <x:v>45926.4564351852</x:v>
       </x:c>
-      <x:c r="J8" s="28" t="n">
+      <x:c r="J8" s="33" t="n">
         <x:v>1215917</x:v>
       </x:c>
-      <x:c r="K8" s="31" t="n">
+      <x:c r="K8" s="36" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L8" s="32">
+      <x:c r="L8" s="34">
         <x:v>45932.239537037</x:v>
       </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="M8" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B12" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="B15" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8821,606 +8944,582 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45951.1032638889</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>45951.103287037</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1346752</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45971.0888194444</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45980.2160416667</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45979</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1346786</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45985.3594791667</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
+        <x:v>45965.2736689815</x:v>
+      </x:c>
+      <x:c r="I8" s="34">
+        <x:v>45965.2736921296</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="n">
+        <x:v>1216000</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45972.1539583333</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="33" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C9" s="33" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="33" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F9" s="33" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G9" s="33" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H9" s="34">
+        <x:v>45965.2661458333</x:v>
+      </x:c>
+      <x:c r="I9" s="35">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J9" s="33" t="n">
+        <x:v>1215999</x:v>
+      </x:c>
+      <x:c r="K9" s="36" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>45972.1364236111</x:v>
+      </x:c>
+      <x:c r="M9" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>45953.5328240741</x:v>
+      </x:c>
+      <x:c r="I10" s="14">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>1215970</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="16">
+        <x:v>45966.0458101852</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D11" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E11" s="11" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>45959.0699074074</x:v>
+      </x:c>
+      <x:c r="I11" s="14">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>1346761</x:v>
+      </x:c>
+      <x:c r="K11" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="16">
+        <x:v>45972.2719560185</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>45958.0724421296</x:v>
+      </x:c>
+      <x:c r="I12" s="14">
+        <x:v>45810</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1216003</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L12" s="16">
+        <x:v>45973.0584490741</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>45973.1309375</x:v>
+      </x:c>
+      <x:c r="I13" s="14">
+        <x:v>45950</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>1216020</x:v>
+      </x:c>
+      <x:c r="K13" s="15" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L13" s="16">
+        <x:v>45985.2116666667</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>45971.2436226852</x:v>
+      </x:c>
+      <x:c r="I14" s="14">
+        <x:v>45608</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1216004</x:v>
+      </x:c>
+      <x:c r="K14" s="15" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L14" s="16">
+        <x:v>45973.2287268518</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>45951.103287037</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1346752</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45971.0888194444</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45979</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1346786</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45985.3594791667</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45965.2736689815</x:v>
-      </x:c>
-      <x:c r="I8" s="29">
-        <x:v>45965.2736921296</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1216000</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>45972.1539583333</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>45965.2661458333</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1215999</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
-        <x:v>45972.1364236111</x:v>
-      </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D10" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="27" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F10" s="27" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G10" s="27" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H10" s="29">
-        <x:v>45953.5328240741</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J10" s="28" t="n">
-        <x:v>1215970</x:v>
-      </x:c>
-      <x:c r="K10" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="32">
-        <x:v>45966.0458101852</x:v>
-      </x:c>
-      <x:c r="M10" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="27" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G11" s="27" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H11" s="29">
-        <x:v>45959.0699074074</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J11" s="28" t="n">
-        <x:v>1346761</x:v>
-      </x:c>
-      <x:c r="K11" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="32">
-        <x:v>45972.2719560185</x:v>
-      </x:c>
-      <x:c r="M11" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D12" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="C15" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s"/>
+      <x:c r="E15" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="G15" s="11" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="H15" s="13">
+        <x:v>45954.4189930556</x:v>
+      </x:c>
+      <x:c r="I15" s="13">
+        <x:v>45954.4190277778</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1215987</x:v>
+      </x:c>
+      <x:c r="K15" s="15" t="n">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="L15" s="16">
+        <x:v>45967.2850694444</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H12" s="29">
-        <x:v>45958.0724421296</x:v>
-      </x:c>
-      <x:c r="I12" s="30">
-        <x:v>45810</x:v>
-      </x:c>
-      <x:c r="J12" s="28" t="n">
-        <x:v>1216003</x:v>
-      </x:c>
-      <x:c r="K12" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L12" s="32">
-        <x:v>45973.0584490741</x:v>
-      </x:c>
-      <x:c r="M12" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="D16" s="12" t="s"/>
+      <x:c r="E16" s="11" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="F16" s="11" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="G16" s="11" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G13" s="27" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H13" s="29">
-        <x:v>45973.1309375</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>45950</x:v>
-      </x:c>
-      <x:c r="J13" s="28" t="n">
-        <x:v>1216020</x:v>
-      </x:c>
-      <x:c r="K13" s="31" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L13" s="32">
-        <x:v>45985.2116666667</x:v>
-      </x:c>
-      <x:c r="M13" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D14" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="27" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F14" s="27" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G14" s="27" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H14" s="29">
-        <x:v>45971.2436226852</x:v>
-      </x:c>
-      <x:c r="I14" s="30">
-        <x:v>45608</x:v>
-      </x:c>
-      <x:c r="J14" s="28" t="n">
-        <x:v>1216004</x:v>
-      </x:c>
-      <x:c r="K14" s="31" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L14" s="32">
-        <x:v>45973.2287268518</x:v>
-      </x:c>
-      <x:c r="M14" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="27" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F15" s="27" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G15" s="27" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H15" s="29">
-        <x:v>45954.4189930556</x:v>
-      </x:c>
-      <x:c r="I15" s="29">
-        <x:v>45954.4190277778</x:v>
-      </x:c>
-      <x:c r="J15" s="28" t="n">
-        <x:v>1215987</x:v>
-      </x:c>
-      <x:c r="K15" s="31" t="n">
-        <x:v>1986</x:v>
-      </x:c>
-      <x:c r="L15" s="32">
-        <x:v>45967.2850694444</x:v>
-      </x:c>
-      <x:c r="M15" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="27" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F16" s="27" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G16" s="27" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H16" s="29">
+      <x:c r="H16" s="13">
         <x:v>45959.2592013889</x:v>
       </x:c>
-      <x:c r="I16" s="29">
+      <x:c r="I16" s="13">
         <x:v>45959.259224537</x:v>
       </x:c>
-      <x:c r="J16" s="28" t="n">
+      <x:c r="J16" s="12" t="n">
         <x:v>1216022</x:v>
       </x:c>
-      <x:c r="K16" s="31" t="n">
+      <x:c r="K16" s="15" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L16" s="32">
+      <x:c r="L16" s="16">
         <x:v>45986.1291898148</x:v>
       </x:c>
-      <x:c r="M16" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="M16" s="11" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s"/>
-      <x:c r="D19" s="16" t="s"/>
-      <x:c r="E19" s="17" t="s"/>
-      <x:c r="F19" s="17" t="s"/>
+      <x:c r="B19" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="22" t="s"/>
     </x:row>
     <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C20" s="19" t="s"/>
-      <x:c r="D20" s="19" t="s"/>
-      <x:c r="E20" s="19" t="s"/>
-      <x:c r="F20" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B20" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
+      <x:c r="B21" s="26" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="21" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="23" t="n">
+      <x:c r="B22" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="21" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="23" t="n">
+      <x:c r="B23" s="26" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="22" t="s"/>
-      <x:c r="F24" s="23" t="n">
+      <x:c r="B24" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="21" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="23" t="n">
+      <x:c r="B25" s="26" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s"/>
-      <x:c r="D26" s="22" t="s"/>
-      <x:c r="E26" s="22" t="s"/>
-      <x:c r="F26" s="23" t="n">
+      <x:c r="B26" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="n">
+      <x:c r="B27" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -10478,291 +10577,267 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="E6" s="11" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45981.1374421296</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216030</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45996.1054282407</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45994.1029050926</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>45169</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216035</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>12780</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46006.2230439815</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
+        <x:v>45973.2824074074</x:v>
+      </x:c>
+      <x:c r="I8" s="35">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="n">
+        <x:v>1216029</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>45993.0810763889</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="33" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="D9" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="33" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="F9" s="33" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="G9" s="33" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45981.1374421296</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216030</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
+      <x:c r="H9" s="34">
+        <x:v>45988.1651388889</x:v>
+      </x:c>
+      <x:c r="I9" s="35">
+        <x:v>45974</x:v>
+      </x:c>
+      <x:c r="J9" s="33" t="n">
+        <x:v>1216036</x:v>
+      </x:c>
+      <x:c r="K9" s="36" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45996.1054282407</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45994.1029050926</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>45169</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216035</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>12780</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46006.2230439815</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45973.2824074074</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1216029</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>45993.0810763889</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
-        <x:v>45988.1651388889</x:v>
-      </x:c>
-      <x:c r="I9" s="30">
-        <x:v>45974</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="n">
-        <x:v>1216036</x:v>
-      </x:c>
-      <x:c r="K9" s="31" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L9" s="32">
+      <x:c r="L9" s="34">
         <x:v>46006.2389583333</x:v>
       </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="M9" s="33" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="B12" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B13" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="B15" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -11827,300 +11902,276 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="E6" s="11" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46033.3509837963</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1216094</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46049.2368865741</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46010.1939351852</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46029</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1216062</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46034.111087963</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
+        <x:v>45989.0397222222</x:v>
+      </x:c>
+      <x:c r="I8" s="35">
+        <x:v>45597</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="n">
+        <x:v>1216078</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="n">
+        <x:v>8280</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46043.2235069444</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="33" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="C9" s="33" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="s"/>
+      <x:c r="E9" s="33" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="F9" s="33" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="G9" s="33" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46033.3509837963</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1216094</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46049.2368865741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46010.1939351852</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46029</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1216062</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46034.111087963</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>45989.0397222222</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>45597</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1216078</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>8280</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>46043.2235069444</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D9" s="28" t="s"/>
-      <x:c r="E9" s="27" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H9" s="29">
+      <x:c r="H9" s="34">
         <x:v>46043.045474537</x:v>
       </x:c>
-      <x:c r="I9" s="29">
+      <x:c r="I9" s="34">
         <x:v>46043.0455092593</x:v>
       </x:c>
-      <x:c r="J9" s="28" t="n">
+      <x:c r="J9" s="33" t="n">
         <x:v>1216091</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="n">
+      <x:c r="K9" s="36" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L9" s="32">
+      <x:c r="L9" s="34">
         <x:v>46048.2516435185</x:v>
       </x:c>
-      <x:c r="M9" s="27" t="s">
-        <x:v>35</x:v>
+      <x:c r="M9" s="33" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="B12" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B13" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="B15" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="B16" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13185,264 +13236,253 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>46058.3038078704</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1195989</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>46066.3127777778</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>46066.3781828704</x:v>
+      </x:c>
+      <x:c r="I7" s="32">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>46077.0856712963</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="33" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C8" s="33" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D8" s="33" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="E8" s="33" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H8" s="34">
+        <x:v>46062.2741666667</x:v>
+      </x:c>
+      <x:c r="I8" s="35">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="34">
+        <x:v>46077.1029513889</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
-        <x:v>46058.3038078704</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>1195989</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="12">
-        <x:v>46066.3127777778</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I7" s="13">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K7" s="14" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="12">
-        <x:v>46077.0856712963</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="28" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="27" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F8" s="27" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G8" s="27" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H8" s="29">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I8" s="30">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J8" s="28" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K8" s="31" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="32">
-        <x:v>46077.1029513889</x:v>
-      </x:c>
-      <x:c r="M8" s="27" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s"/>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="17" t="s"/>
-      <x:c r="F11" s="17" t="s"/>
+      <x:c r="B11" s="20" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="s"/>
+      <x:c r="D11" s="21" t="s"/>
+      <x:c r="E11" s="22" t="s"/>
+      <x:c r="F11" s="22" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="20" t="s">
-        <x:v>27</x:v>
+      <x:c r="B12" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="24" t="s"/>
+      <x:c r="D12" s="24" t="s"/>
+      <x:c r="E12" s="24" t="s"/>
+      <x:c r="F12" s="25" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="B14" s="26" t="s">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="B15" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -32,7 +32,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>PERMIT SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -1162,7 +1162,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1198,39 +1198,43 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1282,7 +1286,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1299,6 +1303,34 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1624,7 +1656,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1664,7 +1696,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>24</x:v>
@@ -1687,7 +1719,7 @@
       <x:c r="H7" s="18">
         <x:v>46077.2833680556</x:v>
       </x:c>
-      <x:c r="I7" s="32">
+      <x:c r="I7" s="33">
         <x:v>46097</x:v>
       </x:c>
       <x:c r="J7" s="17" t="n">
@@ -1706,708 +1738,734 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
+      <x:c r="B8" s="34" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C8" s="33" t="s">
+      <x:c r="C8" s="34" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D8" s="33" t="s">
+      <x:c r="D8" s="34" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E8" s="33" t="s">
+      <x:c r="E8" s="34" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="F8" s="33" t="s">
+      <x:c r="F8" s="34" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G8" s="33" t="s">
+      <x:c r="G8" s="34" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="H8" s="34">
+      <x:c r="H8" s="35">
         <x:v>46076.2809953704</x:v>
       </x:c>
-      <x:c r="I8" s="34">
+      <x:c r="I8" s="35">
         <x:v>46076.2810185185</x:v>
       </x:c>
-      <x:c r="J8" s="33" t="n">
+      <x:c r="J8" s="34" t="n">
         <x:v>1216194</x:v>
       </x:c>
-      <x:c r="K8" s="36" t="n">
+      <x:c r="K8" s="37" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="35">
         <x:v>46097.2411111111</x:v>
       </x:c>
-      <x:c r="M8" s="33" t="s">
+      <x:c r="M8" s="34" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="33" t="s">
+      <x:c r="B9" s="34" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C9" s="33" t="s">
+      <x:c r="C9" s="34" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D9" s="33" t="s">
+      <x:c r="D9" s="34" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E9" s="33" t="s">
+      <x:c r="E9" s="34" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F9" s="33" t="s">
+      <x:c r="F9" s="34" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G9" s="33" t="s">
+      <x:c r="G9" s="34" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H9" s="34">
+      <x:c r="H9" s="35">
         <x:v>46076.245</x:v>
       </x:c>
-      <x:c r="I9" s="34">
+      <x:c r="I9" s="35">
         <x:v>46076.2450115741</x:v>
       </x:c>
-      <x:c r="J9" s="33" t="n">
+      <x:c r="J9" s="34" t="n">
         <x:v>1216190</x:v>
       </x:c>
-      <x:c r="K9" s="36" t="n">
+      <x:c r="K9" s="37" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="35">
         <x:v>46094.1710416667</x:v>
       </x:c>
-      <x:c r="M9" s="33" t="s">
+      <x:c r="M9" s="34" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="38" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="38" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s">
+      <x:c r="D10" s="39" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="E10" s="38" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="38" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="38" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="40">
         <x:v>46076.2578009259</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="40">
         <x:v>46076.2578240741</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="39" t="n">
         <x:v>1216197</x:v>
       </x:c>
-      <x:c r="K10" s="15" t="n">
+      <x:c r="K10" s="42" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="16">
+      <x:c r="L10" s="43">
         <x:v>46097.2583912037</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+      <x:c r="B11" s="38" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="C11" s="38" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="D11" s="39" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="E11" s="38" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="F11" s="38" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="G11" s="38" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="H11" s="40">
         <x:v>46076.2633564815</x:v>
       </x:c>
-      <x:c r="I11" s="13">
+      <x:c r="I11" s="40">
         <x:v>46076.2633680556</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="39" t="n">
         <x:v>1216188</x:v>
       </x:c>
-      <x:c r="K11" s="15" t="n">
+      <x:c r="K11" s="42" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L11" s="16">
+      <x:c r="L11" s="43">
         <x:v>46094.1562731481</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
+      <x:c r="M11" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
+      <x:c r="B12" s="38" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="s">
+      <x:c r="C12" s="38" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="s">
+      <x:c r="D12" s="39" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="E12" s="38" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="F12" s="38" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="G12" s="38" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="H12" s="40">
         <x:v>46076.3755324074</x:v>
       </x:c>
-      <x:c r="I12" s="13">
+      <x:c r="I12" s="40">
         <x:v>46076.3755439815</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="39" t="n">
         <x:v>1216189</x:v>
       </x:c>
-      <x:c r="K12" s="15" t="n">
+      <x:c r="K12" s="42" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="16">
+      <x:c r="L12" s="43">
         <x:v>46094.1653935185</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
+      <x:c r="M12" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
+      <x:c r="B13" s="38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="C13" s="38" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s">
+      <x:c r="D13" s="39" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="E13" s="38" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="F13" s="38" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="G13" s="38" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="H13" s="40">
         <x:v>46046.1343634259</x:v>
       </x:c>
-      <x:c r="I13" s="14">
+      <x:c r="I13" s="41">
         <x:v>45917</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="39" t="n">
         <x:v>1216183</x:v>
       </x:c>
-      <x:c r="K13" s="15" t="n">
+      <x:c r="K13" s="42" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L13" s="16">
+      <x:c r="L13" s="43">
         <x:v>46093.2878703704</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
+      <x:c r="M13" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
+      <x:c r="B14" s="38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C14" s="38" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="s">
+      <x:c r="D14" s="39" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="E14" s="38" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="F14" s="38" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="G14" s="38" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="H14" s="40">
         <x:v>46046.1309027778</x:v>
       </x:c>
-      <x:c r="I14" s="14">
+      <x:c r="I14" s="41">
         <x:v>46021</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="39" t="n">
         <x:v>1216181</x:v>
       </x:c>
-      <x:c r="K14" s="15" t="n">
+      <x:c r="K14" s="42" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L14" s="16">
+      <x:c r="L14" s="43">
         <x:v>46093.273287037</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
+      <x:c r="M14" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B15" s="38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
+      <x:c r="C15" s="38" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="s">
+      <x:c r="D15" s="39" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="E15" s="38" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="F15" s="38" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="G15" s="38" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="H15" s="40">
         <x:v>46046.1237615741</x:v>
       </x:c>
-      <x:c r="I15" s="14">
+      <x:c r="I15" s="41">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="39" t="n">
         <x:v>1216180</x:v>
       </x:c>
-      <x:c r="K15" s="15" t="n">
+      <x:c r="K15" s="42" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L15" s="16">
+      <x:c r="L15" s="43">
         <x:v>46093.2636342593</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
+      <x:c r="M15" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
+      <x:c r="B16" s="38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="C16" s="38" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="D16" s="39" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="E16" s="38" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="F16" s="38" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="G16" s="38" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="H16" s="40">
         <x:v>46046.1140856482</x:v>
       </x:c>
-      <x:c r="I16" s="14">
+      <x:c r="I16" s="41">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="39" t="n">
         <x:v>1216182</x:v>
       </x:c>
-      <x:c r="K16" s="15" t="n">
+      <x:c r="K16" s="42" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L16" s="16">
+      <x:c r="L16" s="43">
         <x:v>46093.2825231481</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
+      <x:c r="M16" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
+      <x:c r="B17" s="38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="s">
+      <x:c r="C17" s="38" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="s">
+      <x:c r="D17" s="39" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="E17" s="38" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="F17" s="38" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="G17" s="38" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="H17" s="40">
         <x:v>46048.0974768518</x:v>
       </x:c>
-      <x:c r="I17" s="14">
+      <x:c r="I17" s="41">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="39" t="n">
         <x:v>1216184</x:v>
       </x:c>
-      <x:c r="K17" s="15" t="n">
+      <x:c r="K17" s="42" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L17" s="16">
+      <x:c r="L17" s="43">
         <x:v>46093.2926041667</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
+      <x:c r="M17" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
+      <x:c r="B18" s="38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="s">
+      <x:c r="C18" s="38" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="s">
+      <x:c r="D18" s="39" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="E18" s="38" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="F18" s="38" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="G18" s="38" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="H18" s="40">
         <x:v>46076.318900463</x:v>
       </x:c>
-      <x:c r="I18" s="14">
+      <x:c r="I18" s="41">
         <x:v>46074</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="39" t="n">
         <x:v>1216168</x:v>
       </x:c>
-      <x:c r="K18" s="15" t="n">
+      <x:c r="K18" s="42" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L18" s="16">
+      <x:c r="L18" s="43">
         <x:v>46092.1400231481</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
+      <x:c r="M18" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
+      <x:c r="B19" s="38" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="C19" s="38" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s">
+      <x:c r="D19" s="39" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="E19" s="38" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
+      <x:c r="F19" s="38" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="s">
+      <x:c r="G19" s="38" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H19" s="13">
+      <x:c r="H19" s="40">
         <x:v>46079.2852546296</x:v>
       </x:c>
-      <x:c r="I19" s="13">
+      <x:c r="I19" s="40">
         <x:v>46079.2852662037</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
+      <x:c r="J19" s="39" t="n">
         <x:v>1216195</x:v>
       </x:c>
-      <x:c r="K19" s="15" t="n">
+      <x:c r="K19" s="42" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L19" s="16">
+      <x:c r="L19" s="43">
         <x:v>46097.2459143518</x:v>
       </x:c>
-      <x:c r="M19" s="11" t="s">
+      <x:c r="M19" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="11" t="s">
+      <x:c r="B20" s="38" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="s">
+      <x:c r="C20" s="38" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="s">
+      <x:c r="D20" s="39" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E20" s="11" t="s">
+      <x:c r="E20" s="38" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="F20" s="11" t="s">
+      <x:c r="F20" s="38" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="G20" s="11" t="s">
+      <x:c r="G20" s="38" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="H20" s="13">
+      <x:c r="H20" s="40">
         <x:v>46079.2747222222</x:v>
       </x:c>
-      <x:c r="I20" s="13">
+      <x:c r="I20" s="40">
         <x:v>46079.2747453704</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="n">
+      <x:c r="J20" s="39" t="n">
         <x:v>1216196</x:v>
       </x:c>
-      <x:c r="K20" s="15" t="n">
+      <x:c r="K20" s="42" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L20" s="16">
+      <x:c r="L20" s="43">
         <x:v>46097.2536342593</x:v>
       </x:c>
-      <x:c r="M20" s="11" t="s">
+      <x:c r="M20" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="11" t="s">
+      <x:c r="B21" s="38" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="11" t="s">
+      <x:c r="C21" s="38" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="s"/>
-      <x:c r="E21" s="11" t="s">
+      <x:c r="D21" s="39" t="s"/>
+      <x:c r="E21" s="38" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="F21" s="11" t="s">
+      <x:c r="F21" s="38" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G21" s="11" t="s">
+      <x:c r="G21" s="38" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="H21" s="13">
+      <x:c r="H21" s="40">
         <x:v>46090.2854050926</x:v>
       </x:c>
-      <x:c r="I21" s="13">
+      <x:c r="I21" s="40">
         <x:v>46090.2854282407</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="s">
+      <x:c r="J21" s="39" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="K21" s="15" t="n">
+      <x:c r="K21" s="42" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L21" s="16">
+      <x:c r="L21" s="43">
         <x:v>46094.0865740741</x:v>
       </x:c>
-      <x:c r="M21" s="11" t="s">
+      <x:c r="M21" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="11" t="s">
+      <x:c r="B22" s="38" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C22" s="11" t="s">
+      <x:c r="C22" s="38" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="s"/>
-      <x:c r="E22" s="11" t="s">
+      <x:c r="D22" s="39" t="s"/>
+      <x:c r="E22" s="38" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="F22" s="11" t="s">
+      <x:c r="F22" s="38" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G22" s="11" t="s">
+      <x:c r="G22" s="38" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="H22" s="13">
+      <x:c r="H22" s="40">
         <x:v>46090.2540972222</x:v>
       </x:c>
-      <x:c r="I22" s="13">
+      <x:c r="I22" s="40">
         <x:v>46090.2541203704</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="n">
+      <x:c r="J22" s="39" t="n">
         <x:v>1216185</x:v>
       </x:c>
-      <x:c r="K22" s="15" t="n">
+      <x:c r="K22" s="42" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L22" s="16">
+      <x:c r="L22" s="43">
         <x:v>46094.0818981481</x:v>
       </x:c>
-      <x:c r="M22" s="11" t="s">
+      <x:c r="M22" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="11" t="s">
+      <x:c r="B23" s="38" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="11" t="s">
+      <x:c r="C23" s="38" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="s"/>
-      <x:c r="E23" s="11" t="s">
+      <x:c r="D23" s="39" t="s"/>
+      <x:c r="E23" s="38" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="F23" s="11" t="s">
+      <x:c r="F23" s="38" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G23" s="11" t="s">
+      <x:c r="G23" s="38" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="H23" s="13">
+      <x:c r="H23" s="40">
         <x:v>46090.2349189815</x:v>
       </x:c>
-      <x:c r="I23" s="13">
+      <x:c r="I23" s="40">
         <x:v>46090.2349305556</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="n">
+      <x:c r="J23" s="39" t="n">
         <x:v>1216187</x:v>
       </x:c>
-      <x:c r="K23" s="15" t="n">
+      <x:c r="K23" s="42" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L23" s="16">
+      <x:c r="L23" s="43">
         <x:v>46094.0939351852</x:v>
       </x:c>
-      <x:c r="M23" s="11" t="s">
+      <x:c r="M23" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="20" t="s">
+    <x:row r="24" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B24" s="44" t="s"/>
+      <x:c r="C24" s="44" t="s"/>
+      <x:c r="D24" s="44" t="s"/>
+      <x:c r="E24" s="44" t="s"/>
+      <x:c r="F24" s="44" t="s"/>
+      <x:c r="G24" s="44" t="s"/>
+      <x:c r="H24" s="44" t="s"/>
+      <x:c r="I24" s="44" t="s"/>
+      <x:c r="J24" s="44" t="s"/>
+      <x:c r="K24" s="44" t="s"/>
+      <x:c r="L24" s="44" t="s"/>
+      <x:c r="M24" s="44" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B25" s="44" t="s"/>
+      <x:c r="C25" s="44" t="s"/>
+      <x:c r="D25" s="44" t="s"/>
+      <x:c r="E25" s="44" t="s"/>
+      <x:c r="F25" s="44" t="s"/>
+      <x:c r="G25" s="44" t="s"/>
+      <x:c r="H25" s="44" t="s"/>
+      <x:c r="I25" s="44" t="s"/>
+      <x:c r="J25" s="44" t="s"/>
+      <x:c r="K25" s="44" t="s"/>
+      <x:c r="L25" s="44" t="s"/>
+      <x:c r="M25" s="44" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C26" s="21" t="s"/>
-      <x:c r="D26" s="21" t="s"/>
-      <x:c r="E26" s="22" t="s"/>
-      <x:c r="F26" s="22" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="23" t="s">
+      <x:c r="C28" s="22" t="s"/>
+      <x:c r="D28" s="22" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="23" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C27" s="24" t="s"/>
-      <x:c r="D27" s="24" t="s"/>
-      <x:c r="E27" s="24" t="s"/>
-      <x:c r="F27" s="25" t="s">
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="27" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="C30" s="28" t="s"/>
+      <x:c r="D30" s="28" t="s"/>
+      <x:c r="E30" s="28" t="s"/>
+      <x:c r="F30" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="27" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="27" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="C33" s="28" t="s"/>
+      <x:c r="D33" s="28" t="s"/>
+      <x:c r="E33" s="28" t="s"/>
+      <x:c r="F33" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="27" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C34" s="28" t="s"/>
+      <x:c r="D34" s="28" t="s"/>
+      <x:c r="E34" s="28" t="s"/>
+      <x:c r="F34" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="27" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="C35" s="28" t="s"/>
+      <x:c r="D35" s="28" t="s"/>
+      <x:c r="E35" s="28" t="s"/>
+      <x:c r="F35" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="29" t="s">
+    <x:row r="36" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B36" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C34" s="30" t="s"/>
-      <x:c r="D34" s="30" t="s"/>
-      <x:c r="E34" s="30" t="s"/>
-      <x:c r="F34" s="31" t="n">
+      <x:c r="C36" s="31" t="s"/>
+      <x:c r="D36" s="31" t="s"/>
+      <x:c r="E36" s="31" t="s"/>
+      <x:c r="F36" s="32" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3366,18 +3424,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B26:F26"/>
-    <x:mergeCell ref="B27:E27"/>
-    <x:mergeCell ref="B28:E28"/>
+  <x:mergeCells count="12">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B28:F28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3455,7 +3514,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45839</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -3516,7 +3575,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -3556,7 +3615,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>8</x:v>
@@ -3594,90 +3653,90 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+      <x:c r="B8" s="20" t="s"/>
+      <x:c r="C8" s="20" t="s"/>
+      <x:c r="D8" s="20" t="s"/>
+      <x:c r="E8" s="20" t="s"/>
+      <x:c r="F8" s="20" t="s"/>
+      <x:c r="G8" s="20" t="s"/>
+      <x:c r="H8" s="20" t="s"/>
+      <x:c r="I8" s="20" t="s"/>
+      <x:c r="J8" s="20" t="s"/>
+      <x:c r="K8" s="20" t="s"/>
+      <x:c r="L8" s="20" t="s"/>
+      <x:c r="M8" s="20" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="20" t="s"/>
+      <x:c r="C9" s="20" t="s"/>
+      <x:c r="D9" s="20" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="20" t="s"/>
+      <x:c r="H9" s="20" t="s"/>
+      <x:c r="I9" s="20" t="s"/>
+      <x:c r="J9" s="20" t="s"/>
+      <x:c r="K9" s="20" t="s"/>
+      <x:c r="L9" s="20" t="s"/>
+      <x:c r="M9" s="20" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="22" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="23" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="s">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="27" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4656,14 +4715,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -4741,7 +4801,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45870</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -4802,7 +4862,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -4842,7 +4902,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>24</x:v>
@@ -4865,7 +4925,7 @@
       <x:c r="H7" s="18">
         <x:v>45875.2238888889</x:v>
       </x:c>
-      <x:c r="I7" s="32">
+      <x:c r="I7" s="33">
         <x:v>45921</x:v>
       </x:c>
       <x:c r="J7" s="17" t="n">
@@ -4884,232 +4944,3076 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
+      <x:c r="B8" s="34" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C8" s="33" t="s">
+      <x:c r="C8" s="34" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="33" t="s">
+      <x:c r="D8" s="34" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E8" s="33" t="s">
+      <x:c r="E8" s="34" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F8" s="33" t="s">
+      <x:c r="F8" s="34" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G8" s="33" t="s">
+      <x:c r="G8" s="34" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H8" s="34">
+      <x:c r="H8" s="35">
         <x:v>45880.1214814815</x:v>
       </x:c>
+      <x:c r="I8" s="36">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1346457</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45881.1618981482</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s"/>
+      <x:c r="E9" s="34" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>45873.2195486111</x:v>
+      </x:c>
+      <x:c r="I9" s="35">
+        <x:v>45873.2195601852</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1195700</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>45882.1150694444</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="38" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="38" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D10" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="38" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="38" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G10" s="38" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H10" s="40">
+        <x:v>45875.361724537</x:v>
+      </x:c>
+      <x:c r="I10" s="41">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J10" s="39" t="n">
+        <x:v>1215851</x:v>
+      </x:c>
+      <x:c r="K10" s="42" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="43">
+        <x:v>45876.2230902778</x:v>
+      </x:c>
+      <x:c r="M10" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="38" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="38" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="38" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F11" s="38" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G11" s="38" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H11" s="40">
+        <x:v>45875.2324652778</x:v>
+      </x:c>
+      <x:c r="I11" s="41">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J11" s="39" t="n">
+        <x:v>1215852</x:v>
+      </x:c>
+      <x:c r="K11" s="42" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="43">
+        <x:v>45876.2319791667</x:v>
+      </x:c>
+      <x:c r="M11" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B12" s="44" t="s"/>
+      <x:c r="C12" s="44" t="s"/>
+      <x:c r="D12" s="44" t="s"/>
+      <x:c r="E12" s="44" t="s"/>
+      <x:c r="F12" s="44" t="s"/>
+      <x:c r="G12" s="44" t="s"/>
+      <x:c r="H12" s="44" t="s"/>
+      <x:c r="I12" s="44" t="s"/>
+      <x:c r="J12" s="44" t="s"/>
+      <x:c r="K12" s="44" t="s"/>
+      <x:c r="L12" s="44" t="s"/>
+      <x:c r="M12" s="44" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B13" s="44" t="s"/>
+      <x:c r="C13" s="44" t="s"/>
+      <x:c r="D13" s="44" t="s"/>
+      <x:c r="E13" s="44" t="s"/>
+      <x:c r="F13" s="44" t="s"/>
+      <x:c r="G13" s="44" t="s"/>
+      <x:c r="H13" s="44" t="s"/>
+      <x:c r="I13" s="44" t="s"/>
+      <x:c r="J13" s="44" t="s"/>
+      <x:c r="K13" s="44" t="s"/>
+      <x:c r="L13" s="44" t="s"/>
+      <x:c r="M13" s="44" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="23" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="27" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="27" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C22" s="31" t="s"/>
+      <x:c r="D22" s="31" t="s"/>
+      <x:c r="E22" s="31" t="s"/>
+      <x:c r="F22" s="32" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="10">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B16:F16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45915.355787037</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215901</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45918.2339583333</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E7" s="17" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45903.3849652778</x:v>
+      </x:c>
+      <x:c r="I7" s="33">
+        <x:v>45916</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215886</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>3150</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45908.2848958333</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45919.4023032407</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>45926</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1215905</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45925.945150463</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>45918.1053935185</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>45900</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1215910</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>45929.2194097222</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="38" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="38" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D10" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="38" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F10" s="38" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G10" s="38" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H10" s="40">
+        <x:v>45908.2183449074</x:v>
+      </x:c>
+      <x:c r="I10" s="41">
+        <x:v>45918</x:v>
+      </x:c>
+      <x:c r="J10" s="39" t="n">
+        <x:v>1215894</x:v>
+      </x:c>
+      <x:c r="K10" s="42" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="43">
+        <x:v>45912.1906134259</x:v>
+      </x:c>
+      <x:c r="M10" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="38" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="38" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D11" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="38" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F11" s="38" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G11" s="38" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H11" s="40">
+        <x:v>45922.1415393519</x:v>
+      </x:c>
+      <x:c r="I11" s="41">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J11" s="39" t="n">
+        <x:v>1346550</x:v>
+      </x:c>
+      <x:c r="K11" s="42" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="43">
+        <x:v>45922.1832523148</x:v>
+      </x:c>
+      <x:c r="M11" s="38" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C12" s="38" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D12" s="39" t="s"/>
+      <x:c r="E12" s="38" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F12" s="38" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G12" s="38" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H12" s="40">
+        <x:v>45919.473287037</x:v>
+      </x:c>
+      <x:c r="I12" s="40">
+        <x:v>45919.4732986111</x:v>
+      </x:c>
+      <x:c r="J12" s="39" t="n">
+        <x:v>1215906</x:v>
+      </x:c>
+      <x:c r="K12" s="42" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L12" s="43">
+        <x:v>45926.2586111111</x:v>
+      </x:c>
+      <x:c r="M12" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B13" s="44" t="s"/>
+      <x:c r="C13" s="44" t="s"/>
+      <x:c r="D13" s="44" t="s"/>
+      <x:c r="E13" s="44" t="s"/>
+      <x:c r="F13" s="44" t="s"/>
+      <x:c r="G13" s="44" t="s"/>
+      <x:c r="H13" s="44" t="s"/>
+      <x:c r="I13" s="44" t="s"/>
+      <x:c r="J13" s="44" t="s"/>
+      <x:c r="K13" s="44" t="s"/>
+      <x:c r="L13" s="44" t="s"/>
+      <x:c r="M13" s="44" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B14" s="44" t="s"/>
+      <x:c r="C14" s="44" t="s"/>
+      <x:c r="D14" s="44" t="s"/>
+      <x:c r="E14" s="44" t="s"/>
+      <x:c r="F14" s="44" t="s"/>
+      <x:c r="G14" s="44" t="s"/>
+      <x:c r="H14" s="44" t="s"/>
+      <x:c r="I14" s="44" t="s"/>
+      <x:c r="J14" s="44" t="s"/>
+      <x:c r="K14" s="44" t="s"/>
+      <x:c r="L14" s="44" t="s"/>
+      <x:c r="M14" s="44" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="23" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="28" t="s"/>
+      <x:c r="D19" s="28" t="s"/>
+      <x:c r="E19" s="28" t="s"/>
+      <x:c r="F19" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="27" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="27" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C23" s="31" t="s"/>
+      <x:c r="D23" s="31" t="s"/>
+      <x:c r="E23" s="31" t="s"/>
+      <x:c r="F23" s="32" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="10">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B17:F17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B6" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>45933.0884375</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>45932</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>1215922</x:v>
+      </x:c>
+      <x:c r="K6" s="15" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L6" s="16">
+        <x:v>45936.014837963</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s"/>
+      <x:c r="E7" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F7" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G7" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H7" s="18">
+        <x:v>45928.9304513889</x:v>
+      </x:c>
+      <x:c r="I7" s="18">
+        <x:v>45928.9304861111</x:v>
+      </x:c>
+      <x:c r="J7" s="17" t="n">
+        <x:v>1215924</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L7" s="18">
+        <x:v>45938.0359375</x:v>
+      </x:c>
+      <x:c r="M7" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s"/>
+      <x:c r="E8" s="34" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45926.4563888889</x:v>
+      </x:c>
       <x:c r="I8" s="35">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J8" s="33" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K8" s="36" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L8" s="34">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M8" s="33" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="33" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="s"/>
-      <x:c r="E9" s="33" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H9" s="34">
-        <x:v>45873.2195486111</x:v>
-      </x:c>
-      <x:c r="I9" s="34">
-        <x:v>45873.2195601852</x:v>
-      </x:c>
-      <x:c r="J9" s="33" t="n">
-        <x:v>1195700</x:v>
-      </x:c>
-      <x:c r="K9" s="36" t="n">
-        <x:v>2790</x:v>
-      </x:c>
-      <x:c r="L9" s="34">
-        <x:v>45882.1150694444</x:v>
-      </x:c>
-      <x:c r="M9" s="33" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+        <x:v>45926.4564351852</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1215917</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45932.239537037</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="20" t="s"/>
+      <x:c r="C9" s="20" t="s"/>
+      <x:c r="D9" s="20" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="20" t="s"/>
+      <x:c r="H9" s="20" t="s"/>
+      <x:c r="I9" s="20" t="s"/>
+      <x:c r="J9" s="20" t="s"/>
+      <x:c r="K9" s="20" t="s"/>
+      <x:c r="L9" s="20" t="s"/>
+      <x:c r="M9" s="20" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B10" s="44" t="s"/>
+      <x:c r="C10" s="44" t="s"/>
+      <x:c r="D10" s="44" t="s"/>
+      <x:c r="E10" s="44" t="s"/>
+      <x:c r="F10" s="44" t="s"/>
+      <x:c r="G10" s="44" t="s"/>
+      <x:c r="H10" s="44" t="s"/>
+      <x:c r="I10" s="44" t="s"/>
+      <x:c r="J10" s="44" t="s"/>
+      <x:c r="K10" s="44" t="s"/>
+      <x:c r="L10" s="44" t="s"/>
+      <x:c r="M10" s="44" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="23" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="27" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E10" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H10" s="13">
-        <x:v>45875.361724537</x:v>
-      </x:c>
-      <x:c r="I10" s="14">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="n">
-        <x:v>1215851</x:v>
-      </x:c>
-      <x:c r="K10" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="16">
-        <x:v>45876.2230902778</x:v>
-      </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H11" s="13">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I11" s="14">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K11" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="16">
-        <x:v>45876.2319791667</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6084,16 +8988,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B14:F14"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -6110,7 +9013,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6171,7 +9074,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45901</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -6232,360 +9135,550 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>44</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H6" s="13">
-        <x:v>45915.355787037</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45851</x:v>
+        <x:v>45951.1032638889</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>45951.103287037</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
-        <x:v>1215901</x:v>
+        <x:v>1346752</x:v>
       </x:c>
       <x:c r="K6" s="15" t="n">
-        <x:v>2550</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L6" s="16">
-        <x:v>45918.2339583333</x:v>
+        <x:v>45971.0888194444</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>48</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="17" t="s">
-        <x:v>49</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E7" s="17" t="s">
-        <x:v>50</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F7" s="17" t="s">
-        <x:v>51</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G7" s="17" t="s">
-        <x:v>52</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H7" s="18">
-        <x:v>45903.3849652778</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>45916</x:v>
+        <x:v>45980.2160416667</x:v>
+      </x:c>
+      <x:c r="I7" s="33">
+        <x:v>45979</x:v>
       </x:c>
       <x:c r="J7" s="17" t="n">
-        <x:v>1215886</x:v>
+        <x:v>1346786</x:v>
       </x:c>
       <x:c r="K7" s="19" t="n">
-        <x:v>3150</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L7" s="18">
-        <x:v>45908.2848958333</x:v>
+        <x:v>45985.3594791667</x:v>
       </x:c>
       <x:c r="M7" s="17" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
+      <x:c r="B8" s="34" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45965.2736689815</x:v>
+      </x:c>
+      <x:c r="I8" s="35">
+        <x:v>45965.2736921296</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1216000</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45972.1539583333</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="33" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="s">
+      <x:c r="C9" s="34" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E8" s="33" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H8" s="34">
-        <x:v>45919.4023032407</x:v>
-      </x:c>
-      <x:c r="I8" s="35">
-        <x:v>45926</x:v>
-      </x:c>
-      <x:c r="J8" s="33" t="n">
-        <x:v>1215905</x:v>
-      </x:c>
-      <x:c r="K8" s="36" t="n">
+      <x:c r="E9" s="34" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>45965.2661458333</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1215999</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="34">
-        <x:v>45925.945150463</x:v>
-      </x:c>
-      <x:c r="M8" s="33" t="s">
+      <x:c r="L9" s="35">
+        <x:v>45972.1364236111</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="33" t="s">
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="38" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="33" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="s">
+      <x:c r="C10" s="38" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D10" s="39" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E9" s="33" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H9" s="34">
-        <x:v>45918.1053935185</x:v>
-      </x:c>
-      <x:c r="I9" s="35">
-        <x:v>45900</x:v>
-      </x:c>
-      <x:c r="J9" s="33" t="n">
-        <x:v>1215910</x:v>
-      </x:c>
-      <x:c r="K9" s="36" t="n">
+      <x:c r="E10" s="38" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F10" s="38" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G10" s="38" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H10" s="40">
+        <x:v>45953.5328240741</x:v>
+      </x:c>
+      <x:c r="I10" s="41">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J10" s="39" t="n">
+        <x:v>1215970</x:v>
+      </x:c>
+      <x:c r="K10" s="42" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="43">
+        <x:v>45966.0458101852</x:v>
+      </x:c>
+      <x:c r="M10" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="38" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="38" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D11" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E11" s="38" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F11" s="38" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G11" s="38" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H11" s="40">
+        <x:v>45959.0699074074</x:v>
+      </x:c>
+      <x:c r="I11" s="41">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J11" s="39" t="n">
+        <x:v>1346761</x:v>
+      </x:c>
+      <x:c r="K11" s="42" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="43">
+        <x:v>45972.2719560185</x:v>
+      </x:c>
+      <x:c r="M11" s="38" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="38" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="38" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D12" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E12" s="38" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F12" s="38" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G12" s="38" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H12" s="40">
+        <x:v>45958.0724421296</x:v>
+      </x:c>
+      <x:c r="I12" s="41">
+        <x:v>45810</x:v>
+      </x:c>
+      <x:c r="J12" s="39" t="n">
+        <x:v>1216003</x:v>
+      </x:c>
+      <x:c r="K12" s="42" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L9" s="34">
-        <x:v>45929.2194097222</x:v>
-      </x:c>
-      <x:c r="M9" s="33" t="s">
+      <x:c r="L12" s="43">
+        <x:v>45973.0584490741</x:v>
+      </x:c>
+      <x:c r="M12" s="38" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="38" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D13" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F13" s="38" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G13" s="38" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H13" s="40">
+        <x:v>45973.1309375</x:v>
+      </x:c>
+      <x:c r="I13" s="41">
+        <x:v>45950</x:v>
+      </x:c>
+      <x:c r="J13" s="39" t="n">
+        <x:v>1216020</x:v>
+      </x:c>
+      <x:c r="K13" s="42" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L13" s="43">
+        <x:v>45985.2116666667</x:v>
+      </x:c>
+      <x:c r="M13" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="38" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C14" s="38" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D14" s="39" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E14" s="38" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F14" s="38" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G14" s="38" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="H14" s="40">
+        <x:v>45971.2436226852</x:v>
+      </x:c>
+      <x:c r="I14" s="41">
+        <x:v>45608</x:v>
+      </x:c>
+      <x:c r="J14" s="39" t="n">
+        <x:v>1216004</x:v>
+      </x:c>
+      <x:c r="K14" s="42" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L14" s="43">
+        <x:v>45973.2287268518</x:v>
+      </x:c>
+      <x:c r="M14" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C15" s="38" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D15" s="39" t="s"/>
+      <x:c r="E15" s="38" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F15" s="38" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G15" s="38" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H15" s="40">
+        <x:v>45954.4189930556</x:v>
+      </x:c>
+      <x:c r="I15" s="40">
+        <x:v>45954.4190277778</x:v>
+      </x:c>
+      <x:c r="J15" s="39" t="n">
+        <x:v>1215987</x:v>
+      </x:c>
+      <x:c r="K15" s="42" t="n">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="L15" s="43">
+        <x:v>45967.2850694444</x:v>
+      </x:c>
+      <x:c r="M15" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="38" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C16" s="38" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D16" s="39" t="s"/>
+      <x:c r="E16" s="38" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F16" s="38" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G16" s="38" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H16" s="40">
+        <x:v>45959.2592013889</x:v>
+      </x:c>
+      <x:c r="I16" s="40">
+        <x:v>45959.259224537</x:v>
+      </x:c>
+      <x:c r="J16" s="39" t="n">
+        <x:v>1216022</x:v>
+      </x:c>
+      <x:c r="K16" s="42" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L16" s="43">
+        <x:v>45986.1291898148</x:v>
+      </x:c>
+      <x:c r="M16" s="38" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B17" s="44" t="s"/>
+      <x:c r="C17" s="44" t="s"/>
+      <x:c r="D17" s="44" t="s"/>
+      <x:c r="E17" s="44" t="s"/>
+      <x:c r="F17" s="44" t="s"/>
+      <x:c r="G17" s="44" t="s"/>
+      <x:c r="H17" s="44" t="s"/>
+      <x:c r="I17" s="44" t="s"/>
+      <x:c r="J17" s="44" t="s"/>
+      <x:c r="K17" s="44" t="s"/>
+      <x:c r="L17" s="44" t="s"/>
+      <x:c r="M17" s="44" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B18" s="44" t="s"/>
+      <x:c r="C18" s="44" t="s"/>
+      <x:c r="D18" s="44" t="s"/>
+      <x:c r="E18" s="44" t="s"/>
+      <x:c r="F18" s="44" t="s"/>
+      <x:c r="G18" s="44" t="s"/>
+      <x:c r="H18" s="44" t="s"/>
+      <x:c r="I18" s="44" t="s"/>
+      <x:c r="J18" s="44" t="s"/>
+      <x:c r="K18" s="44" t="s"/>
+      <x:c r="L18" s="44" t="s"/>
+      <x:c r="M18" s="44" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="23" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="27" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H10" s="13">
-        <x:v>45908.2183449074</x:v>
-      </x:c>
-      <x:c r="I10" s="14">
-        <x:v>45918</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="n">
-        <x:v>1215894</x:v>
-      </x:c>
-      <x:c r="K10" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="16">
-        <x:v>45912.1906134259</x:v>
-      </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C24" s="28" t="s"/>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="28" t="s"/>
+      <x:c r="F24" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H11" s="13">
-        <x:v>45922.1415393519</x:v>
-      </x:c>
-      <x:c r="I11" s="14">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="n">
-        <x:v>1346550</x:v>
-      </x:c>
-      <x:c r="K11" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="16">
-        <x:v>45922.1832523148</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="27" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C25" s="28" t="s"/>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="28" t="s"/>
+      <x:c r="F25" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="27" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="28" t="s"/>
+      <x:c r="D26" s="28" t="s"/>
+      <x:c r="E26" s="28" t="s"/>
+      <x:c r="F26" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="27" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="27" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="s"/>
-      <x:c r="E12" s="11" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H12" s="13">
-        <x:v>45919.473287037</x:v>
-      </x:c>
-      <x:c r="I12" s="13">
-        <x:v>45919.4732986111</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="n">
-        <x:v>1215906</x:v>
-      </x:c>
-      <x:c r="K12" s="15" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L12" s="16">
-        <x:v>45926.2586111111</x:v>
-      </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B29" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C29" s="31" t="s"/>
+      <x:c r="D29" s="31" t="s"/>
+      <x:c r="E29" s="31" t="s"/>
+      <x:c r="F29" s="32" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7551,16 +10644,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
+  <x:mergeCells count="12">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B21:F21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -7577,7 +10673,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="0" summaryRight="0"/>
@@ -7638,7 +10734,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45931</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -7699,39 +10795,39 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>73</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>74</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>75</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>76</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H6" s="13">
-        <x:v>45933.0884375</x:v>
+        <x:v>45981.1374421296</x:v>
       </x:c>
       <x:c r="I6" s="14">
-        <x:v>45932</x:v>
+        <x:v>45969</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
-        <x:v>1215922</x:v>
+        <x:v>1216030</x:v>
       </x:c>
       <x:c r="K6" s="15" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L6" s="16">
-        <x:v>45936.014837963</x:v>
+        <x:v>45996.1054282407</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
         <x:v>23</x:v>
@@ -7739,38 +10835,40 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s"/>
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="E7" s="17" t="s">
-        <x:v>78</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F7" s="17" t="s">
-        <x:v>79</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G7" s="17" t="s">
-        <x:v>80</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H7" s="18">
-        <x:v>45928.9304513889</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>45928.9304861111</x:v>
+        <x:v>45994.1029050926</x:v>
+      </x:c>
+      <x:c r="I7" s="33">
+        <x:v>45169</x:v>
       </x:c>
       <x:c r="J7" s="17" t="n">
-        <x:v>1215924</x:v>
+        <x:v>1216035</x:v>
       </x:c>
       <x:c r="K7" s="19" t="n">
-        <x:v>456</x:v>
+        <x:v>12780</x:v>
       </x:c>
       <x:c r="L7" s="18">
-        <x:v>45938.0359375</x:v>
+        <x:v>46006.2230439815</x:v>
       </x:c>
       <x:c r="M7" s="17" t="s">
         <x:v>23</x:v>
@@ -7779,111 +10877,153 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="s"/>
-      <x:c r="E8" s="33" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H8" s="34">
-        <x:v>45926.4563888889</x:v>
-      </x:c>
-      <x:c r="I8" s="34">
-        <x:v>45926.4564351852</x:v>
-      </x:c>
-      <x:c r="J8" s="33" t="n">
-        <x:v>1215917</x:v>
-      </x:c>
-      <x:c r="K8" s="36" t="n">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="L8" s="34">
-        <x:v>45932.239537037</x:v>
-      </x:c>
-      <x:c r="M8" s="33" t="s">
+      <x:c r="B8" s="34" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45973.2824074074</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1216029</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>45993.0810763889</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="34" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>45988.1651388889</x:v>
+      </x:c>
+      <x:c r="I9" s="36">
+        <x:v>45974</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1216036</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>46006.2389583333</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B10" s="44" t="s"/>
+      <x:c r="C10" s="44" t="s"/>
+      <x:c r="D10" s="44" t="s"/>
+      <x:c r="E10" s="44" t="s"/>
+      <x:c r="F10" s="44" t="s"/>
+      <x:c r="G10" s="44" t="s"/>
+      <x:c r="H10" s="44" t="s"/>
+      <x:c r="I10" s="44" t="s"/>
+      <x:c r="J10" s="44" t="s"/>
+      <x:c r="K10" s="44" t="s"/>
+      <x:c r="L10" s="44" t="s"/>
+      <x:c r="M10" s="44" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B11" s="44" t="s"/>
+      <x:c r="C11" s="44" t="s"/>
+      <x:c r="D11" s="44" t="s"/>
+      <x:c r="E11" s="44" t="s"/>
+      <x:c r="F11" s="44" t="s"/>
+      <x:c r="G11" s="44" t="s"/>
+      <x:c r="H11" s="44" t="s"/>
+      <x:c r="I11" s="44" t="s"/>
+      <x:c r="J11" s="44" t="s"/>
+      <x:c r="K11" s="44" t="s"/>
+      <x:c r="L11" s="44" t="s"/>
+      <x:c r="M11" s="44" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8862,13 +12002,13 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -8885,7 +12025,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8946,7 +12086,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45962</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -9007,522 +12147,253 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>85</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>87</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H6" s="13">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45951.103287037</x:v>
+        <x:v>46033.3509837963</x:v>
+      </x:c>
+      <x:c r="I6" s="14">
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
-        <x:v>1346752</x:v>
+        <x:v>1216094</x:v>
       </x:c>
       <x:c r="K6" s="15" t="n">
-        <x:v>130</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L6" s="16">
-        <x:v>45971.0888194444</x:v>
+        <x:v>46049.2368865741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>2</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D7" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E7" s="17" t="s">
-        <x:v>90</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F7" s="17" t="s">
-        <x:v>91</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G7" s="17" t="s">
-        <x:v>92</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H7" s="18">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>45979</x:v>
+        <x:v>46010.1939351852</x:v>
+      </x:c>
+      <x:c r="I7" s="33">
+        <x:v>46029</x:v>
       </x:c>
       <x:c r="J7" s="17" t="n">
-        <x:v>1346786</x:v>
+        <x:v>1216062</x:v>
       </x:c>
       <x:c r="K7" s="19" t="n">
-        <x:v>5280</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L7" s="18">
-        <x:v>45985.3594791667</x:v>
+        <x:v>46034.111087963</x:v>
       </x:c>
       <x:c r="M7" s="17" t="s">
-        <x:v>7</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H8" s="34">
-        <x:v>45965.2736689815</x:v>
-      </x:c>
-      <x:c r="I8" s="34">
-        <x:v>45965.2736921296</x:v>
-      </x:c>
-      <x:c r="J8" s="33" t="n">
-        <x:v>1216000</x:v>
-      </x:c>
-      <x:c r="K8" s="36" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="34">
-        <x:v>45972.1539583333</x:v>
-      </x:c>
-      <x:c r="M8" s="33" t="s">
+      <x:c r="B8" s="34" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>45989.0397222222</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>45597</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1216078</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>8280</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>46043.2235069444</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="33" t="s">
+      <x:c r="B9" s="34" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="s"/>
+      <x:c r="E9" s="34" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H9" s="35">
+        <x:v>46043.045474537</x:v>
+      </x:c>
+      <x:c r="I9" s="35">
+        <x:v>46043.0455092593</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="n">
+        <x:v>1216091</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="n">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="L9" s="35">
+        <x:v>46048.2516435185</x:v>
+      </x:c>
+      <x:c r="M9" s="34" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B10" s="44" t="s"/>
+      <x:c r="C10" s="44" t="s"/>
+      <x:c r="D10" s="44" t="s"/>
+      <x:c r="E10" s="44" t="s"/>
+      <x:c r="F10" s="44" t="s"/>
+      <x:c r="G10" s="44" t="s"/>
+      <x:c r="H10" s="44" t="s"/>
+      <x:c r="I10" s="44" t="s"/>
+      <x:c r="J10" s="44" t="s"/>
+      <x:c r="K10" s="44" t="s"/>
+      <x:c r="L10" s="44" t="s"/>
+      <x:c r="M10" s="44" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B11" s="44" t="s"/>
+      <x:c r="C11" s="44" t="s"/>
+      <x:c r="D11" s="44" t="s"/>
+      <x:c r="E11" s="44" t="s"/>
+      <x:c r="F11" s="44" t="s"/>
+      <x:c r="G11" s="44" t="s"/>
+      <x:c r="H11" s="44" t="s"/>
+      <x:c r="I11" s="44" t="s"/>
+      <x:c r="J11" s="44" t="s"/>
+      <x:c r="K11" s="44" t="s"/>
+      <x:c r="L11" s="44" t="s"/>
+      <x:c r="M11" s="44" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="23" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="33" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="s">
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E9" s="33" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H9" s="34">
-        <x:v>45965.2661458333</x:v>
-      </x:c>
-      <x:c r="I9" s="35">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J9" s="33" t="n">
-        <x:v>1215999</x:v>
-      </x:c>
-      <x:c r="K9" s="36" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="34">
-        <x:v>45972.1364236111</x:v>
-      </x:c>
-      <x:c r="M9" s="33" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="27" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H10" s="13">
-        <x:v>45953.5328240741</x:v>
-      </x:c>
-      <x:c r="I10" s="14">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J10" s="12" t="n">
-        <x:v>1215970</x:v>
-      </x:c>
-      <x:c r="K10" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="16">
-        <x:v>45966.0458101852</x:v>
-      </x:c>
-      <x:c r="M10" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H11" s="13">
-        <x:v>45959.0699074074</x:v>
-      </x:c>
-      <x:c r="I11" s="14">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="n">
-        <x:v>1346761</x:v>
-      </x:c>
-      <x:c r="K11" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="16">
-        <x:v>45972.2719560185</x:v>
-      </x:c>
-      <x:c r="M11" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H12" s="13">
-        <x:v>45958.0724421296</x:v>
-      </x:c>
-      <x:c r="I12" s="14">
-        <x:v>45810</x:v>
-      </x:c>
-      <x:c r="J12" s="12" t="n">
-        <x:v>1216003</x:v>
-      </x:c>
-      <x:c r="K12" s="15" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L12" s="16">
-        <x:v>45973.0584490741</x:v>
-      </x:c>
-      <x:c r="M12" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H13" s="13">
-        <x:v>45973.1309375</x:v>
-      </x:c>
-      <x:c r="I13" s="14">
-        <x:v>45950</x:v>
-      </x:c>
-      <x:c r="J13" s="12" t="n">
-        <x:v>1216020</x:v>
-      </x:c>
-      <x:c r="K13" s="15" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L13" s="16">
-        <x:v>45985.2116666667</x:v>
-      </x:c>
-      <x:c r="M13" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H14" s="13">
-        <x:v>45971.2436226852</x:v>
-      </x:c>
-      <x:c r="I14" s="14">
-        <x:v>45608</x:v>
-      </x:c>
-      <x:c r="J14" s="12" t="n">
-        <x:v>1216004</x:v>
-      </x:c>
-      <x:c r="K14" s="15" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L14" s="16">
-        <x:v>45973.2287268518</x:v>
-      </x:c>
-      <x:c r="M14" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="s"/>
-      <x:c r="E15" s="11" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H15" s="13">
-        <x:v>45954.4189930556</x:v>
-      </x:c>
-      <x:c r="I15" s="13">
-        <x:v>45954.4190277778</x:v>
-      </x:c>
-      <x:c r="J15" s="12" t="n">
-        <x:v>1215987</x:v>
-      </x:c>
-      <x:c r="K15" s="15" t="n">
-        <x:v>1986</x:v>
-      </x:c>
-      <x:c r="L15" s="16">
-        <x:v>45967.2850694444</x:v>
-      </x:c>
-      <x:c r="M15" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="s"/>
-      <x:c r="E16" s="11" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H16" s="13">
-        <x:v>45959.2592013889</x:v>
-      </x:c>
-      <x:c r="I16" s="13">
-        <x:v>45959.259224537</x:v>
-      </x:c>
-      <x:c r="J16" s="12" t="n">
-        <x:v>1216022</x:v>
-      </x:c>
-      <x:c r="K16" s="15" t="n">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="L16" s="16">
-        <x:v>45986.1291898148</x:v>
-      </x:c>
-      <x:c r="M16" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="22" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C18" s="31" t="s"/>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="31" t="s"/>
+      <x:c r="F18" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10490,18 +13361,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -10518,7 +13386,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:outlinePr summaryBelow="0" summaryRight="0"/>
@@ -10579,7 +13447,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45992</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -10640,209 +13508,208 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>128</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H6" s="13">
-        <x:v>45981.1374421296</x:v>
+        <x:v>46058.3038078704</x:v>
       </x:c>
       <x:c r="I6" s="14">
-        <x:v>45969</x:v>
+        <x:v>46055</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
-        <x:v>1216030</x:v>
+        <x:v>1195989</x:v>
       </x:c>
       <x:c r="K6" s="15" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L6" s="16">
-        <x:v>45996.1054282407</x:v>
+        <x:v>46066.3127777778</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="17" t="s">
-        <x:v>132</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E7" s="17" t="s">
-        <x:v>133</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="F7" s="17" t="s">
-        <x:v>134</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G7" s="17" t="s">
-        <x:v>135</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H7" s="18">
-        <x:v>45994.1029050926</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>45169</x:v>
+        <x:v>46066.3781828704</x:v>
+      </x:c>
+      <x:c r="I7" s="33">
+        <x:v>46081</x:v>
       </x:c>
       <x:c r="J7" s="17" t="n">
-        <x:v>1216035</x:v>
+        <x:v>1346991</x:v>
       </x:c>
       <x:c r="K7" s="19" t="n">
-        <x:v>12780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L7" s="18">
-        <x:v>46006.2230439815</x:v>
+        <x:v>46077.0856712963</x:v>
       </x:c>
       <x:c r="M7" s="17" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
+      <x:c r="B8" s="34" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="33" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="s">
+      <x:c r="C8" s="34" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E8" s="33" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H8" s="34">
-        <x:v>45973.2824074074</x:v>
-      </x:c>
-      <x:c r="I8" s="35">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J8" s="33" t="n">
-        <x:v>1216029</x:v>
-      </x:c>
-      <x:c r="K8" s="36" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L8" s="34">
-        <x:v>45993.0810763889</x:v>
-      </x:c>
-      <x:c r="M8" s="33" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="33" t="s">
+      <x:c r="E8" s="34" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H8" s="35">
+        <x:v>46062.2741666667</x:v>
+      </x:c>
+      <x:c r="I8" s="36">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="35">
+        <x:v>46077.1029513889</x:v>
+      </x:c>
+      <x:c r="M8" s="34" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="20" t="s"/>
+      <x:c r="C9" s="20" t="s"/>
+      <x:c r="D9" s="20" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="20" t="s"/>
+      <x:c r="H9" s="20" t="s"/>
+      <x:c r="I9" s="20" t="s"/>
+      <x:c r="J9" s="20" t="s"/>
+      <x:c r="K9" s="20" t="s"/>
+      <x:c r="L9" s="20" t="s"/>
+      <x:c r="M9" s="20" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B10" s="44" t="s"/>
+      <x:c r="C10" s="44" t="s"/>
+      <x:c r="D10" s="44" t="s"/>
+      <x:c r="E10" s="44" t="s"/>
+      <x:c r="F10" s="44" t="s"/>
+      <x:c r="G10" s="44" t="s"/>
+      <x:c r="H10" s="44" t="s"/>
+      <x:c r="I10" s="44" t="s"/>
+      <x:c r="J10" s="44" t="s"/>
+      <x:c r="K10" s="44" t="s"/>
+      <x:c r="L10" s="44" t="s"/>
+      <x:c r="M10" s="44" t="s"/>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="23" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="33" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="s">
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C17" s="31" t="s"/>
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="31" t="s"/>
+      <x:c r="F17" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E9" s="33" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H9" s="34">
-        <x:v>45988.1651388889</x:v>
-      </x:c>
-      <x:c r="I9" s="35">
-        <x:v>45974</x:v>
-      </x:c>
-      <x:c r="J9" s="33" t="n">
-        <x:v>1216036</x:v>
-      </x:c>
-      <x:c r="K9" s="36" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L9" s="34">
-        <x:v>46006.2389583333</x:v>
-      </x:c>
-      <x:c r="M9" s="33" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -11820,2659 +14687,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-  </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="0" summaryRight="0"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:AB993"/>
-  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
-  <x:cols>
-    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
-    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
-    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
-      <x:c r="N5" s="4" t="s"/>
-      <x:c r="O5" s="5" t="s"/>
-      <x:c r="P5" s="5" t="s"/>
-      <x:c r="Q5" s="5" t="s"/>
-      <x:c r="R5" s="5" t="s"/>
-      <x:c r="S5" s="5" t="s"/>
-      <x:c r="T5" s="5" t="s"/>
-      <x:c r="U5" s="5" t="s"/>
-      <x:c r="V5" s="5" t="s"/>
-      <x:c r="W5" s="5" t="s"/>
-      <x:c r="X5" s="5" t="s"/>
-      <x:c r="Y5" s="5" t="s"/>
-      <x:c r="Z5" s="5" t="s"/>
-      <x:c r="AA5" s="5" t="s"/>
-      <x:c r="AB5" s="5" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46033.3509837963</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216094</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46049.2368865741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N6" s="6" t="s"/>
-      <x:c r="O6" s="7" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46010.1939351852</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46029</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216062</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46034.111087963</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H8" s="34">
-        <x:v>45989.0397222222</x:v>
-      </x:c>
-      <x:c r="I8" s="35">
-        <x:v>45597</x:v>
-      </x:c>
-      <x:c r="J8" s="33" t="n">
-        <x:v>1216078</x:v>
-      </x:c>
-      <x:c r="K8" s="36" t="n">
-        <x:v>8280</x:v>
-      </x:c>
-      <x:c r="L8" s="34">
-        <x:v>46043.2235069444</x:v>
-      </x:c>
-      <x:c r="M8" s="33" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="33" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="s"/>
-      <x:c r="E9" s="33" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H9" s="34">
-        <x:v>46043.045474537</x:v>
-      </x:c>
-      <x:c r="I9" s="34">
-        <x:v>46043.0455092593</x:v>
-      </x:c>
-      <x:c r="J9" s="33" t="n">
-        <x:v>1216091</x:v>
-      </x:c>
-      <x:c r="K9" s="36" t="n">
-        <x:v>1986</x:v>
-      </x:c>
-      <x:c r="L9" s="34">
-        <x:v>46048.2516435185</x:v>
-      </x:c>
-      <x:c r="M9" s="33" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
-  </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
-  </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
-    <x:oddHeader/>
-    <x:oddFooter/>
-    <x:evenHeader/>
-    <x:evenFooter/>
-    <x:firstHeader/>
-    <x:firstFooter/>
-  </x:headerFooter>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="0" summaryRight="0"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:AB993"/>
-  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
-  <x:cols>
-    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
-    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
-    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
-      <x:c r="N4" s="3" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
-      <x:c r="N5" s="4" t="s"/>
-      <x:c r="O5" s="5" t="s"/>
-      <x:c r="P5" s="5" t="s"/>
-      <x:c r="Q5" s="5" t="s"/>
-      <x:c r="R5" s="5" t="s"/>
-      <x:c r="S5" s="5" t="s"/>
-      <x:c r="T5" s="5" t="s"/>
-      <x:c r="U5" s="5" t="s"/>
-      <x:c r="V5" s="5" t="s"/>
-      <x:c r="W5" s="5" t="s"/>
-      <x:c r="X5" s="5" t="s"/>
-      <x:c r="Y5" s="5" t="s"/>
-      <x:c r="Z5" s="5" t="s"/>
-      <x:c r="AA5" s="5" t="s"/>
-      <x:c r="AB5" s="5" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46058.3038078704</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1195989</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46066.3127777778</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="N6" s="6" t="s"/>
-      <x:c r="O6" s="7" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I7" s="32">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46077.0856712963</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="33" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H8" s="34">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I8" s="35">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J8" s="33" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K8" s="36" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="34">
-        <x:v>46077.1029513889</x:v>
-      </x:c>
-      <x:c r="M8" s="33" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="22" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
-  </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1626,7 +1626,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1696,7 +1696,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>24</x:v>
@@ -3545,7 +3545,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3615,7 +3615,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>8</x:v>
@@ -4832,7 +4832,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -4902,7 +4902,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>24</x:v>
@@ -6289,7 +6289,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -6359,7 +6359,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>47</x:v>
@@ -7783,7 +7783,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -7853,7 +7853,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>8</x:v>
@@ -9105,7 +9105,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -9173,7 +9173,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>24</x:v>
@@ -10765,7 +10765,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -10835,7 +10835,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -12117,7 +12117,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -12187,7 +12187,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>1</x:v>
@@ -13478,7 +13478,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -13548,7 +13548,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="17" t="s">
         <x:v>24</x:v>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,9 +30,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
   <x:si>
     <x:t>PERMIT SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -756,7 +792,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -801,22 +837,14 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -840,7 +868,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
   </x:fonts>
@@ -1075,7 +1103,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1086,10 +1114,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1101,68 +1135,50 @@
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1193,120 +1209,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1325,11 +1229,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1628,18 +1596,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1657,812 +1613,824 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46088.1798263889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46088.179837963</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216179</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46093.2393865741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46077.2833680556</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1217027</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46094.1366782407</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>163</x:v>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="B8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46088.1798263889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46088.179837963</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216179</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46093.2393865741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46077.2833680556</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1217027</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46094.1366782407</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>46076.2809953704</x:v>
       </x:c>
-      <x:c r="I8" s="35">
+      <x:c r="I10" s="29">
         <x:v>46076.2810185185</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1216194</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>46097.2411111111</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="34" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E9" s="34" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F9" s="34" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H9" s="35">
+      <x:c r="M10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>46076.245</x:v>
       </x:c>
-      <x:c r="I9" s="35">
+      <x:c r="I11" s="29">
         <x:v>46076.2450115741</x:v>
       </x:c>
-      <x:c r="J9" s="34" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1216190</x:v>
       </x:c>
-      <x:c r="K9" s="37" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="35">
+      <x:c r="L11" s="32">
         <x:v>46094.1710416667</x:v>
       </x:c>
-      <x:c r="M9" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="38" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C10" s="38" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F10" s="38" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G10" s="38" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H10" s="40">
+      <x:c r="M11" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
         <x:v>46076.2578009259</x:v>
       </x:c>
-      <x:c r="I10" s="40">
+      <x:c r="I12" s="29">
         <x:v>46076.2578240741</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J12" s="28" t="n">
         <x:v>1216197</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="32">
         <x:v>46097.2583912037</x:v>
       </x:c>
-      <x:c r="M10" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="38" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C11" s="38" t="s">
+      <x:c r="M12" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I13" s="29">
+        <x:v>46076.2633680556</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="n">
+        <x:v>1216188</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L13" s="32">
+        <x:v>46094.1562731481</x:v>
+      </x:c>
+      <x:c r="M13" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H14" s="29">
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I14" s="29">
+        <x:v>46076.3755439815</x:v>
+      </x:c>
+      <x:c r="J14" s="28" t="n">
+        <x:v>1216189</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="32">
+        <x:v>46094.1653935185</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="F15" s="27" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H15" s="29">
+        <x:v>46046.1343634259</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>45917</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="n">
+        <x:v>1216183</x:v>
+      </x:c>
+      <x:c r="K15" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L15" s="32">
+        <x:v>46093.2878703704</x:v>
+      </x:c>
+      <x:c r="M15" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F16" s="27" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H16" s="29">
+        <x:v>46046.1309027778</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>46021</x:v>
+      </x:c>
+      <x:c r="J16" s="28" t="n">
+        <x:v>1216181</x:v>
+      </x:c>
+      <x:c r="K16" s="31" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L16" s="32">
+        <x:v>46093.273287037</x:v>
+      </x:c>
+      <x:c r="M16" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D17" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="27" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="F17" s="27" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G17" s="27" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H17" s="29">
+        <x:v>46046.1237615741</x:v>
+      </x:c>
+      <x:c r="I17" s="30">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J17" s="28" t="n">
+        <x:v>1216180</x:v>
+      </x:c>
+      <x:c r="K17" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L17" s="32">
+        <x:v>46093.2636342593</x:v>
+      </x:c>
+      <x:c r="M17" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D18" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E18" s="27" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="F18" s="27" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G18" s="27" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="H18" s="29">
+        <x:v>46046.1140856482</x:v>
+      </x:c>
+      <x:c r="I18" s="30">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J18" s="28" t="n">
+        <x:v>1216182</x:v>
+      </x:c>
+      <x:c r="K18" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="32">
+        <x:v>46093.2825231481</x:v>
+      </x:c>
+      <x:c r="M18" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D19" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E19" s="27" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="F19" s="27" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G19" s="27" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="H19" s="29">
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I19" s="30">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J19" s="28" t="n">
+        <x:v>1216184</x:v>
+      </x:c>
+      <x:c r="K19" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L19" s="32">
+        <x:v>46093.2926041667</x:v>
+      </x:c>
+      <x:c r="M19" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D20" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E20" s="27" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="F20" s="27" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G20" s="27" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H20" s="29">
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I20" s="30">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J20" s="28" t="n">
+        <x:v>1216168</x:v>
+      </x:c>
+      <x:c r="K20" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L20" s="32">
+        <x:v>46092.1400231481</x:v>
+      </x:c>
+      <x:c r="M20" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="27" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D11" s="39" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E11" s="38" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F11" s="38" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G11" s="38" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H11" s="40">
-        <x:v>46076.2633564815</x:v>
-      </x:c>
-      <x:c r="I11" s="40">
-        <x:v>46076.2633680556</x:v>
-      </x:c>
-      <x:c r="J11" s="39" t="n">
-        <x:v>1216188</x:v>
-      </x:c>
-      <x:c r="K11" s="42" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L11" s="43">
-        <x:v>46094.1562731481</x:v>
-      </x:c>
-      <x:c r="M11" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="38" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C12" s="38" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E12" s="38" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F12" s="38" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G12" s="38" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H12" s="40">
-        <x:v>46076.3755324074</x:v>
-      </x:c>
-      <x:c r="I12" s="40">
-        <x:v>46076.3755439815</x:v>
-      </x:c>
-      <x:c r="J12" s="39" t="n">
-        <x:v>1216189</x:v>
-      </x:c>
-      <x:c r="K12" s="42" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="43">
-        <x:v>46094.1653935185</x:v>
-      </x:c>
-      <x:c r="M12" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="38" t="s">
+      <x:c r="D21" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E21" s="27" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F21" s="27" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G21" s="27" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H21" s="29">
+        <x:v>46079.2852546296</x:v>
+      </x:c>
+      <x:c r="I21" s="29">
+        <x:v>46079.2852662037</x:v>
+      </x:c>
+      <x:c r="J21" s="28" t="n">
+        <x:v>1216195</x:v>
+      </x:c>
+      <x:c r="K21" s="31" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L21" s="32">
+        <x:v>46097.2459143518</x:v>
+      </x:c>
+      <x:c r="M21" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="27" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D13" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E13" s="38" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F13" s="38" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G13" s="38" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H13" s="40">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I13" s="41">
-        <x:v>45917</x:v>
-      </x:c>
-      <x:c r="J13" s="39" t="n">
-        <x:v>1216183</x:v>
-      </x:c>
-      <x:c r="K13" s="42" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L13" s="43">
-        <x:v>46093.2878703704</x:v>
-      </x:c>
-      <x:c r="M13" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="38" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D14" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="38" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F14" s="38" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G14" s="38" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H14" s="40">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I14" s="41">
-        <x:v>46021</x:v>
-      </x:c>
-      <x:c r="J14" s="39" t="n">
-        <x:v>1216181</x:v>
-      </x:c>
-      <x:c r="K14" s="42" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L14" s="43">
-        <x:v>46093.273287037</x:v>
-      </x:c>
-      <x:c r="M14" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="38" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D15" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E15" s="38" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="F15" s="38" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="G15" s="38" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="H15" s="40">
-        <x:v>46046.1237615741</x:v>
-      </x:c>
-      <x:c r="I15" s="41">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J15" s="39" t="n">
-        <x:v>1216180</x:v>
-      </x:c>
-      <x:c r="K15" s="42" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L15" s="43">
-        <x:v>46093.2636342593</x:v>
-      </x:c>
-      <x:c r="M15" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="38" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D16" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E16" s="38" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="F16" s="38" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="G16" s="38" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H16" s="40">
-        <x:v>46046.1140856482</x:v>
-      </x:c>
-      <x:c r="I16" s="41">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J16" s="39" t="n">
-        <x:v>1216182</x:v>
-      </x:c>
-      <x:c r="K16" s="42" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L16" s="43">
-        <x:v>46093.2825231481</x:v>
-      </x:c>
-      <x:c r="M16" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="38" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="D17" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E17" s="38" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F17" s="38" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G17" s="38" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="H17" s="40">
-        <x:v>46048.0974768518</x:v>
-      </x:c>
-      <x:c r="I17" s="41">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J17" s="39" t="n">
-        <x:v>1216184</x:v>
-      </x:c>
-      <x:c r="K17" s="42" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L17" s="43">
-        <x:v>46093.2926041667</x:v>
-      </x:c>
-      <x:c r="M17" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="38" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D18" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E18" s="38" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F18" s="38" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G18" s="38" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H18" s="40">
-        <x:v>46076.318900463</x:v>
-      </x:c>
-      <x:c r="I18" s="41">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J18" s="39" t="n">
-        <x:v>1216168</x:v>
-      </x:c>
-      <x:c r="K18" s="42" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="43">
-        <x:v>46092.1400231481</x:v>
-      </x:c>
-      <x:c r="M18" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="38" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C19" s="38" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D19" s="39" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E19" s="38" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F19" s="38" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G19" s="38" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H19" s="40">
-        <x:v>46079.2852546296</x:v>
-      </x:c>
-      <x:c r="I19" s="40">
-        <x:v>46079.2852662037</x:v>
-      </x:c>
-      <x:c r="J19" s="39" t="n">
-        <x:v>1216195</x:v>
-      </x:c>
-      <x:c r="K19" s="42" t="n">
+      <x:c r="D22" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E22" s="27" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="F22" s="27" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G22" s="27" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H22" s="29">
+        <x:v>46079.2747222222</x:v>
+      </x:c>
+      <x:c r="I22" s="29">
+        <x:v>46079.2747453704</x:v>
+      </x:c>
+      <x:c r="J22" s="28" t="n">
+        <x:v>1216196</x:v>
+      </x:c>
+      <x:c r="K22" s="31" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L19" s="43">
-        <x:v>46097.2459143518</x:v>
-      </x:c>
-      <x:c r="M19" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="38" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C20" s="38" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D20" s="39" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E20" s="38" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F20" s="38" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G20" s="38" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H20" s="40">
-        <x:v>46079.2747222222</x:v>
-      </x:c>
-      <x:c r="I20" s="40">
-        <x:v>46079.2747453704</x:v>
-      </x:c>
-      <x:c r="J20" s="39" t="n">
-        <x:v>1216196</x:v>
-      </x:c>
-      <x:c r="K20" s="42" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L20" s="43">
+      <x:c r="L22" s="32">
         <x:v>46097.2536342593</x:v>
       </x:c>
-      <x:c r="M20" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C21" s="38" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D21" s="39" t="s"/>
-      <x:c r="E21" s="38" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="F21" s="38" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G21" s="38" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H21" s="40">
+      <x:c r="M22" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="27" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="F23" s="27" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G23" s="27" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H23" s="29">
         <x:v>46090.2854050926</x:v>
       </x:c>
-      <x:c r="I21" s="40">
+      <x:c r="I23" s="29">
         <x:v>46090.2854282407</x:v>
       </x:c>
-      <x:c r="J21" s="39" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="K21" s="42" t="n">
+      <x:c r="J23" s="28" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="K23" s="31" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L21" s="43">
+      <x:c r="L23" s="32">
         <x:v>46094.0865740741</x:v>
       </x:c>
-      <x:c r="M21" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C22" s="38" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="D22" s="39" t="s"/>
-      <x:c r="E22" s="38" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F22" s="38" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G22" s="38" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="H22" s="40">
+      <x:c r="M23" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="27" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F24" s="27" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G24" s="27" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H24" s="29">
         <x:v>46090.2540972222</x:v>
       </x:c>
-      <x:c r="I22" s="40">
+      <x:c r="I24" s="29">
         <x:v>46090.2541203704</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J24" s="28" t="n">
         <x:v>1216185</x:v>
       </x:c>
-      <x:c r="K22" s="42" t="n">
+      <x:c r="K24" s="31" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L22" s="43">
+      <x:c r="L24" s="32">
         <x:v>46094.0818981481</x:v>
       </x:c>
-      <x:c r="M22" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C23" s="38" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D23" s="39" t="s"/>
-      <x:c r="E23" s="38" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F23" s="38" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G23" s="38" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="H23" s="40">
+      <x:c r="M24" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D25" s="28" t="s"/>
+      <x:c r="E25" s="27" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="F25" s="27" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G25" s="27" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H25" s="29">
         <x:v>46090.2349189815</x:v>
       </x:c>
-      <x:c r="I23" s="40">
+      <x:c r="I25" s="29">
         <x:v>46090.2349305556</x:v>
       </x:c>
-      <x:c r="J23" s="39" t="n">
+      <x:c r="J25" s="28" t="n">
         <x:v>1216187</x:v>
       </x:c>
-      <x:c r="K23" s="42" t="n">
+      <x:c r="K25" s="31" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L23" s="43">
+      <x:c r="L25" s="32">
         <x:v>46094.0939351852</x:v>
       </x:c>
-      <x:c r="M23" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B24" s="44" t="s"/>
-      <x:c r="C24" s="44" t="s"/>
-      <x:c r="D24" s="44" t="s"/>
-      <x:c r="E24" s="44" t="s"/>
-      <x:c r="F24" s="44" t="s"/>
-      <x:c r="G24" s="44" t="s"/>
-      <x:c r="H24" s="44" t="s"/>
-      <x:c r="I24" s="44" t="s"/>
-      <x:c r="J24" s="44" t="s"/>
-      <x:c r="K24" s="44" t="s"/>
-      <x:c r="L24" s="44" t="s"/>
-      <x:c r="M24" s="44" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B25" s="44" t="s"/>
-      <x:c r="C25" s="44" t="s"/>
-      <x:c r="D25" s="44" t="s"/>
-      <x:c r="E25" s="44" t="s"/>
-      <x:c r="F25" s="44" t="s"/>
-      <x:c r="G25" s="44" t="s"/>
-      <x:c r="H25" s="44" t="s"/>
-      <x:c r="I25" s="44" t="s"/>
-      <x:c r="J25" s="44" t="s"/>
-      <x:c r="K25" s="44" t="s"/>
-      <x:c r="L25" s="44" t="s"/>
-      <x:c r="M25" s="44" t="s"/>
+      <x:c r="M25" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="21" t="s">
+      <x:c r="B28" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="s"/>
+      <x:c r="D28" s="16" t="s"/>
+      <x:c r="E28" s="17" t="s"/>
+      <x:c r="F28" s="17" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C29" s="19" t="s"/>
+      <x:c r="D29" s="19" t="s"/>
+      <x:c r="E29" s="19" t="s"/>
+      <x:c r="F29" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="21" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C30" s="22" t="s"/>
+      <x:c r="D30" s="22" t="s"/>
+      <x:c r="E30" s="22" t="s"/>
+      <x:c r="F30" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C31" s="22" t="s"/>
+      <x:c r="D31" s="22" t="s"/>
+      <x:c r="E31" s="22" t="s"/>
+      <x:c r="F31" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="21" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C32" s="22" t="s"/>
+      <x:c r="D32" s="22" t="s"/>
+      <x:c r="E32" s="22" t="s"/>
+      <x:c r="F32" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C28" s="22" t="s"/>
-      <x:c r="D28" s="22" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="23" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="27" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="27" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C32" s="28" t="s"/>
-      <x:c r="D32" s="28" t="s"/>
-      <x:c r="E32" s="28" t="s"/>
-      <x:c r="F32" s="29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="27" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C33" s="28" t="s"/>
-      <x:c r="D33" s="28" t="s"/>
-      <x:c r="E33" s="28" t="s"/>
-      <x:c r="F33" s="29" t="n">
+      <x:c r="C33" s="22" t="s"/>
+      <x:c r="D33" s="22" t="s"/>
+      <x:c r="E33" s="22" t="s"/>
+      <x:c r="F33" s="23" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="27" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C34" s="28" t="s"/>
-      <x:c r="D34" s="28" t="s"/>
-      <x:c r="E34" s="28" t="s"/>
-      <x:c r="F34" s="29" t="n">
+      <x:c r="B34" s="21" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C34" s="22" t="s"/>
+      <x:c r="D34" s="22" t="s"/>
+      <x:c r="E34" s="22" t="s"/>
+      <x:c r="F34" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C35" s="28" t="s"/>
-      <x:c r="D35" s="28" t="s"/>
-      <x:c r="E35" s="28" t="s"/>
-      <x:c r="F35" s="29" t="n">
+      <x:c r="B35" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C35" s="22" t="s"/>
+      <x:c r="D35" s="22" t="s"/>
+      <x:c r="E35" s="22" t="s"/>
+      <x:c r="F35" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C36" s="31" t="s"/>
-      <x:c r="D36" s="31" t="s"/>
-      <x:c r="E36" s="31" t="s"/>
-      <x:c r="F36" s="32" t="n">
+      <x:c r="B36" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C36" s="25" t="s"/>
+      <x:c r="D36" s="25" t="s"/>
+      <x:c r="E36" s="25" t="s"/>
+      <x:c r="F36" s="26" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -3547,18 +3515,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3576,164 +3532,176 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45860.0993981482</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346409</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45860.1449537037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s"/>
-      <x:c r="E7" s="17" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="s">
+      <x:c r="M7" s="10" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H7" s="18">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45860.0993981482</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346409</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45860.1449537037</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
         <x:v>45861.1130439815</x:v>
       </x:c>
-      <x:c r="I7" s="18">
+      <x:c r="I9" s="12">
         <x:v>45861.1130555556</x:v>
       </x:c>
-      <x:c r="J7" s="17" t="n">
+      <x:c r="J9" s="11" t="n">
         <x:v>1346412</x:v>
       </x:c>
-      <x:c r="K7" s="19" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="L7" s="18">
+      <x:c r="L9" s="12">
         <x:v>45862.3035648148</x:v>
       </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
-      <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s"/>
-      <x:c r="C8" s="20" t="s"/>
-      <x:c r="D8" s="20" t="s"/>
-      <x:c r="E8" s="20" t="s"/>
-      <x:c r="F8" s="20" t="s"/>
-      <x:c r="G8" s="20" t="s"/>
-      <x:c r="H8" s="20" t="s"/>
-      <x:c r="I8" s="20" t="s"/>
-      <x:c r="J8" s="20" t="s"/>
-      <x:c r="K8" s="20" t="s"/>
-      <x:c r="L8" s="20" t="s"/>
-      <x:c r="M8" s="20" t="s"/>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -4834,18 +4802,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4863,338 +4819,350 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45866.2802893519</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45866.2803009259</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215849</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45873.1184143519</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45875.2238888889</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1215853</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45876.2432986111</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>23</x:v>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F8" s="34" t="s">
+      <x:c r="D8" s="11" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G8" s="34" t="s">
+      <x:c r="E8" s="11" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="F8" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45866.2802893519</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45866.2803009259</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215849</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45873.1184143519</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45875.2238888889</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215853</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45876.2432986111</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45880.1214814815</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="30">
         <x:v>45882</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1346457</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>45881.1618981482</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="34" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="s"/>
-      <x:c r="E9" s="34" t="s">
+      <x:c r="M10" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s"/>
+      <x:c r="E11" s="27" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
+        <x:v>45873.2195486111</x:v>
+      </x:c>
+      <x:c r="I11" s="29">
+        <x:v>45873.2195601852</x:v>
+      </x:c>
+      <x:c r="J11" s="28" t="n">
+        <x:v>1195700</x:v>
+      </x:c>
+      <x:c r="K11" s="31" t="n">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="L11" s="32">
+        <x:v>45882.1150694444</x:v>
+      </x:c>
+      <x:c r="M11" s="27" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
+        <x:v>45875.361724537</x:v>
+      </x:c>
+      <x:c r="I12" s="30">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J12" s="28" t="n">
+        <x:v>1215851</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="32">
+        <x:v>45876.2230902778</x:v>
+      </x:c>
+      <x:c r="M12" s="27" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F9" s="34" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H9" s="35">
-        <x:v>45873.2195486111</x:v>
-      </x:c>
-      <x:c r="I9" s="35">
-        <x:v>45873.2195601852</x:v>
-      </x:c>
-      <x:c r="J9" s="34" t="n">
-        <x:v>1195700</x:v>
-      </x:c>
-      <x:c r="K9" s="37" t="n">
-        <x:v>2790</x:v>
-      </x:c>
-      <x:c r="L9" s="35">
-        <x:v>45882.1150694444</x:v>
-      </x:c>
-      <x:c r="M9" s="34" t="s">
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
         <x:v>38</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="38" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="38" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G10" s="38" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H10" s="40">
-        <x:v>45875.361724537</x:v>
-      </x:c>
-      <x:c r="I10" s="41">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J10" s="39" t="n">
-        <x:v>1215851</x:v>
-      </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="F13" s="27" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
+        <x:v>45875.2324652778</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="n">
+        <x:v>1215852</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="43">
-        <x:v>45876.2230902778</x:v>
-      </x:c>
-      <x:c r="M10" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="38" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D11" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="38" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F11" s="38" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G11" s="38" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H11" s="40">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I11" s="41">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J11" s="39" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K11" s="42" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="43">
+      <x:c r="L13" s="32">
         <x:v>45876.2319791667</x:v>
       </x:c>
-      <x:c r="M11" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="44" t="s"/>
-      <x:c r="C12" s="44" t="s"/>
-      <x:c r="D12" s="44" t="s"/>
-      <x:c r="E12" s="44" t="s"/>
-      <x:c r="F12" s="44" t="s"/>
-      <x:c r="G12" s="44" t="s"/>
-      <x:c r="H12" s="44" t="s"/>
-      <x:c r="I12" s="44" t="s"/>
-      <x:c r="J12" s="44" t="s"/>
-      <x:c r="K12" s="44" t="s"/>
-      <x:c r="L12" s="44" t="s"/>
-      <x:c r="M12" s="44" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="44" t="s"/>
-      <x:c r="C13" s="44" t="s"/>
-      <x:c r="D13" s="44" t="s"/>
-      <x:c r="E13" s="44" t="s"/>
-      <x:c r="F13" s="44" t="s"/>
-      <x:c r="G13" s="44" t="s"/>
-      <x:c r="H13" s="44" t="s"/>
-      <x:c r="I13" s="44" t="s"/>
-      <x:c r="J13" s="44" t="s"/>
-      <x:c r="K13" s="44" t="s"/>
-      <x:c r="L13" s="44" t="s"/>
-      <x:c r="M13" s="44" t="s"/>
+      <x:c r="M13" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s"/>
+      <x:c r="D16" s="16" t="s"/>
+      <x:c r="E16" s="17" t="s"/>
+      <x:c r="F16" s="17" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="s"/>
+      <x:c r="D17" s="19" t="s"/>
+      <x:c r="E17" s="19" t="s"/>
+      <x:c r="F17" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="21" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="21" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="23" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="27" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C22" s="31" t="s"/>
-      <x:c r="D22" s="31" t="s"/>
-      <x:c r="E22" s="31" t="s"/>
-      <x:c r="F22" s="32" t="n">
+      <x:c r="B22" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -6291,18 +6259,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6320,376 +6276,388 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45915.355787037</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215901</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45918.2339583333</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45903.3849652778</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45916</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1215886</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>3150</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45908.2848958333</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>23</x:v>
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G8" s="34" t="s">
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="F8" s="11" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45915.355787037</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215901</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45918.2339583333</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45903.3849652778</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45916</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215886</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>3150</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45908.2848958333</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45919.4023032407</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="30">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1215905</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>45925.945150463</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="34" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F9" s="34" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H9" s="35">
+      <x:c r="M10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>45918.1053935185</x:v>
       </x:c>
-      <x:c r="I9" s="36">
+      <x:c r="I11" s="30">
         <x:v>45900</x:v>
       </x:c>
-      <x:c r="J9" s="34" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1215910</x:v>
       </x:c>
-      <x:c r="K9" s="37" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L9" s="35">
+      <x:c r="L11" s="32">
         <x:v>45929.2194097222</x:v>
       </x:c>
-      <x:c r="M9" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="38" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F10" s="38" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G10" s="38" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H10" s="40">
+      <x:c r="M11" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
         <x:v>45908.2183449074</x:v>
       </x:c>
-      <x:c r="I10" s="41">
+      <x:c r="I12" s="30">
         <x:v>45918</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J12" s="28" t="n">
         <x:v>1215894</x:v>
       </x:c>
-      <x:c r="K10" s="42" t="n">
+      <x:c r="K12" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="43">
+      <x:c r="L12" s="32">
         <x:v>45912.1906134259</x:v>
       </x:c>
-      <x:c r="M10" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="38" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D11" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="38" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F11" s="38" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G11" s="38" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H11" s="40">
+      <x:c r="M12" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
         <x:v>45922.1415393519</x:v>
       </x:c>
-      <x:c r="I11" s="41">
+      <x:c r="I13" s="30">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J11" s="39" t="n">
+      <x:c r="J13" s="28" t="n">
         <x:v>1346550</x:v>
       </x:c>
-      <x:c r="K11" s="42" t="n">
+      <x:c r="K13" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="43">
+      <x:c r="L13" s="32">
         <x:v>45922.1832523148</x:v>
       </x:c>
-      <x:c r="M11" s="38" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="38" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="s"/>
-      <x:c r="E12" s="38" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F12" s="38" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G12" s="38" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H12" s="40">
+      <x:c r="M13" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="27" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H14" s="29">
         <x:v>45919.473287037</x:v>
       </x:c>
-      <x:c r="I12" s="40">
+      <x:c r="I14" s="29">
         <x:v>45919.4732986111</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J14" s="28" t="n">
         <x:v>1215906</x:v>
       </x:c>
-      <x:c r="K12" s="42" t="n">
+      <x:c r="K14" s="31" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L12" s="43">
+      <x:c r="L14" s="32">
         <x:v>45926.2586111111</x:v>
       </x:c>
-      <x:c r="M12" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="44" t="s"/>
-      <x:c r="C13" s="44" t="s"/>
-      <x:c r="D13" s="44" t="s"/>
-      <x:c r="E13" s="44" t="s"/>
-      <x:c r="F13" s="44" t="s"/>
-      <x:c r="G13" s="44" t="s"/>
-      <x:c r="H13" s="44" t="s"/>
-      <x:c r="I13" s="44" t="s"/>
-      <x:c r="J13" s="44" t="s"/>
-      <x:c r="K13" s="44" t="s"/>
-      <x:c r="L13" s="44" t="s"/>
-      <x:c r="M13" s="44" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B14" s="44" t="s"/>
-      <x:c r="C14" s="44" t="s"/>
-      <x:c r="D14" s="44" t="s"/>
-      <x:c r="E14" s="44" t="s"/>
-      <x:c r="F14" s="44" t="s"/>
-      <x:c r="G14" s="44" t="s"/>
-      <x:c r="H14" s="44" t="s"/>
-      <x:c r="I14" s="44" t="s"/>
-      <x:c r="J14" s="44" t="s"/>
-      <x:c r="K14" s="44" t="s"/>
-      <x:c r="L14" s="44" t="s"/>
-      <x:c r="M14" s="44" t="s"/>
+      <x:c r="M14" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+      <x:c r="B17" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s"/>
+      <x:c r="D17" s="16" t="s"/>
+      <x:c r="E17" s="17" t="s"/>
+      <x:c r="F17" s="17" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="19" t="s"/>
+      <x:c r="D18" s="19" t="s"/>
+      <x:c r="E18" s="19" t="s"/>
+      <x:c r="F18" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C19" s="22" t="s"/>
+      <x:c r="D19" s="22" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="21" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="23" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s"/>
-      <x:c r="D19" s="28" t="s"/>
-      <x:c r="E19" s="28" t="s"/>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="22" t="s"/>
+      <x:c r="F22" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="27" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="27" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="29" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s"/>
-      <x:c r="D22" s="28" t="s"/>
-      <x:c r="E22" s="28" t="s"/>
-      <x:c r="F22" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C23" s="31" t="s"/>
-      <x:c r="D23" s="31" t="s"/>
-      <x:c r="E23" s="31" t="s"/>
-      <x:c r="F23" s="32" t="n">
+      <x:c r="B23" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7785,18 +7753,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -7814,200 +7770,212 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45933.0884375</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45932</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215922</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45936.014837963</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s"/>
-      <x:c r="E7" s="17" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45928.9304513889</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>45928.9304861111</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1215924</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45938.0359375</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>23</x:v>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s"/>
-      <x:c r="E8" s="34" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45933.0884375</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45932</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215922</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45936.014837963</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45928.9304513889</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45928.9304861111</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215924</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45938.0359375</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s"/>
+      <x:c r="E10" s="27" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45926.4563888889</x:v>
       </x:c>
-      <x:c r="I8" s="35">
+      <x:c r="I10" s="29">
         <x:v>45926.4564351852</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1215917</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>45932.239537037</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="44" t="s"/>
-      <x:c r="C10" s="44" t="s"/>
-      <x:c r="D10" s="44" t="s"/>
-      <x:c r="E10" s="44" t="s"/>
-      <x:c r="F10" s="44" t="s"/>
-      <x:c r="G10" s="44" t="s"/>
-      <x:c r="H10" s="44" t="s"/>
-      <x:c r="I10" s="44" t="s"/>
-      <x:c r="J10" s="44" t="s"/>
-      <x:c r="K10" s="44" t="s"/>
-      <x:c r="L10" s="44" t="s"/>
-      <x:c r="M10" s="44" t="s"/>
+      <x:c r="M10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s"/>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="17" t="s"/>
+      <x:c r="F13" s="17" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="23" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="B16" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -9107,18 +9075,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9136,546 +9092,558 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45951.103287037</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1346752</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45971.0888194444</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45979</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1346786</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>45985.3594791667</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45951.1032638889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45951.103287037</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1346752</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45971.0888194444</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45980.2160416667</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45979</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346786</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45985.3594791667</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
+        <x:v>45965.2736689815</x:v>
+      </x:c>
+      <x:c r="I10" s="29">
+        <x:v>45965.2736921296</x:v>
+      </x:c>
+      <x:c r="J10" s="28" t="n">
+        <x:v>1216000</x:v>
+      </x:c>
+      <x:c r="K10" s="31" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="32">
+        <x:v>45972.1539583333</x:v>
+      </x:c>
+      <x:c r="M10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
+        <x:v>45965.2661458333</x:v>
+      </x:c>
+      <x:c r="I11" s="30">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J11" s="28" t="n">
+        <x:v>1215999</x:v>
+      </x:c>
+      <x:c r="K11" s="31" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="32">
+        <x:v>45972.1364236111</x:v>
+      </x:c>
+      <x:c r="M11" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="F12" s="27" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G12" s="27" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H12" s="29">
+        <x:v>45953.5328240741</x:v>
+      </x:c>
+      <x:c r="I12" s="30">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J12" s="28" t="n">
+        <x:v>1215970</x:v>
+      </x:c>
+      <x:c r="K12" s="31" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="32">
+        <x:v>45966.0458101852</x:v>
+      </x:c>
+      <x:c r="M12" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F13" s="27" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H13" s="29">
+        <x:v>45959.0699074074</x:v>
+      </x:c>
+      <x:c r="I13" s="30">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="n">
+        <x:v>1346761</x:v>
+      </x:c>
+      <x:c r="K13" s="31" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="32">
+        <x:v>45972.2719560185</x:v>
+      </x:c>
+      <x:c r="M13" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H14" s="29">
+        <x:v>45958.0724421296</x:v>
+      </x:c>
+      <x:c r="I14" s="30">
+        <x:v>45810</x:v>
+      </x:c>
+      <x:c r="J14" s="28" t="n">
+        <x:v>1216003</x:v>
+      </x:c>
+      <x:c r="K14" s="31" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L14" s="32">
+        <x:v>45973.0584490741</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="27" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D15" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="F15" s="27" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G15" s="27" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H15" s="29">
+        <x:v>45973.1309375</x:v>
+      </x:c>
+      <x:c r="I15" s="30">
+        <x:v>45950</x:v>
+      </x:c>
+      <x:c r="J15" s="28" t="n">
+        <x:v>1216020</x:v>
+      </x:c>
+      <x:c r="K15" s="31" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L15" s="32">
+        <x:v>45985.2116666667</x:v>
+      </x:c>
+      <x:c r="M15" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="27" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F16" s="27" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H16" s="29">
+        <x:v>45971.2436226852</x:v>
+      </x:c>
+      <x:c r="I16" s="30">
+        <x:v>45608</x:v>
+      </x:c>
+      <x:c r="J16" s="28" t="n">
+        <x:v>1216004</x:v>
+      </x:c>
+      <x:c r="K16" s="31" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L16" s="32">
+        <x:v>45973.2287268518</x:v>
+      </x:c>
+      <x:c r="M16" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C8" s="34" t="s">
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="27" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H8" s="35">
-        <x:v>45965.2736689815</x:v>
-      </x:c>
-      <x:c r="I8" s="35">
-        <x:v>45965.2736921296</x:v>
-      </x:c>
-      <x:c r="J8" s="34" t="n">
-        <x:v>1216000</x:v>
-      </x:c>
-      <x:c r="K8" s="37" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L8" s="35">
-        <x:v>45972.1539583333</x:v>
-      </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="34" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F9" s="34" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H9" s="35">
-        <x:v>45965.2661458333</x:v>
-      </x:c>
-      <x:c r="I9" s="36">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J9" s="34" t="n">
-        <x:v>1215999</x:v>
-      </x:c>
-      <x:c r="K9" s="37" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="35">
-        <x:v>45972.1364236111</x:v>
-      </x:c>
-      <x:c r="M9" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="38" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="F10" s="38" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G10" s="38" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="H10" s="40">
-        <x:v>45953.5328240741</x:v>
-      </x:c>
-      <x:c r="I10" s="41">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J10" s="39" t="n">
-        <x:v>1215970</x:v>
-      </x:c>
-      <x:c r="K10" s="42" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="43">
-        <x:v>45966.0458101852</x:v>
-      </x:c>
-      <x:c r="M10" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="38" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="38" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F11" s="38" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G11" s="38" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H11" s="40">
-        <x:v>45959.0699074074</x:v>
-      </x:c>
-      <x:c r="I11" s="41">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J11" s="39" t="n">
-        <x:v>1346761</x:v>
-      </x:c>
-      <x:c r="K11" s="42" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="43">
-        <x:v>45972.2719560185</x:v>
-      </x:c>
-      <x:c r="M11" s="38" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="38" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="38" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E12" s="38" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F12" s="38" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G12" s="38" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H12" s="40">
-        <x:v>45958.0724421296</x:v>
-      </x:c>
-      <x:c r="I12" s="41">
-        <x:v>45810</x:v>
-      </x:c>
-      <x:c r="J12" s="39" t="n">
-        <x:v>1216003</x:v>
-      </x:c>
-      <x:c r="K12" s="42" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L12" s="43">
-        <x:v>45973.0584490741</x:v>
-      </x:c>
-      <x:c r="M12" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="38" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C13" s="38" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D13" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E13" s="38" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F13" s="38" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G13" s="38" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H13" s="40">
-        <x:v>45973.1309375</x:v>
-      </x:c>
-      <x:c r="I13" s="41">
-        <x:v>45950</x:v>
-      </x:c>
-      <x:c r="J13" s="39" t="n">
-        <x:v>1216020</x:v>
-      </x:c>
-      <x:c r="K13" s="42" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L13" s="43">
-        <x:v>45985.2116666667</x:v>
-      </x:c>
-      <x:c r="M13" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="38" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C14" s="38" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D14" s="39" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="38" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F14" s="38" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G14" s="38" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="H14" s="40">
-        <x:v>45971.2436226852</x:v>
-      </x:c>
-      <x:c r="I14" s="41">
-        <x:v>45608</x:v>
-      </x:c>
-      <x:c r="J14" s="39" t="n">
-        <x:v>1216004</x:v>
-      </x:c>
-      <x:c r="K14" s="42" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L14" s="43">
-        <x:v>45973.2287268518</x:v>
-      </x:c>
-      <x:c r="M14" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="38" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D15" s="39" t="s"/>
-      <x:c r="E15" s="38" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F15" s="38" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G15" s="38" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H15" s="40">
+      <x:c r="F17" s="27" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G17" s="27" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H17" s="29">
         <x:v>45954.4189930556</x:v>
       </x:c>
-      <x:c r="I15" s="40">
+      <x:c r="I17" s="29">
         <x:v>45954.4190277778</x:v>
       </x:c>
-      <x:c r="J15" s="39" t="n">
+      <x:c r="J17" s="28" t="n">
         <x:v>1215987</x:v>
       </x:c>
-      <x:c r="K15" s="42" t="n">
+      <x:c r="K17" s="31" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L15" s="43">
+      <x:c r="L17" s="32">
         <x:v>45967.2850694444</x:v>
       </x:c>
-      <x:c r="M15" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="38" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="38" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D16" s="39" t="s"/>
-      <x:c r="E16" s="38" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F16" s="38" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G16" s="38" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H16" s="40">
+      <x:c r="M17" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="27" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F18" s="27" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G18" s="27" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H18" s="29">
         <x:v>45959.2592013889</x:v>
       </x:c>
-      <x:c r="I16" s="40">
+      <x:c r="I18" s="29">
         <x:v>45959.259224537</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J18" s="28" t="n">
         <x:v>1216022</x:v>
       </x:c>
-      <x:c r="K16" s="42" t="n">
+      <x:c r="K18" s="31" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L16" s="43">
+      <x:c r="L18" s="32">
         <x:v>45986.1291898148</x:v>
       </x:c>
-      <x:c r="M16" s="38" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B17" s="44" t="s"/>
-      <x:c r="C17" s="44" t="s"/>
-      <x:c r="D17" s="44" t="s"/>
-      <x:c r="E17" s="44" t="s"/>
-      <x:c r="F17" s="44" t="s"/>
-      <x:c r="G17" s="44" t="s"/>
-      <x:c r="H17" s="44" t="s"/>
-      <x:c r="I17" s="44" t="s"/>
-      <x:c r="J17" s="44" t="s"/>
-      <x:c r="K17" s="44" t="s"/>
-      <x:c r="L17" s="44" t="s"/>
-      <x:c r="M17" s="44" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B18" s="44" t="s"/>
-      <x:c r="C18" s="44" t="s"/>
-      <x:c r="D18" s="44" t="s"/>
-      <x:c r="E18" s="44" t="s"/>
-      <x:c r="F18" s="44" t="s"/>
-      <x:c r="G18" s="44" t="s"/>
-      <x:c r="H18" s="44" t="s"/>
-      <x:c r="I18" s="44" t="s"/>
-      <x:c r="J18" s="44" t="s"/>
-      <x:c r="K18" s="44" t="s"/>
-      <x:c r="L18" s="44" t="s"/>
-      <x:c r="M18" s="44" t="s"/>
+      <x:c r="M18" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+      <x:c r="B21" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s"/>
+      <x:c r="D21" s="16" t="s"/>
+      <x:c r="E21" s="17" t="s"/>
+      <x:c r="F21" s="17" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C22" s="19" t="s"/>
+      <x:c r="D22" s="19" t="s"/>
+      <x:c r="E22" s="19" t="s"/>
+      <x:c r="F22" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="21" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="s"/>
+      <x:c r="D23" s="22" t="s"/>
+      <x:c r="E23" s="22" t="s"/>
+      <x:c r="F23" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="s"/>
+      <x:c r="D24" s="22" t="s"/>
+      <x:c r="E24" s="22" t="s"/>
+      <x:c r="F24" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="21" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="23" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="27" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C23" s="28" t="s"/>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="28" t="s"/>
-      <x:c r="F23" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="27" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C25" s="28" t="s"/>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="28" t="s"/>
-      <x:c r="F25" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="27" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C26" s="28" t="s"/>
-      <x:c r="D26" s="28" t="s"/>
-      <x:c r="E26" s="28" t="s"/>
-      <x:c r="F26" s="29" t="n">
+      <x:c r="C26" s="22" t="s"/>
+      <x:c r="D26" s="22" t="s"/>
+      <x:c r="E26" s="22" t="s"/>
+      <x:c r="F26" s="23" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="27" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="B27" s="21" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C27" s="22" t="s"/>
+      <x:c r="D27" s="22" t="s"/>
+      <x:c r="E27" s="22" t="s"/>
+      <x:c r="F27" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
+      <x:c r="B28" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C28" s="22" t="s"/>
+      <x:c r="D28" s="22" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C29" s="31" t="s"/>
-      <x:c r="D29" s="31" t="s"/>
-      <x:c r="E29" s="31" t="s"/>
-      <x:c r="F29" s="32" t="n">
+      <x:c r="B29" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -10767,18 +10735,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -10796,231 +10752,243 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45981.1374421296</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216030</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>45996.1054282407</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>45994.1029050926</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>45169</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216035</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>12780</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46006.2230439815</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>23</x:v>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45981.1374421296</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216030</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45996.1054282407</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45994.1029050926</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>45169</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216035</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>12780</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46006.2230439815</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45973.2824074074</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="30">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1216029</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>45993.0810763889</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E9" s="34" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F9" s="34" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H9" s="35">
+      <x:c r="M10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>45988.1651388889</x:v>
       </x:c>
-      <x:c r="I9" s="36">
+      <x:c r="I11" s="30">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J9" s="34" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1216036</x:v>
       </x:c>
-      <x:c r="K9" s="37" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L9" s="35">
+      <x:c r="L11" s="32">
         <x:v>46006.2389583333</x:v>
       </x:c>
-      <x:c r="M9" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="44" t="s"/>
-      <x:c r="C10" s="44" t="s"/>
-      <x:c r="D10" s="44" t="s"/>
-      <x:c r="E10" s="44" t="s"/>
-      <x:c r="F10" s="44" t="s"/>
-      <x:c r="G10" s="44" t="s"/>
-      <x:c r="H10" s="44" t="s"/>
-      <x:c r="I10" s="44" t="s"/>
-      <x:c r="J10" s="44" t="s"/>
-      <x:c r="K10" s="44" t="s"/>
-      <x:c r="L10" s="44" t="s"/>
-      <x:c r="M10" s="44" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="44" t="s"/>
-      <x:c r="C11" s="44" t="s"/>
-      <x:c r="D11" s="44" t="s"/>
-      <x:c r="E11" s="44" t="s"/>
-      <x:c r="F11" s="44" t="s"/>
-      <x:c r="G11" s="44" t="s"/>
-      <x:c r="H11" s="44" t="s"/>
-      <x:c r="I11" s="44" t="s"/>
-      <x:c r="J11" s="44" t="s"/>
-      <x:c r="K11" s="44" t="s"/>
-      <x:c r="L11" s="44" t="s"/>
-      <x:c r="M11" s="44" t="s"/>
+      <x:c r="M11" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s"/>
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="17" t="s"/>
+      <x:c r="F14" s="17" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12119,18 +12087,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -12148,240 +12104,252 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46033.3509837963</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216094</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46049.2368865741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="17" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46010.1939351852</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>46029</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1216062</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46034.111087963</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
-        <x:v>150</x:v>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46033.3509837963</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216094</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46049.2368865741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46010.1939351852</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46029</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216062</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46034.111087963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>45989.0397222222</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="30">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1216078</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>46043.2235069444</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="34" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="s"/>
-      <x:c r="E9" s="34" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F9" s="34" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H9" s="35">
+      <x:c r="M10" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="27" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="s"/>
+      <x:c r="E11" s="27" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="F11" s="27" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G11" s="27" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="H11" s="29">
         <x:v>46043.045474537</x:v>
       </x:c>
-      <x:c r="I9" s="35">
+      <x:c r="I11" s="29">
         <x:v>46043.0455092593</x:v>
       </x:c>
-      <x:c r="J9" s="34" t="n">
+      <x:c r="J11" s="28" t="n">
         <x:v>1216091</x:v>
       </x:c>
-      <x:c r="K9" s="37" t="n">
+      <x:c r="K11" s="31" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L9" s="35">
+      <x:c r="L11" s="32">
         <x:v>46048.2516435185</x:v>
       </x:c>
-      <x:c r="M9" s="34" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="44" t="s"/>
-      <x:c r="C10" s="44" t="s"/>
-      <x:c r="D10" s="44" t="s"/>
-      <x:c r="E10" s="44" t="s"/>
-      <x:c r="F10" s="44" t="s"/>
-      <x:c r="G10" s="44" t="s"/>
-      <x:c r="H10" s="44" t="s"/>
-      <x:c r="I10" s="44" t="s"/>
-      <x:c r="J10" s="44" t="s"/>
-      <x:c r="K10" s="44" t="s"/>
-      <x:c r="L10" s="44" t="s"/>
-      <x:c r="M10" s="44" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B11" s="44" t="s"/>
-      <x:c r="C11" s="44" t="s"/>
-      <x:c r="D11" s="44" t="s"/>
-      <x:c r="E11" s="44" t="s"/>
-      <x:c r="F11" s="44" t="s"/>
-      <x:c r="G11" s="44" t="s"/>
-      <x:c r="H11" s="44" t="s"/>
-      <x:c r="I11" s="44" t="s"/>
-      <x:c r="J11" s="44" t="s"/>
-      <x:c r="K11" s="44" t="s"/>
-      <x:c r="L11" s="44" t="s"/>
-      <x:c r="M11" s="44" t="s"/>
+      <x:c r="M11" s="27" t="s">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s"/>
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="17" t="s"/>
+      <x:c r="F14" s="17" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="s"/>
+      <x:c r="D15" s="19" t="s"/>
+      <x:c r="E15" s="19" t="s"/>
+      <x:c r="F15" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="23" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="31" t="s"/>
-      <x:c r="F18" s="32" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13480,18 +13448,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -13509,204 +13465,216 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46058.3038078704</x:v>
-      </x:c>
-      <x:c r="I6" s="14">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1195989</x:v>
-      </x:c>
-      <x:c r="K6" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L6" s="16">
-        <x:v>46066.3127777778</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>163</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="s">
+      <x:c r="D7" s="10" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="17" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F7" s="17" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G7" s="17" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H7" s="18">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I7" s="33">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J7" s="17" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="18">
-        <x:v>46077.0856712963</x:v>
-      </x:c>
-      <x:c r="M7" s="17" t="s">
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="34" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H8" s="35">
+      <x:c r="B8" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46058.3038078704</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1195989</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46066.3127777778</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46066.3781828704</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K9" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46077.0856712963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="27" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H10" s="29">
         <x:v>46062.2741666667</x:v>
       </x:c>
-      <x:c r="I8" s="36">
+      <x:c r="I10" s="30">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J8" s="34" t="n">
+      <x:c r="J10" s="28" t="n">
         <x:v>1346991</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="n">
+      <x:c r="K10" s="31" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="35">
+      <x:c r="L10" s="32">
         <x:v>46077.1029513889</x:v>
       </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B10" s="44" t="s"/>
-      <x:c r="C10" s="44" t="s"/>
-      <x:c r="D10" s="44" t="s"/>
-      <x:c r="E10" s="44" t="s"/>
-      <x:c r="F10" s="44" t="s"/>
-      <x:c r="G10" s="44" t="s"/>
-      <x:c r="H10" s="44" t="s"/>
-      <x:c r="I10" s="44" t="s"/>
-      <x:c r="J10" s="44" t="s"/>
-      <x:c r="K10" s="44" t="s"/>
-      <x:c r="L10" s="44" t="s"/>
-      <x:c r="M10" s="44" t="s"/>
+      <x:c r="M10" s="27" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+      <x:c r="B13" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s"/>
+      <x:c r="D13" s="16" t="s"/>
+      <x:c r="E13" s="17" t="s"/>
+      <x:c r="F13" s="17" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="18" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="20" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="21" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="23" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="C16" s="22" t="s"/>
+      <x:c r="D16" s="22" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="30" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C17" s="31" t="s"/>
-      <x:c r="D17" s="31" t="s"/>
-      <x:c r="E17" s="31" t="s"/>
-      <x:c r="F17" s="32" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1103,9 +1103,12 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1178,7 +1181,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1208,6 +1211,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1546,7 +1553,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1618,819 +1627,819 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46088.1798263889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46088.179837963</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216179</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46093.2393865741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46077.2833680556</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1217027</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46094.1366782407</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>46076.2809953704</x:v>
       </x:c>
-      <x:c r="I10" s="29">
+      <x:c r="I10" s="30">
         <x:v>46076.2810185185</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1216194</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46097.2411111111</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>46076.245</x:v>
       </x:c>
-      <x:c r="I11" s="29">
+      <x:c r="I11" s="30">
         <x:v>46076.2450115741</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1216190</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46094.1710416667</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>46076.2578009259</x:v>
       </x:c>
-      <x:c r="I12" s="29">
+      <x:c r="I12" s="30">
         <x:v>46076.2578240741</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1216197</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>46097.2583912037</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>46076.2633564815</x:v>
       </x:c>
-      <x:c r="I13" s="29">
+      <x:c r="I13" s="30">
         <x:v>46076.2633680556</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1216188</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>46094.1562731481</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s">
+      <x:c r="C14" s="28" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="s">
+      <x:c r="D14" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E14" s="27" t="s">
+      <x:c r="E14" s="28" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F14" s="27" t="s">
+      <x:c r="F14" s="28" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G14" s="27" t="s">
+      <x:c r="G14" s="28" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="H14" s="29">
+      <x:c r="H14" s="30">
         <x:v>46076.3755324074</x:v>
       </x:c>
-      <x:c r="I14" s="29">
+      <x:c r="I14" s="30">
         <x:v>46076.3755439815</x:v>
       </x:c>
-      <x:c r="J14" s="28" t="n">
+      <x:c r="J14" s="29" t="n">
         <x:v>1216189</x:v>
       </x:c>
-      <x:c r="K14" s="31" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="32">
+      <x:c r="L14" s="33">
         <x:v>46094.1653935185</x:v>
       </x:c>
-      <x:c r="M14" s="27" t="s">
+      <x:c r="M14" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s">
+      <x:c r="C15" s="28" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="s">
+      <x:c r="D15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="27" t="s">
+      <x:c r="E15" s="28" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="F15" s="27" t="s">
+      <x:c r="F15" s="28" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G15" s="27" t="s">
+      <x:c r="G15" s="28" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="H15" s="29">
+      <x:c r="H15" s="30">
         <x:v>46046.1343634259</x:v>
       </x:c>
-      <x:c r="I15" s="30">
+      <x:c r="I15" s="31">
         <x:v>45917</x:v>
       </x:c>
-      <x:c r="J15" s="28" t="n">
+      <x:c r="J15" s="29" t="n">
         <x:v>1216183</x:v>
       </x:c>
-      <x:c r="K15" s="31" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L15" s="32">
+      <x:c r="L15" s="33">
         <x:v>46093.2878703704</x:v>
       </x:c>
-      <x:c r="M15" s="27" t="s">
+      <x:c r="M15" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s">
+      <x:c r="C16" s="28" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="D16" s="28" t="s">
+      <x:c r="D16" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="27" t="s">
+      <x:c r="E16" s="28" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="F16" s="27" t="s">
+      <x:c r="F16" s="28" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="G16" s="27" t="s">
+      <x:c r="G16" s="28" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="H16" s="29">
+      <x:c r="H16" s="30">
         <x:v>46046.1309027778</x:v>
       </x:c>
-      <x:c r="I16" s="30">
+      <x:c r="I16" s="31">
         <x:v>46021</x:v>
       </x:c>
-      <x:c r="J16" s="28" t="n">
+      <x:c r="J16" s="29" t="n">
         <x:v>1216181</x:v>
       </x:c>
-      <x:c r="K16" s="31" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L16" s="32">
+      <x:c r="L16" s="33">
         <x:v>46093.273287037</x:v>
       </x:c>
-      <x:c r="M16" s="27" t="s">
+      <x:c r="M16" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s">
+      <x:c r="C17" s="28" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="D17" s="28" t="s">
+      <x:c r="D17" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E17" s="27" t="s">
+      <x:c r="E17" s="28" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F17" s="27" t="s">
+      <x:c r="F17" s="28" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G17" s="27" t="s">
+      <x:c r="G17" s="28" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H17" s="29">
+      <x:c r="H17" s="30">
         <x:v>46046.1237615741</x:v>
       </x:c>
-      <x:c r="I17" s="30">
+      <x:c r="I17" s="31">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J17" s="28" t="n">
+      <x:c r="J17" s="29" t="n">
         <x:v>1216180</x:v>
       </x:c>
-      <x:c r="K17" s="31" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L17" s="32">
+      <x:c r="L17" s="33">
         <x:v>46093.2636342593</x:v>
       </x:c>
-      <x:c r="M17" s="27" t="s">
+      <x:c r="M17" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s">
+      <x:c r="C18" s="28" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="D18" s="28" t="s">
+      <x:c r="D18" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E18" s="27" t="s">
+      <x:c r="E18" s="28" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="F18" s="27" t="s">
+      <x:c r="F18" s="28" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G18" s="27" t="s">
+      <x:c r="G18" s="28" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H18" s="29">
+      <x:c r="H18" s="30">
         <x:v>46046.1140856482</x:v>
       </x:c>
-      <x:c r="I18" s="30">
+      <x:c r="I18" s="31">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J18" s="28" t="n">
+      <x:c r="J18" s="29" t="n">
         <x:v>1216182</x:v>
       </x:c>
-      <x:c r="K18" s="31" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L18" s="32">
+      <x:c r="L18" s="33">
         <x:v>46093.2825231481</x:v>
       </x:c>
-      <x:c r="M18" s="27" t="s">
+      <x:c r="M18" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="27" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s">
+      <x:c r="C19" s="28" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="D19" s="28" t="s">
+      <x:c r="D19" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E19" s="27" t="s">
+      <x:c r="E19" s="28" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F19" s="27" t="s">
+      <x:c r="F19" s="28" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G19" s="27" t="s">
+      <x:c r="G19" s="28" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H19" s="29">
+      <x:c r="H19" s="30">
         <x:v>46048.0974768518</x:v>
       </x:c>
-      <x:c r="I19" s="30">
+      <x:c r="I19" s="31">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J19" s="28" t="n">
+      <x:c r="J19" s="29" t="n">
         <x:v>1216184</x:v>
       </x:c>
-      <x:c r="K19" s="31" t="n">
+      <x:c r="K19" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L19" s="32">
+      <x:c r="L19" s="33">
         <x:v>46093.2926041667</x:v>
       </x:c>
-      <x:c r="M19" s="27" t="s">
+      <x:c r="M19" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="27" t="s">
+      <x:c r="B20" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s">
+      <x:c r="C20" s="28" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="D20" s="28" t="s">
+      <x:c r="D20" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E20" s="27" t="s">
+      <x:c r="E20" s="28" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="F20" s="27" t="s">
+      <x:c r="F20" s="28" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G20" s="27" t="s">
+      <x:c r="G20" s="28" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="H20" s="29">
+      <x:c r="H20" s="30">
         <x:v>46076.318900463</x:v>
       </x:c>
-      <x:c r="I20" s="30">
+      <x:c r="I20" s="31">
         <x:v>46074</x:v>
       </x:c>
-      <x:c r="J20" s="28" t="n">
+      <x:c r="J20" s="29" t="n">
         <x:v>1216168</x:v>
       </x:c>
-      <x:c r="K20" s="31" t="n">
+      <x:c r="K20" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L20" s="32">
+      <x:c r="L20" s="33">
         <x:v>46092.1400231481</x:v>
       </x:c>
-      <x:c r="M20" s="27" t="s">
+      <x:c r="M20" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="27" t="s">
+      <x:c r="B21" s="28" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s">
+      <x:c r="C21" s="28" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D21" s="28" t="s">
+      <x:c r="D21" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E21" s="27" t="s">
+      <x:c r="E21" s="28" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="F21" s="27" t="s">
+      <x:c r="F21" s="28" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="G21" s="27" t="s">
+      <x:c r="G21" s="28" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="H21" s="29">
+      <x:c r="H21" s="30">
         <x:v>46079.2852546296</x:v>
       </x:c>
-      <x:c r="I21" s="29">
+      <x:c r="I21" s="30">
         <x:v>46079.2852662037</x:v>
       </x:c>
-      <x:c r="J21" s="28" t="n">
+      <x:c r="J21" s="29" t="n">
         <x:v>1216195</x:v>
       </x:c>
-      <x:c r="K21" s="31" t="n">
+      <x:c r="K21" s="32" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L21" s="32">
+      <x:c r="L21" s="33">
         <x:v>46097.2459143518</x:v>
       </x:c>
-      <x:c r="M21" s="27" t="s">
+      <x:c r="M21" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="27" t="s">
+      <x:c r="B22" s="28" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s">
+      <x:c r="C22" s="28" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D22" s="28" t="s">
+      <x:c r="D22" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E22" s="27" t="s">
+      <x:c r="E22" s="28" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F22" s="27" t="s">
+      <x:c r="F22" s="28" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G22" s="27" t="s">
+      <x:c r="G22" s="28" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H22" s="29">
+      <x:c r="H22" s="30">
         <x:v>46079.2747222222</x:v>
       </x:c>
-      <x:c r="I22" s="29">
+      <x:c r="I22" s="30">
         <x:v>46079.2747453704</x:v>
       </x:c>
-      <x:c r="J22" s="28" t="n">
+      <x:c r="J22" s="29" t="n">
         <x:v>1216196</x:v>
       </x:c>
-      <x:c r="K22" s="31" t="n">
+      <x:c r="K22" s="32" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L22" s="32">
+      <x:c r="L22" s="33">
         <x:v>46097.2536342593</x:v>
       </x:c>
-      <x:c r="M22" s="27" t="s">
+      <x:c r="M22" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="27" t="s">
+      <x:c r="B23" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s">
+      <x:c r="C23" s="28" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="27" t="s">
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="28" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="F23" s="27" t="s">
+      <x:c r="F23" s="28" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G23" s="27" t="s">
+      <x:c r="G23" s="28" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="H23" s="29">
+      <x:c r="H23" s="30">
         <x:v>46090.2854050926</x:v>
       </x:c>
-      <x:c r="I23" s="29">
+      <x:c r="I23" s="30">
         <x:v>46090.2854282407</x:v>
       </x:c>
-      <x:c r="J23" s="28" t="s">
+      <x:c r="J23" s="29" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="K23" s="31" t="n">
+      <x:c r="K23" s="32" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L23" s="32">
+      <x:c r="L23" s="33">
         <x:v>46094.0865740741</x:v>
       </x:c>
-      <x:c r="M23" s="27" t="s">
+      <x:c r="M23" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="27" t="s">
+      <x:c r="B24" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s">
+      <x:c r="C24" s="28" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="27" t="s">
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="28" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="F24" s="27" t="s">
+      <x:c r="F24" s="28" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G24" s="27" t="s">
+      <x:c r="G24" s="28" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="H24" s="29">
+      <x:c r="H24" s="30">
         <x:v>46090.2540972222</x:v>
       </x:c>
-      <x:c r="I24" s="29">
+      <x:c r="I24" s="30">
         <x:v>46090.2541203704</x:v>
       </x:c>
-      <x:c r="J24" s="28" t="n">
+      <x:c r="J24" s="29" t="n">
         <x:v>1216185</x:v>
       </x:c>
-      <x:c r="K24" s="31" t="n">
+      <x:c r="K24" s="32" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L24" s="32">
+      <x:c r="L24" s="33">
         <x:v>46094.0818981481</x:v>
       </x:c>
-      <x:c r="M24" s="27" t="s">
+      <x:c r="M24" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="27" t="s">
+      <x:c r="B25" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s">
+      <x:c r="C25" s="28" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="D25" s="28" t="s"/>
-      <x:c r="E25" s="27" t="s">
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="28" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="F25" s="27" t="s">
+      <x:c r="F25" s="28" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G25" s="27" t="s">
+      <x:c r="G25" s="28" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H25" s="29">
+      <x:c r="H25" s="30">
         <x:v>46090.2349189815</x:v>
       </x:c>
-      <x:c r="I25" s="29">
+      <x:c r="I25" s="30">
         <x:v>46090.2349305556</x:v>
       </x:c>
-      <x:c r="J25" s="28" t="n">
+      <x:c r="J25" s="29" t="n">
         <x:v>1216187</x:v>
       </x:c>
-      <x:c r="K25" s="31" t="n">
+      <x:c r="K25" s="32" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L25" s="32">
+      <x:c r="L25" s="33">
         <x:v>46094.0939351852</x:v>
       </x:c>
-      <x:c r="M25" s="27" t="s">
+      <x:c r="M25" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="15" t="s">
+      <x:c r="B28" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C28" s="16" t="s"/>
-      <x:c r="D28" s="16" t="s"/>
-      <x:c r="E28" s="17" t="s"/>
-      <x:c r="F28" s="17" t="s"/>
+      <x:c r="C28" s="17" t="s"/>
+      <x:c r="D28" s="17" t="s"/>
+      <x:c r="E28" s="18" t="s"/>
+      <x:c r="F28" s="18" t="s"/>
     </x:row>
     <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="18" t="s">
+      <x:c r="B29" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C29" s="19" t="s"/>
-      <x:c r="D29" s="19" t="s"/>
-      <x:c r="E29" s="19" t="s"/>
-      <x:c r="F29" s="20" t="s">
+      <x:c r="C29" s="20" t="s"/>
+      <x:c r="D29" s="20" t="s"/>
+      <x:c r="E29" s="20" t="s"/>
+      <x:c r="F29" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="21" t="s">
+      <x:c r="B30" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C30" s="22" t="s"/>
-      <x:c r="D30" s="22" t="s"/>
-      <x:c r="E30" s="22" t="s"/>
-      <x:c r="F30" s="23" t="n">
+      <x:c r="C30" s="23" t="s"/>
+      <x:c r="D30" s="23" t="s"/>
+      <x:c r="E30" s="23" t="s"/>
+      <x:c r="F30" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="21" t="s">
+      <x:c r="B31" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C31" s="22" t="s"/>
-      <x:c r="D31" s="22" t="s"/>
-      <x:c r="E31" s="22" t="s"/>
-      <x:c r="F31" s="23" t="n">
+      <x:c r="C31" s="23" t="s"/>
+      <x:c r="D31" s="23" t="s"/>
+      <x:c r="E31" s="23" t="s"/>
+      <x:c r="F31" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="21" t="s">
+      <x:c r="B32" s="22" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C32" s="22" t="s"/>
-      <x:c r="D32" s="22" t="s"/>
-      <x:c r="E32" s="22" t="s"/>
-      <x:c r="F32" s="23" t="n">
+      <x:c r="C32" s="23" t="s"/>
+      <x:c r="D32" s="23" t="s"/>
+      <x:c r="E32" s="23" t="s"/>
+      <x:c r="F32" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="21" t="s">
+      <x:c r="B33" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C33" s="22" t="s"/>
-      <x:c r="D33" s="22" t="s"/>
-      <x:c r="E33" s="22" t="s"/>
-      <x:c r="F33" s="23" t="n">
+      <x:c r="C33" s="23" t="s"/>
+      <x:c r="D33" s="23" t="s"/>
+      <x:c r="E33" s="23" t="s"/>
+      <x:c r="F33" s="24" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="21" t="s">
+      <x:c r="B34" s="22" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="C34" s="22" t="s"/>
-      <x:c r="D34" s="22" t="s"/>
-      <x:c r="E34" s="22" t="s"/>
-      <x:c r="F34" s="23" t="n">
+      <x:c r="C34" s="23" t="s"/>
+      <x:c r="D34" s="23" t="s"/>
+      <x:c r="E34" s="23" t="s"/>
+      <x:c r="F34" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="21" t="s">
+      <x:c r="B35" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C35" s="22" t="s"/>
-      <x:c r="D35" s="22" t="s"/>
-      <x:c r="E35" s="22" t="s"/>
-      <x:c r="F35" s="23" t="n">
+      <x:c r="C35" s="23" t="s"/>
+      <x:c r="D35" s="23" t="s"/>
+      <x:c r="E35" s="23" t="s"/>
+      <x:c r="F35" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="24" t="s">
+      <x:c r="B36" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C36" s="25" t="s"/>
-      <x:c r="D36" s="25" t="s"/>
-      <x:c r="E36" s="25" t="s"/>
-      <x:c r="F36" s="26" t="n">
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -3465,7 +3474,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45839</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3537,171 +3548,171 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45860.0993981482</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1346409</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45860.1449537037</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45861.1130439815</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>45861.1130555556</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1346412</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45862.3035648148</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="C12" s="17" t="s"/>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="18" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -4752,7 +4763,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45870</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -4824,345 +4837,345 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45866.2802893519</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>45866.2803009259</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215849</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45873.1184143519</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45875.2238888889</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215853</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>4030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45876.2432986111</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45880.1214814815</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>45882</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1346457</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45881.1618981482</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="D11" s="29" t="s"/>
+      <x:c r="E11" s="28" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>45873.2195486111</x:v>
       </x:c>
-      <x:c r="I11" s="29">
+      <x:c r="I11" s="30">
         <x:v>45873.2195601852</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1195700</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>2790</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>45882.1150694444</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>45875.361724537</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1215851</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>45876.2230902778</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>45875.2324652778</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1215852</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>45876.2319791667</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="s"/>
-      <x:c r="D16" s="16" t="s"/>
-      <x:c r="E16" s="17" t="s"/>
-      <x:c r="F16" s="17" t="s"/>
+      <x:c r="C16" s="17" t="s"/>
+      <x:c r="D16" s="17" t="s"/>
+      <x:c r="E16" s="18" t="s"/>
+      <x:c r="F16" s="18" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="18" t="s">
+      <x:c r="B17" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C17" s="19" t="s"/>
-      <x:c r="D17" s="19" t="s"/>
-      <x:c r="E17" s="19" t="s"/>
-      <x:c r="F17" s="20" t="s">
+      <x:c r="C17" s="20" t="s"/>
+      <x:c r="D17" s="20" t="s"/>
+      <x:c r="E17" s="20" t="s"/>
+      <x:c r="F17" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="21" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="s"/>
-      <x:c r="D18" s="22" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="23" t="n">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -6209,7 +6222,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45901</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -6281,383 +6296,383 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45915.355787037</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215901</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45918.2339583333</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45903.3849652778</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45916</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215886</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>3150</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45908.2848958333</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45919.4023032407</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1215905</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45925.945150463</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>45918.1053935185</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>45900</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1215910</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>45929.2194097222</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>45908.2183449074</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>45918</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1215894</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>45912.1906134259</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>45922.1415393519</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1346550</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>45922.1832523148</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s">
+      <x:c r="C14" s="28" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="27" t="s">
+      <x:c r="D14" s="29" t="s"/>
+      <x:c r="E14" s="28" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F14" s="27" t="s">
+      <x:c r="F14" s="28" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G14" s="27" t="s">
+      <x:c r="G14" s="28" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H14" s="29">
+      <x:c r="H14" s="30">
         <x:v>45919.473287037</x:v>
       </x:c>
-      <x:c r="I14" s="29">
+      <x:c r="I14" s="30">
         <x:v>45919.4732986111</x:v>
       </x:c>
-      <x:c r="J14" s="28" t="n">
+      <x:c r="J14" s="29" t="n">
         <x:v>1215906</x:v>
       </x:c>
-      <x:c r="K14" s="31" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L14" s="32">
+      <x:c r="L14" s="33">
         <x:v>45926.2586111111</x:v>
       </x:c>
-      <x:c r="M14" s="27" t="s">
+      <x:c r="M14" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C17" s="16" t="s"/>
-      <x:c r="D17" s="16" t="s"/>
-      <x:c r="E17" s="17" t="s"/>
-      <x:c r="F17" s="17" t="s"/>
+      <x:c r="C17" s="17" t="s"/>
+      <x:c r="D17" s="17" t="s"/>
+      <x:c r="E17" s="18" t="s"/>
+      <x:c r="F17" s="18" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="18" t="s">
+      <x:c r="B18" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C18" s="19" t="s"/>
-      <x:c r="D18" s="19" t="s"/>
-      <x:c r="E18" s="19" t="s"/>
-      <x:c r="F18" s="20" t="s">
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="20" t="s"/>
+      <x:c r="F18" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="21" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="s"/>
-      <x:c r="D19" s="22" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="23" t="n">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="21" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="n">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="n">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="21" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="s"/>
-      <x:c r="D22" s="22" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="23" t="n">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7703,7 +7718,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45931</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -7775,207 +7792,207 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45933.0884375</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45932</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1215922</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45936.014837963</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45928.9304513889</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>45928.9304861111</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1215924</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45938.0359375</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s"/>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="D10" s="29" t="s"/>
+      <x:c r="E10" s="28" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45926.4563888889</x:v>
       </x:c>
-      <x:c r="I10" s="29">
+      <x:c r="I10" s="30">
         <x:v>45926.4564351852</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1215917</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45932.239537037</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C13" s="16" t="s"/>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="17" t="s"/>
-      <x:c r="F13" s="17" t="s"/>
+      <x:c r="C13" s="17" t="s"/>
+      <x:c r="D13" s="17" t="s"/>
+      <x:c r="E13" s="18" t="s"/>
+      <x:c r="F13" s="18" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="18" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="20" t="s">
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -9025,7 +9042,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45962</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -9097,553 +9116,553 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45951.1032638889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>45951.103287037</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1346752</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45971.0888194444</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45980.2160416667</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1346786</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45985.3594791667</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45965.2736689815</x:v>
       </x:c>
-      <x:c r="I10" s="29">
+      <x:c r="I10" s="30">
         <x:v>45965.2736921296</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1216000</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45972.1539583333</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>45965.2661458333</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1215999</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>45972.1364236111</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="27" t="s">
+      <x:c r="B12" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s">
+      <x:c r="C12" s="28" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="s">
+      <x:c r="D12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E12" s="27" t="s">
+      <x:c r="E12" s="28" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F12" s="27" t="s">
+      <x:c r="F12" s="28" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G12" s="27" t="s">
+      <x:c r="G12" s="28" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H12" s="29">
+      <x:c r="H12" s="30">
         <x:v>45953.5328240741</x:v>
       </x:c>
-      <x:c r="I12" s="30">
+      <x:c r="I12" s="31">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J12" s="28" t="n">
+      <x:c r="J12" s="29" t="n">
         <x:v>1215970</x:v>
       </x:c>
-      <x:c r="K12" s="31" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="32">
+      <x:c r="L12" s="33">
         <x:v>45966.0458101852</x:v>
       </x:c>
-      <x:c r="M12" s="27" t="s">
+      <x:c r="M12" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="27" t="s">
+      <x:c r="B13" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s">
+      <x:c r="C13" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="s">
+      <x:c r="D13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E13" s="27" t="s">
+      <x:c r="E13" s="28" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F13" s="27" t="s">
+      <x:c r="F13" s="28" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G13" s="27" t="s">
+      <x:c r="G13" s="28" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H13" s="29">
+      <x:c r="H13" s="30">
         <x:v>45959.0699074074</x:v>
       </x:c>
-      <x:c r="I13" s="30">
+      <x:c r="I13" s="31">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J13" s="28" t="n">
+      <x:c r="J13" s="29" t="n">
         <x:v>1346761</x:v>
       </x:c>
-      <x:c r="K13" s="31" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="32">
+      <x:c r="L13" s="33">
         <x:v>45972.2719560185</x:v>
       </x:c>
-      <x:c r="M13" s="27" t="s">
+      <x:c r="M13" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s">
+      <x:c r="C14" s="28" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="s">
+      <x:c r="D14" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E14" s="27" t="s">
+      <x:c r="E14" s="28" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F14" s="27" t="s">
+      <x:c r="F14" s="28" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G14" s="27" t="s">
+      <x:c r="G14" s="28" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H14" s="29">
+      <x:c r="H14" s="30">
         <x:v>45958.0724421296</x:v>
       </x:c>
-      <x:c r="I14" s="30">
+      <x:c r="I14" s="31">
         <x:v>45810</x:v>
       </x:c>
-      <x:c r="J14" s="28" t="n">
+      <x:c r="J14" s="29" t="n">
         <x:v>1216003</x:v>
       </x:c>
-      <x:c r="K14" s="31" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L14" s="32">
+      <x:c r="L14" s="33">
         <x:v>45973.0584490741</x:v>
       </x:c>
-      <x:c r="M14" s="27" t="s">
+      <x:c r="M14" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="27" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s">
+      <x:c r="C15" s="28" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="s">
+      <x:c r="D15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E15" s="27" t="s">
+      <x:c r="E15" s="28" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="F15" s="27" t="s">
+      <x:c r="F15" s="28" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G15" s="27" t="s">
+      <x:c r="G15" s="28" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H15" s="29">
+      <x:c r="H15" s="30">
         <x:v>45973.1309375</x:v>
       </x:c>
-      <x:c r="I15" s="30">
+      <x:c r="I15" s="31">
         <x:v>45950</x:v>
       </x:c>
-      <x:c r="J15" s="28" t="n">
+      <x:c r="J15" s="29" t="n">
         <x:v>1216020</x:v>
       </x:c>
-      <x:c r="K15" s="31" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L15" s="32">
+      <x:c r="L15" s="33">
         <x:v>45985.2116666667</x:v>
       </x:c>
-      <x:c r="M15" s="27" t="s">
+      <x:c r="M15" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s">
+      <x:c r="C16" s="28" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D16" s="28" t="s">
+      <x:c r="D16" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E16" s="27" t="s">
+      <x:c r="E16" s="28" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="F16" s="27" t="s">
+      <x:c r="F16" s="28" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G16" s="27" t="s">
+      <x:c r="G16" s="28" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="H16" s="29">
+      <x:c r="H16" s="30">
         <x:v>45971.2436226852</x:v>
       </x:c>
-      <x:c r="I16" s="30">
+      <x:c r="I16" s="31">
         <x:v>45608</x:v>
       </x:c>
-      <x:c r="J16" s="28" t="n">
+      <x:c r="J16" s="29" t="n">
         <x:v>1216004</x:v>
       </x:c>
-      <x:c r="K16" s="31" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L16" s="32">
+      <x:c r="L16" s="33">
         <x:v>45973.2287268518</x:v>
       </x:c>
-      <x:c r="M16" s="27" t="s">
+      <x:c r="M16" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s">
+      <x:c r="C17" s="28" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="27" t="s">
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="28" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="F17" s="27" t="s">
+      <x:c r="F17" s="28" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G17" s="27" t="s">
+      <x:c r="G17" s="28" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="H17" s="29">
+      <x:c r="H17" s="30">
         <x:v>45954.4189930556</x:v>
       </x:c>
-      <x:c r="I17" s="29">
+      <x:c r="I17" s="30">
         <x:v>45954.4190277778</x:v>
       </x:c>
-      <x:c r="J17" s="28" t="n">
+      <x:c r="J17" s="29" t="n">
         <x:v>1215987</x:v>
       </x:c>
-      <x:c r="K17" s="31" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L17" s="32">
+      <x:c r="L17" s="33">
         <x:v>45967.2850694444</x:v>
       </x:c>
-      <x:c r="M17" s="27" t="s">
+      <x:c r="M17" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s">
+      <x:c r="C18" s="28" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="27" t="s">
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="28" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="F18" s="27" t="s">
+      <x:c r="F18" s="28" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="G18" s="27" t="s">
+      <x:c r="G18" s="28" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="H18" s="29">
+      <x:c r="H18" s="30">
         <x:v>45959.2592013889</x:v>
       </x:c>
-      <x:c r="I18" s="29">
+      <x:c r="I18" s="30">
         <x:v>45959.259224537</x:v>
       </x:c>
-      <x:c r="J18" s="28" t="n">
+      <x:c r="J18" s="29" t="n">
         <x:v>1216022</x:v>
       </x:c>
-      <x:c r="K18" s="31" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L18" s="32">
+      <x:c r="L18" s="33">
         <x:v>45986.1291898148</x:v>
       </x:c>
-      <x:c r="M18" s="27" t="s">
+      <x:c r="M18" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C21" s="16" t="s"/>
-      <x:c r="D21" s="16" t="s"/>
-      <x:c r="E21" s="17" t="s"/>
-      <x:c r="F21" s="17" t="s"/>
+      <x:c r="C21" s="17" t="s"/>
+      <x:c r="D21" s="17" t="s"/>
+      <x:c r="E21" s="18" t="s"/>
+      <x:c r="F21" s="18" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="18" t="s">
+      <x:c r="B22" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C22" s="19" t="s"/>
-      <x:c r="D22" s="19" t="s"/>
-      <x:c r="E22" s="19" t="s"/>
-      <x:c r="F22" s="20" t="s">
+      <x:c r="C22" s="20" t="s"/>
+      <x:c r="D22" s="20" t="s"/>
+      <x:c r="E22" s="20" t="s"/>
+      <x:c r="F22" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="21" t="s">
+      <x:c r="B23" s="22" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="23" t="n">
+      <x:c r="C23" s="23" t="s"/>
+      <x:c r="D23" s="23" t="s"/>
+      <x:c r="E23" s="23" t="s"/>
+      <x:c r="F23" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="21" t="s">
+      <x:c r="B24" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="22" t="s"/>
-      <x:c r="F24" s="23" t="n">
+      <x:c r="C24" s="23" t="s"/>
+      <x:c r="D24" s="23" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="21" t="s">
+      <x:c r="B25" s="22" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="23" t="n">
+      <x:c r="C25" s="23" t="s"/>
+      <x:c r="D25" s="23" t="s"/>
+      <x:c r="E25" s="23" t="s"/>
+      <x:c r="F25" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="21" t="s">
+      <x:c r="B26" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C26" s="22" t="s"/>
-      <x:c r="D26" s="22" t="s"/>
-      <x:c r="E26" s="22" t="s"/>
-      <x:c r="F26" s="23" t="n">
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="21" t="s">
+      <x:c r="B27" s="22" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="C27" s="22" t="s"/>
-      <x:c r="D27" s="22" t="s"/>
-      <x:c r="E27" s="22" t="s"/>
-      <x:c r="F27" s="23" t="n">
+      <x:c r="C27" s="23" t="s"/>
+      <x:c r="D27" s="23" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="21" t="s">
+      <x:c r="B28" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C28" s="22" t="s"/>
-      <x:c r="D28" s="22" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="23" t="n">
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="24" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -10685,7 +10704,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45992</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -10757,238 +10778,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45981.1374421296</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216030</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45996.1054282407</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45994.1029050926</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>45169</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216035</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>12780</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46006.2230439815</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45973.2824074074</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1216029</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>45993.0810763889</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s">
+      <x:c r="D11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="E11" s="28" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>45988.1651388889</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="31">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1216036</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46006.2389583333</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="16" t="s"/>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="17" t="s"/>
-      <x:c r="F14" s="17" t="s"/>
+      <x:c r="C14" s="17" t="s"/>
+      <x:c r="D14" s="17" t="s"/>
+      <x:c r="E14" s="18" t="s"/>
+      <x:c r="F14" s="18" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="18" t="s">
+      <x:c r="B15" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="20" t="s">
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12037,7 +12058,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46023</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -12109,247 +12132,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46033.3509837963</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1216094</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46049.2368865741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46010.1939351852</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46029</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1216062</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46034.111087963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>45989.0397222222</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1216078</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46043.2235069444</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="27" t="s">
+      <x:c r="B11" s="28" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="s">
+      <x:c r="C11" s="28" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="s"/>
-      <x:c r="E11" s="27" t="s">
+      <x:c r="D11" s="29" t="s"/>
+      <x:c r="E11" s="28" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="F11" s="27" t="s">
+      <x:c r="F11" s="28" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="s">
+      <x:c r="G11" s="28" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="H11" s="29">
+      <x:c r="H11" s="30">
         <x:v>46043.045474537</x:v>
       </x:c>
-      <x:c r="I11" s="29">
+      <x:c r="I11" s="30">
         <x:v>46043.0455092593</x:v>
       </x:c>
-      <x:c r="J11" s="28" t="n">
+      <x:c r="J11" s="29" t="n">
         <x:v>1216091</x:v>
       </x:c>
-      <x:c r="K11" s="31" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L11" s="32">
+      <x:c r="L11" s="33">
         <x:v>46048.2516435185</x:v>
       </x:c>
-      <x:c r="M11" s="27" t="s">
+      <x:c r="M11" s="28" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="16" t="s"/>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="17" t="s"/>
-      <x:c r="F14" s="17" t="s"/>
+      <x:c r="C14" s="17" t="s"/>
+      <x:c r="D14" s="17" t="s"/>
+      <x:c r="E14" s="18" t="s"/>
+      <x:c r="F14" s="18" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="18" t="s">
+      <x:c r="B15" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C15" s="19" t="s"/>
-      <x:c r="D15" s="19" t="s"/>
-      <x:c r="E15" s="19" t="s"/>
-      <x:c r="F15" s="20" t="s">
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="21" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="s"/>
-      <x:c r="D17" s="22" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="23" t="n">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="24" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="s"/>
-      <x:c r="D18" s="25" t="s"/>
-      <x:c r="E18" s="25" t="s"/>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13398,7 +13421,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46054</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -13470,211 +13495,211 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46058.3038078704</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>1195989</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46066.3127777778</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46066.3781828704</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="14">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1346991</x:v>
       </x:c>
-      <x:c r="K9" s="14" t="n">
+      <x:c r="K9" s="15" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46077.0856712963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="27" t="s">
+      <x:c r="B10" s="28" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="s">
+      <x:c r="C10" s="28" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="s">
+      <x:c r="D10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="s">
+      <x:c r="E10" s="28" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="s">
+      <x:c r="F10" s="28" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="s">
+      <x:c r="G10" s="28" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="H10" s="29">
+      <x:c r="H10" s="30">
         <x:v>46062.2741666667</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="31">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J10" s="28" t="n">
+      <x:c r="J10" s="29" t="n">
         <x:v>1346991</x:v>
       </x:c>
-      <x:c r="K10" s="31" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="32">
+      <x:c r="L10" s="33">
         <x:v>46077.1029513889</x:v>
       </x:c>
-      <x:c r="M10" s="27" t="s">
+      <x:c r="M10" s="28" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C13" s="16" t="s"/>
-      <x:c r="D13" s="16" t="s"/>
-      <x:c r="E13" s="17" t="s"/>
-      <x:c r="F13" s="17" t="s"/>
+      <x:c r="C13" s="17" t="s"/>
+      <x:c r="D13" s="17" t="s"/>
+      <x:c r="E13" s="18" t="s"/>
+      <x:c r="F13" s="18" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="18" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="20" t="s">
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="21" t="s">
         <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="21" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="s"/>
-      <x:c r="D16" s="22" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="23" t="n">
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,9 +30,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
-  <x:si>
-    <x:t>PERMIT SUMMARY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+  <x:si>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMITS SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | July 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -119,6 +125,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | August 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -197,6 +206,9 @@
     <x:t>61-8-2025-1093</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | September 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>VALIANT ELECTRONICS SUPPLY</x:t>
   </x:si>
   <x:si>
@@ -287,6 +299,9 @@
     <x:t>61-9-2025-1171</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | October 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMCOR INC TIGUMA BRANCH</x:t>
   </x:si>
   <x:si>
@@ -323,6 +338,9 @@
     <x:t>61-9-2025-1178</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | November 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -452,6 +470,9 @@
     <x:t>61-10-2025-1216</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | December 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>AB GADGETS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -500,6 +521,9 @@
     <x:t>61-11-2025-1251-543</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | January 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, Poblacion, San Pablo, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -545,6 +569,9 @@
     <x:t>61-1-2026-1283-474</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>DES APPLIANCE PLAZA, INC.</x:t>
   </x:si>
   <x:si>
@@ -576,6 +603,9 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1317-596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>MINZ CELLPHONE AND ACCESSORIES SHOP</x:t>
@@ -792,7 +822,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -832,6 +862,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1103,15 +1157,21 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1126,52 +1186,10 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1180,8 +1198,50 @@
     <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1212,80 +1272,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1304,7 +1304,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1533,58 +1601,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -1627,819 +1695,819 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46088.1798263889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46088.179837963</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1216179</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46093.2393865741</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46077.2833680556</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1217027</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46094.1366782407</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>46088.1798263889</x:v>
-      </x:c>
-      <x:c r="I8" s="13">
-        <x:v>46088.179837963</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1216179</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46076.2809953704</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>46076.2810185185</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1216194</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>46097.2411111111</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46076.245</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46076.2450115741</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1216190</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>46094.1710416667</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>46076.2578009259</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46076.2578240741</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1216197</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="35">
+        <x:v>46097.2583912037</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46076.2633680556</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="n">
+        <x:v>1216188</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="13">
-        <x:v>46093.2393865741</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="L13" s="35">
+        <x:v>46094.1562731481</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46076.3755439815</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="n">
+        <x:v>1216189</x:v>
+      </x:c>
+      <x:c r="K14" s="34" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="35">
+        <x:v>46094.1653935185</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46077.2833680556</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1217027</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46094.1366782407</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>175</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>46076.2809953704</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>46076.2810185185</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1216194</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46097.2411111111</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>46076.245</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>46076.2450115741</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1216190</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46094.1710416667</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
+      <x:c r="C15" s="30" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46046.1343634259</x:v>
+      </x:c>
+      <x:c r="I15" s="33">
+        <x:v>45917</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="n">
+        <x:v>1216183</x:v>
+      </x:c>
+      <x:c r="K15" s="34" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L15" s="35">
+        <x:v>46093.2878703704</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="F16" s="30" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H16" s="32">
+        <x:v>46046.1309027778</x:v>
+      </x:c>
+      <x:c r="I16" s="33">
+        <x:v>46021</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="n">
+        <x:v>1216181</x:v>
+      </x:c>
+      <x:c r="K16" s="34" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L16" s="35">
+        <x:v>46093.273287037</x:v>
+      </x:c>
+      <x:c r="M16" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F17" s="30" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
+        <x:v>46046.1237615741</x:v>
+      </x:c>
+      <x:c r="I17" s="33">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="n">
+        <x:v>1216180</x:v>
+      </x:c>
+      <x:c r="K17" s="34" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L17" s="35">
+        <x:v>46093.2636342593</x:v>
+      </x:c>
+      <x:c r="M17" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46046.1140856482</x:v>
+      </x:c>
+      <x:c r="I18" s="33">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="n">
+        <x:v>1216182</x:v>
+      </x:c>
+      <x:c r="K18" s="34" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="35">
+        <x:v>46093.2825231481</x:v>
+      </x:c>
+      <x:c r="M18" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F19" s="30" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I19" s="33">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="n">
+        <x:v>1216184</x:v>
+      </x:c>
+      <x:c r="K19" s="34" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L19" s="35">
+        <x:v>46093.2926041667</x:v>
+      </x:c>
+      <x:c r="M19" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F20" s="30" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I20" s="33">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="n">
+        <x:v>1216168</x:v>
+      </x:c>
+      <x:c r="K20" s="34" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L20" s="35">
+        <x:v>46092.1400231481</x:v>
+      </x:c>
+      <x:c r="M20" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="30" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>46076.2578009259</x:v>
-      </x:c>
-      <x:c r="I12" s="30">
-        <x:v>46076.2578240741</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1216197</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>46097.2583912037</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>46076.2633564815</x:v>
-      </x:c>
-      <x:c r="I13" s="30">
-        <x:v>46076.2633680556</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="n">
-        <x:v>1216188</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>46094.1562731481</x:v>
-      </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D14" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E14" s="28" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F14" s="28" t="s">
+      <x:c r="D21" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F21" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46079.2852546296</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46079.2852662037</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="n">
+        <x:v>1216195</x:v>
+      </x:c>
+      <x:c r="K21" s="34" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L21" s="35">
+        <x:v>46097.2459143518</x:v>
+      </x:c>
+      <x:c r="M21" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G14" s="28" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H14" s="30">
-        <x:v>46076.3755324074</x:v>
-      </x:c>
-      <x:c r="I14" s="30">
-        <x:v>46076.3755439815</x:v>
-      </x:c>
-      <x:c r="J14" s="29" t="n">
-        <x:v>1216189</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L14" s="33">
-        <x:v>46094.1653935185</x:v>
-      </x:c>
-      <x:c r="M14" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="D15" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="28" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F15" s="28" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>45917</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="n">
-        <x:v>1216183</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L15" s="33">
-        <x:v>46093.2878703704</x:v>
-      </x:c>
-      <x:c r="M15" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D16" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="28" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F16" s="28" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G16" s="28" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
-        <x:v>46021</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="n">
-        <x:v>1216181</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L16" s="33">
-        <x:v>46093.273287037</x:v>
-      </x:c>
-      <x:c r="M16" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D17" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" s="28" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="F17" s="28" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="G17" s="28" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="H17" s="30">
-        <x:v>46046.1237615741</x:v>
-      </x:c>
-      <x:c r="I17" s="31">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J17" s="29" t="n">
-        <x:v>1216180</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L17" s="33">
-        <x:v>46093.2636342593</x:v>
-      </x:c>
-      <x:c r="M17" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="D18" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="28" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="F18" s="28" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G18" s="28" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
-        <x:v>46046.1140856482</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J18" s="29" t="n">
-        <x:v>1216182</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="33">
-        <x:v>46093.2825231481</x:v>
-      </x:c>
-      <x:c r="M18" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D19" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="28" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F19" s="28" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G19" s="28" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H19" s="30">
-        <x:v>46048.0974768518</x:v>
-      </x:c>
-      <x:c r="I19" s="31">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J19" s="29" t="n">
-        <x:v>1216184</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="33">
-        <x:v>46093.2926041667</x:v>
-      </x:c>
-      <x:c r="M19" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D20" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="28" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="F20" s="28" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="G20" s="28" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H20" s="30">
-        <x:v>46076.318900463</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J20" s="29" t="n">
-        <x:v>1216168</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L20" s="33">
-        <x:v>46092.1400231481</x:v>
-      </x:c>
-      <x:c r="M20" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="28" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="C21" s="28" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="D21" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E21" s="28" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="F21" s="28" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="G21" s="28" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="H21" s="30">
-        <x:v>46079.2852546296</x:v>
-      </x:c>
-      <x:c r="I21" s="30">
-        <x:v>46079.2852662037</x:v>
-      </x:c>
-      <x:c r="J21" s="29" t="n">
-        <x:v>1216195</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
+      <x:c r="D22" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F22" s="30" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>46079.2747222222</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46079.2747453704</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="n">
+        <x:v>1216196</x:v>
+      </x:c>
+      <x:c r="K22" s="34" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L21" s="33">
-        <x:v>46097.2459143518</x:v>
-      </x:c>
-      <x:c r="M21" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="C22" s="28" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="D22" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E22" s="28" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="F22" s="28" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G22" s="28" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="H22" s="30">
-        <x:v>46079.2747222222</x:v>
-      </x:c>
-      <x:c r="I22" s="30">
-        <x:v>46079.2747453704</x:v>
-      </x:c>
-      <x:c r="J22" s="29" t="n">
-        <x:v>1216196</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L22" s="33">
+      <x:c r="L22" s="35">
         <x:v>46097.2536342593</x:v>
       </x:c>
-      <x:c r="M22" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M22" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C23" s="28" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="28" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F23" s="28" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G23" s="28" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H23" s="30">
+      <x:c r="B23" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="s"/>
+      <x:c r="E23" s="30" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
         <x:v>46090.2854050926</x:v>
       </x:c>
-      <x:c r="I23" s="30">
+      <x:c r="I23" s="32">
         <x:v>46090.2854282407</x:v>
       </x:c>
-      <x:c r="J23" s="29" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
+      <x:c r="J23" s="31" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="K23" s="34" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L23" s="33">
+      <x:c r="L23" s="35">
         <x:v>46094.0865740741</x:v>
       </x:c>
-      <x:c r="M23" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M23" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C24" s="28" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="28" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F24" s="28" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G24" s="28" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H24" s="30">
+      <x:c r="B24" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="s"/>
+      <x:c r="E24" s="30" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F24" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="H24" s="32">
         <x:v>46090.2540972222</x:v>
       </x:c>
-      <x:c r="I24" s="30">
+      <x:c r="I24" s="32">
         <x:v>46090.2541203704</x:v>
       </x:c>
-      <x:c r="J24" s="29" t="n">
+      <x:c r="J24" s="31" t="n">
         <x:v>1216185</x:v>
       </x:c>
-      <x:c r="K24" s="32" t="n">
+      <x:c r="K24" s="34" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L24" s="33">
+      <x:c r="L24" s="35">
         <x:v>46094.0818981481</x:v>
       </x:c>
-      <x:c r="M24" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M24" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C25" s="28" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="28" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F25" s="28" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G25" s="28" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H25" s="30">
+      <x:c r="B25" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D25" s="31" t="s"/>
+      <x:c r="E25" s="30" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F25" s="30" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H25" s="32">
         <x:v>46090.2349189815</x:v>
       </x:c>
-      <x:c r="I25" s="30">
+      <x:c r="I25" s="32">
         <x:v>46090.2349305556</x:v>
       </x:c>
-      <x:c r="J25" s="29" t="n">
+      <x:c r="J25" s="31" t="n">
         <x:v>1216187</x:v>
       </x:c>
-      <x:c r="K25" s="32" t="n">
+      <x:c r="K25" s="34" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L25" s="33">
+      <x:c r="L25" s="35">
         <x:v>46094.0939351852</x:v>
       </x:c>
-      <x:c r="M25" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M25" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C28" s="17" t="s"/>
-      <x:c r="D28" s="17" t="s"/>
-      <x:c r="E28" s="18" t="s"/>
-      <x:c r="F28" s="18" t="s"/>
+      <x:c r="B28" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C28" s="19" t="s"/>
+      <x:c r="D28" s="19" t="s"/>
+      <x:c r="E28" s="20" t="s"/>
+      <x:c r="F28" s="20" t="s"/>
     </x:row>
     <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C29" s="20" t="s"/>
-      <x:c r="D29" s="20" t="s"/>
-      <x:c r="E29" s="20" t="s"/>
-      <x:c r="F29" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B29" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C29" s="22" t="s"/>
+      <x:c r="D29" s="22" t="s"/>
+      <x:c r="E29" s="22" t="s"/>
+      <x:c r="F29" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C30" s="23" t="s"/>
-      <x:c r="D30" s="23" t="s"/>
-      <x:c r="E30" s="23" t="s"/>
-      <x:c r="F30" s="24" t="n">
+      <x:c r="B30" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="s"/>
+      <x:c r="D30" s="25" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C31" s="23" t="s"/>
-      <x:c r="D31" s="23" t="s"/>
-      <x:c r="E31" s="23" t="s"/>
-      <x:c r="F31" s="24" t="n">
+      <x:c r="B31" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="22" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C32" s="23" t="s"/>
-      <x:c r="D32" s="23" t="s"/>
-      <x:c r="E32" s="23" t="s"/>
-      <x:c r="F32" s="24" t="n">
+      <x:c r="B32" s="24" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C32" s="25" t="s"/>
+      <x:c r="D32" s="25" t="s"/>
+      <x:c r="E32" s="25" t="s"/>
+      <x:c r="F32" s="26" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C33" s="23" t="s"/>
-      <x:c r="D33" s="23" t="s"/>
-      <x:c r="E33" s="23" t="s"/>
-      <x:c r="F33" s="24" t="n">
+      <x:c r="B33" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C33" s="25" t="s"/>
+      <x:c r="D33" s="25" t="s"/>
+      <x:c r="E33" s="25" t="s"/>
+      <x:c r="F33" s="26" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="22" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="C34" s="23" t="s"/>
-      <x:c r="D34" s="23" t="s"/>
-      <x:c r="E34" s="23" t="s"/>
-      <x:c r="F34" s="24" t="n">
+      <x:c r="B34" s="24" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="C34" s="25" t="s"/>
+      <x:c r="D34" s="25" t="s"/>
+      <x:c r="E34" s="25" t="s"/>
+      <x:c r="F34" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C35" s="23" t="s"/>
-      <x:c r="D35" s="23" t="s"/>
-      <x:c r="E35" s="23" t="s"/>
-      <x:c r="F35" s="24" t="n">
+      <x:c r="B35" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C35" s="25" t="s"/>
+      <x:c r="D35" s="25" t="s"/>
+      <x:c r="E35" s="25" t="s"/>
+      <x:c r="F35" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C36" s="26" t="s"/>
-      <x:c r="D36" s="26" t="s"/>
-      <x:c r="E36" s="26" t="s"/>
-      <x:c r="F36" s="27" t="n">
+      <x:c r="B36" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C36" s="28" t="s"/>
+      <x:c r="D36" s="28" t="s"/>
+      <x:c r="E36" s="28" t="s"/>
+      <x:c r="F36" s="29" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -3404,7 +3472,7 @@
   <x:mergeCells count="12">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B28:F28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
@@ -3454,58 +3522,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45839</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3548,171 +3616,171 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="F8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45860.0993981482</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1346409</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45860.1449537037</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45861.1130439815</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45861.1130555556</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346412</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45862.3035648148</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45861.1130439815</x:v>
-      </x:c>
-      <x:c r="I9" s="13">
-        <x:v>45861.1130555556</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1346412</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45862.3035648148</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s"/>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="18" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B13" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="B14" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -4697,7 +4765,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
@@ -4743,58 +4811,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45870</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -4837,345 +4905,345 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="E8" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45866.2802893519</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="15">
         <x:v>45866.2803009259</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215849</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45873.1184143519</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>35</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45875.2238888889</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215853</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45876.2432986111</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>45880.1214814815</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1346457</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>45881.1618981482</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s"/>
+      <x:c r="E11" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>45873.2195486111</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>45873.2195601852</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1195700</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>45882.1150694444</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
+      <x:c r="C12" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>45875.361724537</x:v>
+      </x:c>
+      <x:c r="I12" s="33">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1215851</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="35">
+        <x:v>45876.2230902778</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45875.2238888889</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1215853</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45876.2432986111</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
+      <x:c r="D13" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>45880.1214814815</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s"/>
-      <x:c r="E11" s="28" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>45873.2195486111</x:v>
-      </x:c>
-      <x:c r="I11" s="30">
-        <x:v>45873.2195601852</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1195700</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>2790</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45882.1150694444</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
+      <x:c r="F13" s="30" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>45875.2324652778</x:v>
+      </x:c>
+      <x:c r="I13" s="33">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="n">
+        <x:v>1215852</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="35">
+        <x:v>45876.2319791667</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>45875.361724537</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1215851</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45876.2230902778</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>45876.2319791667</x:v>
-      </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C16" s="17" t="s"/>
-      <x:c r="D16" s="17" t="s"/>
-      <x:c r="E16" s="18" t="s"/>
-      <x:c r="F16" s="18" t="s"/>
+      <x:c r="B16" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="s"/>
+      <x:c r="D16" s="19" t="s"/>
+      <x:c r="E16" s="20" t="s"/>
+      <x:c r="F16" s="20" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C17" s="20" t="s"/>
-      <x:c r="D17" s="20" t="s"/>
-      <x:c r="E17" s="20" t="s"/>
-      <x:c r="F17" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B17" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="22" t="s"/>
+      <x:c r="D17" s="22" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="24" t="n">
+      <x:c r="B18" s="24" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="s"/>
+      <x:c r="D18" s="25" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="n">
+      <x:c r="B20" s="24" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="n">
+      <x:c r="B21" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
+      <x:c r="B22" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C22" s="28" t="s"/>
+      <x:c r="D22" s="28" t="s"/>
+      <x:c r="E22" s="28" t="s"/>
+      <x:c r="F22" s="29" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -6154,7 +6222,7 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
@@ -6202,58 +6270,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45901</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -6296,383 +6364,383 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45915.355787037</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1215901</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45918.2339583333</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45903.3849652778</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45916</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215886</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3150</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45908.2848958333</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>45915.355787037</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1215901</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>45918.2339583333</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45903.3849652778</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45916</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1215886</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>3150</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45908.2848958333</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
+      <x:c r="C10" s="30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>45919.4023032407</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>45926</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1215905</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>45925.945150463</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>45919.4023032407</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45926</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1215905</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="C11" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>45918.1053935185</x:v>
+      </x:c>
+      <x:c r="I11" s="33">
+        <x:v>45900</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1215910</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>45929.2194097222</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>45908.2183449074</x:v>
+      </x:c>
+      <x:c r="I12" s="33">
+        <x:v>45918</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1215894</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45925.945150463</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="L12" s="35">
+        <x:v>45912.1906134259</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>45918.1053935185</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45900</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1215910</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45929.2194097222</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>45908.2183449074</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45918</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1215894</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
+      <x:c r="C13" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>45922.1415393519</x:v>
+      </x:c>
+      <x:c r="I13" s="33">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="n">
+        <x:v>1346550</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45912.1906134259</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>45922.1415393519</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="n">
-        <x:v>1346550</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
+      <x:c r="L13" s="35">
         <x:v>45922.1832523148</x:v>
       </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>19</x:v>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="28" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F14" s="28" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G14" s="28" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H14" s="30">
+      <x:c r="B14" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s"/>
+      <x:c r="E14" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
         <x:v>45919.473287037</x:v>
       </x:c>
-      <x:c r="I14" s="30">
+      <x:c r="I14" s="32">
         <x:v>45919.4732986111</x:v>
       </x:c>
-      <x:c r="J14" s="29" t="n">
+      <x:c r="J14" s="31" t="n">
         <x:v>1215906</x:v>
       </x:c>
-      <x:c r="K14" s="32" t="n">
+      <x:c r="K14" s="34" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L14" s="33">
+      <x:c r="L14" s="35">
         <x:v>45926.2586111111</x:v>
       </x:c>
-      <x:c r="M14" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M14" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="s"/>
-      <x:c r="D17" s="17" t="s"/>
-      <x:c r="E17" s="18" t="s"/>
-      <x:c r="F17" s="18" t="s"/>
+      <x:c r="B17" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="s"/>
+      <x:c r="D17" s="19" t="s"/>
+      <x:c r="E17" s="20" t="s"/>
+      <x:c r="F17" s="20" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="s"/>
-      <x:c r="D18" s="20" t="s"/>
-      <x:c r="E18" s="20" t="s"/>
-      <x:c r="F18" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B18" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C18" s="22" t="s"/>
+      <x:c r="D18" s="22" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="n">
+      <x:c r="B19" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="s"/>
+      <x:c r="D19" s="25" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="n">
+      <x:c r="B20" s="24" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="s"/>
+      <x:c r="D20" s="25" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="n">
+      <x:c r="B21" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C22" s="23" t="s"/>
-      <x:c r="D22" s="23" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="24" t="n">
+      <x:c r="B22" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
+      <x:c r="B23" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7650,7 +7718,7 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
@@ -7698,58 +7766,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45931</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -7792,207 +7860,207 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="C8" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45933.0884375</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>45932</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215922</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45936.014837963</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>35</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="B9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45928.9304513889</x:v>
       </x:c>
-      <x:c r="I9" s="13">
+      <x:c r="I9" s="15">
         <x:v>45928.9304861111</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1215924</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>45938.0359375</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>35</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s"/>
-      <x:c r="E10" s="28" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
+      <x:c r="B10" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s"/>
+      <x:c r="E10" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
         <x:v>45926.4563888889</x:v>
       </x:c>
-      <x:c r="I10" s="30">
+      <x:c r="I10" s="32">
         <x:v>45926.4564351852</x:v>
       </x:c>
-      <x:c r="J10" s="29" t="n">
+      <x:c r="J10" s="31" t="n">
         <x:v>1215917</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="K10" s="34" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L10" s="33">
+      <x:c r="L10" s="35">
         <x:v>45932.239537037</x:v>
       </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s"/>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="18" t="s"/>
-      <x:c r="F13" s="18" t="s"/>
+      <x:c r="B13" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="20" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B14" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8976,7 +9044,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
@@ -9022,58 +9090,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45962</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -9116,553 +9184,553 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>45951.1032638889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45951.103287037</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1346752</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>45971.0888194444</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45980.2160416667</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45979</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346786</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45985.3594791667</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>45965.2736689815</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>45965.2736921296</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1216000</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="35">
+        <x:v>45972.1539583333</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>45965.2661458333</x:v>
+      </x:c>
+      <x:c r="I11" s="33">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="n">
+        <x:v>1215999</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="35">
+        <x:v>45972.1364236111</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>45953.5328240741</x:v>
+      </x:c>
+      <x:c r="I12" s="33">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="n">
+        <x:v>1215970</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="35">
+        <x:v>45966.0458101852</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>45959.0699074074</x:v>
+      </x:c>
+      <x:c r="I13" s="33">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="n">
+        <x:v>1346761</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="35">
+        <x:v>45972.2719560185</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>45958.0724421296</x:v>
+      </x:c>
+      <x:c r="I14" s="33">
+        <x:v>45810</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="n">
+        <x:v>1216003</x:v>
+      </x:c>
+      <x:c r="K14" s="34" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L14" s="35">
+        <x:v>45973.0584490741</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>45973.1309375</x:v>
+      </x:c>
+      <x:c r="I15" s="33">
+        <x:v>45950</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="n">
+        <x:v>1216020</x:v>
+      </x:c>
+      <x:c r="K15" s="34" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L15" s="35">
+        <x:v>45985.2116666667</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="F16" s="30" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H16" s="32">
+        <x:v>45971.2436226852</x:v>
+      </x:c>
+      <x:c r="I16" s="33">
+        <x:v>45608</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="n">
+        <x:v>1216004</x:v>
+      </x:c>
+      <x:c r="K16" s="34" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L16" s="35">
+        <x:v>45973.2287268518</x:v>
+      </x:c>
+      <x:c r="M16" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="D17" s="31" t="s"/>
+      <x:c r="E17" s="30" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I8" s="13">
-        <x:v>45951.103287037</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1346752</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L8" s="13">
-        <x:v>45971.0888194444</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45979</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1346786</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45985.3594791667</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>45965.2736689815</x:v>
-      </x:c>
-      <x:c r="I10" s="30">
-        <x:v>45965.2736921296</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1216000</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45972.1539583333</x:v>
-      </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
-        <x:v>45965.2661458333</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J11" s="29" t="n">
-        <x:v>1215999</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45972.1364236111</x:v>
-      </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="H12" s="30">
-        <x:v>45953.5328240741</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J12" s="29" t="n">
-        <x:v>1215970</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45966.0458101852</x:v>
-      </x:c>
-      <x:c r="M12" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="F13" s="28" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="G13" s="28" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H13" s="30">
-        <x:v>45959.0699074074</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J13" s="29" t="n">
-        <x:v>1346761</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>45972.2719560185</x:v>
-      </x:c>
-      <x:c r="M13" s="28" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D14" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="28" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F14" s="28" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G14" s="28" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H14" s="30">
-        <x:v>45958.0724421296</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>45810</x:v>
-      </x:c>
-      <x:c r="J14" s="29" t="n">
-        <x:v>1216003</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="33">
-        <x:v>45973.0584490741</x:v>
-      </x:c>
-      <x:c r="M14" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="28" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D15" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="28" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F15" s="28" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G15" s="28" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H15" s="30">
-        <x:v>45973.1309375</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>45950</x:v>
-      </x:c>
-      <x:c r="J15" s="29" t="n">
-        <x:v>1216020</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L15" s="33">
-        <x:v>45985.2116666667</x:v>
-      </x:c>
-      <x:c r="M15" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="D16" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="28" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F16" s="28" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G16" s="28" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H16" s="30">
-        <x:v>45971.2436226852</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
-        <x:v>45608</x:v>
-      </x:c>
-      <x:c r="J16" s="29" t="n">
-        <x:v>1216004</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L16" s="33">
-        <x:v>45973.2287268518</x:v>
-      </x:c>
-      <x:c r="M16" s="28" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="28" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F17" s="28" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G17" s="28" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H17" s="30">
+      <x:c r="F17" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
         <x:v>45954.4189930556</x:v>
       </x:c>
-      <x:c r="I17" s="30">
+      <x:c r="I17" s="32">
         <x:v>45954.4190277778</x:v>
       </x:c>
-      <x:c r="J17" s="29" t="n">
+      <x:c r="J17" s="31" t="n">
         <x:v>1215987</x:v>
       </x:c>
-      <x:c r="K17" s="32" t="n">
+      <x:c r="K17" s="34" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L17" s="33">
+      <x:c r="L17" s="35">
         <x:v>45967.2850694444</x:v>
       </x:c>
-      <x:c r="M17" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M17" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="28" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F18" s="28" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G18" s="28" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H18" s="30">
+      <x:c r="B18" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s"/>
+      <x:c r="E18" s="30" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
         <x:v>45959.2592013889</x:v>
       </x:c>
-      <x:c r="I18" s="30">
+      <x:c r="I18" s="32">
         <x:v>45959.259224537</x:v>
       </x:c>
-      <x:c r="J18" s="29" t="n">
+      <x:c r="J18" s="31" t="n">
         <x:v>1216022</x:v>
       </x:c>
-      <x:c r="K18" s="32" t="n">
+      <x:c r="K18" s="34" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L18" s="33">
+      <x:c r="L18" s="35">
         <x:v>45986.1291898148</x:v>
       </x:c>
-      <x:c r="M18" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M18" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C21" s="17" t="s"/>
-      <x:c r="D21" s="17" t="s"/>
-      <x:c r="E21" s="18" t="s"/>
-      <x:c r="F21" s="18" t="s"/>
+      <x:c r="B21" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C21" s="19" t="s"/>
+      <x:c r="D21" s="19" t="s"/>
+      <x:c r="E21" s="20" t="s"/>
+      <x:c r="F21" s="20" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C22" s="20" t="s"/>
-      <x:c r="D22" s="20" t="s"/>
-      <x:c r="E22" s="20" t="s"/>
-      <x:c r="F22" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B22" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="s"/>
+      <x:c r="D22" s="22" t="s"/>
+      <x:c r="E22" s="22" t="s"/>
+      <x:c r="F22" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="22" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C23" s="23" t="s"/>
-      <x:c r="D23" s="23" t="s"/>
-      <x:c r="E23" s="23" t="s"/>
-      <x:c r="F23" s="24" t="n">
+      <x:c r="B23" s="24" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s"/>
-      <x:c r="D24" s="23" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="24" t="n">
+      <x:c r="B24" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="22" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s"/>
-      <x:c r="D25" s="23" t="s"/>
-      <x:c r="E25" s="23" t="s"/>
-      <x:c r="F25" s="24" t="n">
+      <x:c r="B25" s="24" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C26" s="23" t="s"/>
-      <x:c r="D26" s="23" t="s"/>
-      <x:c r="E26" s="23" t="s"/>
-      <x:c r="F26" s="24" t="n">
+      <x:c r="B26" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="24" t="n">
+      <x:c r="B27" s="24" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="24" t="n">
+      <x:c r="B28" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
+      <x:c r="B29" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -10634,7 +10702,7 @@
   <x:mergeCells count="12">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B21:F21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
@@ -10684,58 +10752,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45992</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -10778,238 +10846,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="C8" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45981.1374421296</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216030</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>45996.1054282407</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>35</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45994.1029050926</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>45169</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216035</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>12780</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>46006.2230439815</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>35</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
+      <x:c r="B10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
+      <x:c r="C10" s="30" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
         <x:v>45973.2824074074</x:v>
       </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="I10" s="33">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="29" t="n">
+      <x:c r="J10" s="31" t="n">
         <x:v>1216029</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="K10" s="34" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="33">
+      <x:c r="L10" s="35">
         <x:v>45993.0810763889</x:v>
       </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s">
+      <x:c r="B11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
+      <x:c r="C11" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
         <x:v>45988.1651388889</x:v>
       </x:c>
-      <x:c r="I11" s="31">
+      <x:c r="I11" s="33">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J11" s="29" t="n">
+      <x:c r="J11" s="31" t="n">
         <x:v>1216036</x:v>
       </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="K11" s="34" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="33">
+      <x:c r="L11" s="35">
         <x:v>46006.2389583333</x:v>
       </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M11" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s"/>
-      <x:c r="D14" s="17" t="s"/>
-      <x:c r="E14" s="18" t="s"/>
-      <x:c r="F14" s="18" t="s"/>
+      <x:c r="B14" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="20" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B15" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -11993,7 +12061,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
@@ -12038,58 +12106,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -12132,247 +12200,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="C8" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46033.3509837963</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I8" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216094</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="15">
         <x:v>46049.2368865741</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>35</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
+      <x:c r="C9" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46010.1939351852</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="16">
         <x:v>46029</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216062</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="13">
+      <x:c r="L9" s="15">
         <x:v>46034.111087963</x:v>
       </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>162</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
+      <x:c r="B10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
+      <x:c r="C10" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
         <x:v>45989.0397222222</x:v>
       </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="I10" s="33">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J10" s="29" t="n">
+      <x:c r="J10" s="31" t="n">
         <x:v>1216078</x:v>
       </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="K10" s="34" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L10" s="33">
+      <x:c r="L10" s="35">
         <x:v>46043.2235069444</x:v>
       </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="28" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="s"/>
-      <x:c r="E11" s="28" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F11" s="28" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H11" s="30">
+      <x:c r="B11" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s"/>
+      <x:c r="E11" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
         <x:v>46043.045474537</x:v>
       </x:c>
-      <x:c r="I11" s="30">
+      <x:c r="I11" s="32">
         <x:v>46043.0455092593</x:v>
       </x:c>
-      <x:c r="J11" s="29" t="n">
+      <x:c r="J11" s="31" t="n">
         <x:v>1216091</x:v>
       </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="K11" s="34" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L11" s="33">
+      <x:c r="L11" s="35">
         <x:v>46048.2516435185</x:v>
       </x:c>
-      <x:c r="M11" s="28" t="s">
-        <x:v>35</x:v>
+      <x:c r="M11" s="30" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="s"/>
-      <x:c r="D14" s="17" t="s"/>
-      <x:c r="E14" s="18" t="s"/>
-      <x:c r="F14" s="18" t="s"/>
+      <x:c r="B14" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="20" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B15" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="n">
+      <x:c r="B17" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="B18" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13355,7 +13423,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
@@ -13401,58 +13469,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -13495,211 +13563,211 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="L7" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46058.3038078704</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="n">
+        <x:v>1195989</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46066.3127777778</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46066.3781828704</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>46077.0856712963</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H8" s="13">
-        <x:v>46058.3038078704</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J8" s="12" t="n">
-        <x:v>1195989</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="C10" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46062.2741666667</x:v>
+      </x:c>
+      <x:c r="I10" s="33">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="n">
+        <x:v>1346991</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="13">
-        <x:v>46066.3127777778</x:v>
-      </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>175</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46077.0856712963</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="28" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F10" s="28" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="G10" s="28" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H10" s="30">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J10" s="29" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
+      <x:c r="L10" s="35">
         <x:v>46077.1029513889</x:v>
       </x:c>
-      <x:c r="M10" s="28" t="s">
-        <x:v>19</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="s"/>
-      <x:c r="D13" s="17" t="s"/>
-      <x:c r="E13" s="18" t="s"/>
-      <x:c r="F13" s="18" t="s"/>
+      <x:c r="B13" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="20" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="19" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="21" t="s">
-        <x:v>27</x:v>
+      <x:c r="B14" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -14683,7 +14751,7 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -690,6 +690,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1360-023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3D'S&amp;B CELLPHONE AND ACCESORIES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gumahan, Poblacion, Josefina, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09073370000-0052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1377-766</x:t>
   </x:si>
   <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
@@ -2018,19 +2030,19 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46046.1343634259</x:v>
+        <x:v>46083.2965972222</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>45917</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="J15" s="30" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216198</x:v>
       </x:c>
       <x:c r="K15" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46098.2996296296</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>38</x:v>
@@ -2056,19 +2068,19 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46046.1309027778</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46021</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J16" s="30" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K16" s="32" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46093.273287037</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>38</x:v>
@@ -2079,34 +2091,34 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D17" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E17" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F17" s="29" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G17" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J17" s="30" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>38</x:v>
@@ -2117,7 +2129,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D18" s="30" t="s">
         <x:v>17</x:v>
@@ -2132,19 +2144,19 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46024</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J18" s="30" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>38</x:v>
@@ -2170,19 +2182,19 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J19" s="30" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>38</x:v>
@@ -2208,19 +2220,19 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46076.318900463</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J20" s="30" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>38</x:v>
@@ -2228,13 +2240,13 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B21" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="29" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="C21" s="29" t="s">
-        <x:v>200</x:v>
-      </x:c>
       <x:c r="D21" s="30" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E21" s="29" t="s">
         <x:v>244</x:v>
@@ -2246,19 +2258,19 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46079.2852546296</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46079.2852662037</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J21" s="30" t="n">
-        <x:v>1216195</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>2130</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46097.2459143518</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>38</x:v>
@@ -2266,37 +2278,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D22" s="30" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E22" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46079.2747222222</x:v>
+        <x:v>46079.2852546296</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46079.2747453704</x:v>
+        <x:v>46079.2852662037</x:v>
       </x:c>
       <x:c r="J22" s="30" t="n">
-        <x:v>1216196</x:v>
+        <x:v>1216195</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
         <x:v>2130</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46097.2536342593</x:v>
+        <x:v>46097.2459143518</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>38</x:v>
@@ -2304,12 +2316,14 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="29" t="s">
-        <x:v>22</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C23" s="29" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="D23" s="30" t="s"/>
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="D23" s="30" t="s">
+        <x:v>34</x:v>
+      </x:c>
       <x:c r="E23" s="29" t="s">
         <x:v>251</x:v>
       </x:c>
@@ -2320,19 +2334,19 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46090.2854050926</x:v>
+        <x:v>46079.2747222222</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J23" s="30" t="s">
-        <x:v>253</x:v>
+        <x:v>46079.2747453704</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="n">
+        <x:v>1216196</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
-        <x:v>426</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46097.2536342593</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>38</x:v>
@@ -2356,19 +2370,19 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46090.2540972222</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46090.2541203704</x:v>
-      </x:c>
-      <x:c r="J24" s="30" t="n">
-        <x:v>1216185</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J24" s="30" t="s">
+        <x:v>257</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>38</x:v>
@@ -2383,69 +2397,94 @@
       </x:c>
       <x:c r="D25" s="30" t="s"/>
       <x:c r="E25" s="29" t="s">
-        <x:v>255</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G25" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2540972222</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46090.2349305556</x:v>
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J25" s="30" t="n">
-        <x:v>1216187</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="29" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F26" s="29" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H26" s="31">
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I26" s="31">
+        <x:v>46090.2349305556</x:v>
+      </x:c>
+      <x:c r="J26" s="30" t="n">
+        <x:v>1216187</x:v>
+      </x:c>
+      <x:c r="K26" s="32" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L26" s="33">
+        <x:v>46094.0939351852</x:v>
+      </x:c>
+      <x:c r="M26" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="17" t="s">
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="17" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C28" s="18" t="s"/>
-      <x:c r="D28" s="18" t="s"/>
-      <x:c r="E28" s="19" t="s"/>
-      <x:c r="F28" s="19" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="20" t="s">
+      <x:c r="C29" s="18" t="s"/>
+      <x:c r="D29" s="18" t="s"/>
+      <x:c r="E29" s="19" t="s"/>
+      <x:c r="F29" s="19" t="s"/>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B30" s="20" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C29" s="21" t="s"/>
-      <x:c r="D29" s="21" t="s"/>
-      <x:c r="E29" s="21" t="s"/>
-      <x:c r="F29" s="22" t="s">
+      <x:c r="C30" s="21" t="s"/>
+      <x:c r="D30" s="21" t="s"/>
+      <x:c r="E30" s="21" t="s"/>
+      <x:c r="F30" s="22" t="s">
         <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="23" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C30" s="24" t="s"/>
-      <x:c r="D30" s="24" t="s"/>
-      <x:c r="E30" s="24" t="s"/>
-      <x:c r="F30" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="23" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="24" t="s"/>
       <x:c r="D31" s="24" t="s"/>
@@ -2456,60 +2495,70 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="23" t="s">
-        <x:v>111</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C32" s="24" t="s"/>
       <x:c r="D32" s="24" t="s"/>
       <x:c r="E32" s="24" t="s"/>
       <x:c r="F32" s="25" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="23" t="s">
-        <x:v>15</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C33" s="24" t="s"/>
       <x:c r="D33" s="24" t="s"/>
       <x:c r="E33" s="24" t="s"/>
       <x:c r="F33" s="25" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="23" t="s">
-        <x:v>243</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C34" s="24" t="s"/>
       <x:c r="D34" s="24" t="s"/>
       <x:c r="E34" s="24" t="s"/>
       <x:c r="F34" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="23" t="s">
-        <x:v>22</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C35" s="24" t="s"/>
       <x:c r="D35" s="24" t="s"/>
       <x:c r="E35" s="24" t="s"/>
       <x:c r="F35" s="25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="23" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C36" s="24" t="s"/>
+      <x:c r="D36" s="24" t="s"/>
+      <x:c r="E36" s="24" t="s"/>
+      <x:c r="F36" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B36" s="26" t="s">
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C37" s="27" t="s"/>
+      <x:c r="D37" s="27" t="s"/>
+      <x:c r="E37" s="27" t="s"/>
+      <x:c r="F37" s="28" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3472,8 +3521,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B28:F28"/>
-    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B29:F29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
@@ -3481,6 +3529,7 @@
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -95,6 +95,9 @@
     <x:t>61-7-2025-1070</x:t>
   </x:si>
   <x:si>
+    <x:t>1346409</x:t>
+  </x:si>
+  <x:si>
     <x:t>Neil Jon Angeles</x:t>
   </x:si>
   <x:si>
@@ -113,6 +116,9 @@
     <x:t>61-7-2025-1072</x:t>
   </x:si>
   <x:si>
+    <x:t>1346412</x:t>
+  </x:si>
+  <x:si>
     <x:t>SUMMARY</x:t>
   </x:si>
   <x:si>
@@ -146,6 +152,9 @@
     <x:t>61-7-2025-1086</x:t>
   </x:si>
   <x:si>
+    <x:t>1215849</x:t>
+  </x:si>
+  <x:si>
     <x:t>Catalina EBON</x:t>
   </x:si>
   <x:si>
@@ -164,6 +173,9 @@
     <x:t>61-8-2025-1092</x:t>
   </x:si>
   <x:si>
+    <x:t>1215853</x:t>
+  </x:si>
+  <x:si>
     <x:t>UPSON INTERNATIONAL CORP.</x:t>
   </x:si>
   <x:si>
@@ -176,6 +188,9 @@
     <x:t>61-8-2025-1108</x:t>
   </x:si>
   <x:si>
+    <x:t>1346457</x:t>
+  </x:si>
+  <x:si>
     <x:t>Permit to PURCHASE</x:t>
   </x:si>
   <x:si>
@@ -191,6 +206,9 @@
     <x:t>61-8-2025-1088</x:t>
   </x:si>
   <x:si>
+    <x:t>1195700</x:t>
+  </x:si>
+  <x:si>
     <x:t>Alexander Tomales</x:t>
   </x:si>
   <x:si>
@@ -200,12 +218,18 @@
     <x:t>61-8-2025-1095</x:t>
   </x:si>
   <x:si>
+    <x:t>1215851</x:t>
+  </x:si>
+  <x:si>
     <x:t>MP-ROIX-01007-25</x:t>
   </x:si>
   <x:si>
     <x:t>61-8-2025-1093</x:t>
   </x:si>
   <x:si>
+    <x:t>1215852</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | September 2025</x:t>
   </x:si>
   <x:si>
@@ -221,6 +245,9 @@
     <x:t>61-9-2025-1155</x:t>
   </x:si>
   <x:si>
+    <x:t>1215901</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (MODIFICATION)</x:t>
   </x:si>
   <x:si>
@@ -239,6 +266,9 @@
     <x:t>61-9-2025-1143</x:t>
   </x:si>
   <x:si>
+    <x:t>1215886</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMCOR</x:t>
   </x:si>
   <x:si>
@@ -251,6 +281,9 @@
     <x:t>61-9-2025-1170</x:t>
   </x:si>
   <x:si>
+    <x:t>1215905</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMCOR, INC. SAN MIGUEL BRANCH</x:t>
   </x:si>
   <x:si>
@@ -263,6 +296,9 @@
     <x:t>61-9-2025-1163</x:t>
   </x:si>
   <x:si>
+    <x:t>1215910</x:t>
+  </x:si>
+  <x:si>
     <x:t>MICHAEL’S GADGET SHOP</x:t>
   </x:si>
   <x:si>
@@ -275,6 +311,9 @@
     <x:t>61-9-2025-1147</x:t>
   </x:si>
   <x:si>
+    <x:t>1215894</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBILE MYX GADGETS AND ACCESSORIES CENTER</x:t>
   </x:si>
   <x:si>
@@ -287,6 +326,9 @@
     <x:t>61-9-2025-1172</x:t>
   </x:si>
   <x:si>
+    <x:t>1346550</x:t>
+  </x:si>
+  <x:si>
     <x:t>JENNELYN S. PARACUELES</x:t>
   </x:si>
   <x:si>
@@ -299,6 +341,9 @@
     <x:t>61-9-2025-1171</x:t>
   </x:si>
   <x:si>
+    <x:t>1215906</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | October 2025</x:t>
   </x:si>
   <x:si>
@@ -314,6 +359,9 @@
     <x:t>61-10-2025-1183</x:t>
   </x:si>
   <x:si>
+    <x:t>1215922</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDDIE P. BATONGMALAQUE</x:t>
   </x:si>
   <x:si>
@@ -326,6 +374,9 @@
     <x:t>61-9-2025-1179</x:t>
   </x:si>
   <x:si>
+    <x:t>1215924</x:t>
+  </x:si>
+  <x:si>
     <x:t>JESSIE B. POLANCO</x:t>
   </x:si>
   <x:si>
@@ -338,6 +389,9 @@
     <x:t>61-9-2025-1178</x:t>
   </x:si>
   <x:si>
+    <x:t>1215917</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | November 2025</x:t>
   </x:si>
   <x:si>
@@ -356,6 +410,9 @@
     <x:t>61-10-2025-1198</x:t>
   </x:si>
   <x:si>
+    <x:t>1346752</x:t>
+  </x:si>
+  <x:si>
     <x:t>3 FLR GAISANO MALL SAN PEDRO DISTRICT, Sta. Filomena, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -365,6 +422,9 @@
     <x:t>61-11-2025-1245-086</x:t>
   </x:si>
   <x:si>
+    <x:t>1346786</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -380,6 +440,9 @@
     <x:t>61-11-2025-1222</x:t>
   </x:si>
   <x:si>
+    <x:t>1216000</x:t>
+  </x:si>
+  <x:si>
     <x:t>AB GADGETZ</x:t>
   </x:si>
   <x:si>
@@ -392,6 +455,9 @@
     <x:t>61-11-2025-1221</x:t>
   </x:si>
   <x:si>
+    <x:t>1215999</x:t>
+  </x:si>
+  <x:si>
     <x:t>BUEN GENERAL MERCHANDISE</x:t>
   </x:si>
   <x:si>
@@ -404,6 +470,9 @@
     <x:t>61-10-2025-1205</x:t>
   </x:si>
   <x:si>
+    <x:t>1215970</x:t>
+  </x:si>
+  <x:si>
     <x:t>Makuguihon, Molave, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -413,6 +482,9 @@
     <x:t>61-10-2025-1215</x:t>
   </x:si>
   <x:si>
+    <x:t>1346761</x:t>
+  </x:si>
+  <x:si>
     <x:t>LOURETA RABAY EMBODO</x:t>
   </x:si>
   <x:si>
@@ -425,6 +497,9 @@
     <x:t>61-10-2025-1211</x:t>
   </x:si>
   <x:si>
+    <x:t>1216003</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -440,6 +515,9 @@
     <x:t>61-11-2025-1238</x:t>
   </x:si>
   <x:si>
+    <x:t>1216020</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIX'ST &amp; FIT CELLPHONE AND ACC.</x:t>
   </x:si>
   <x:si>
@@ -452,12 +530,18 @@
     <x:t>61-11-2025-1231</x:t>
   </x:si>
   <x:si>
+    <x:t>1216004</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEMP-ROIX-02490-25</x:t>
   </x:si>
   <x:si>
     <x:t>61-10-2025-1208</x:t>
   </x:si>
   <x:si>
+    <x:t>1215987</x:t>
+  </x:si>
+  <x:si>
     <x:t>MAT ANDREO DE LARA</x:t>
   </x:si>
   <x:si>
@@ -470,6 +554,9 @@
     <x:t>61-10-2025-1216</x:t>
   </x:si>
   <x:si>
+    <x:t>1216022</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | December 2025</x:t>
   </x:si>
   <x:si>
@@ -485,6 +572,9 @@
     <x:t>61-11-2025-1247-533</x:t>
   </x:si>
   <x:si>
+    <x:t>1216030</x:t>
+  </x:si>
+  <x:si>
     <x:t>GS PLUS CELLPHONE AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -497,6 +587,9 @@
     <x:t>61-12-2025-1254-706</x:t>
   </x:si>
   <x:si>
+    <x:t>1216035</x:t>
+  </x:si>
+  <x:si>
     <x:t>NAX MOBILE PHONE AND ACCESSORIES -BRANCH 2</x:t>
   </x:si>
   <x:si>
@@ -509,6 +602,9 @@
     <x:t>61-11-2025-1239</x:t>
   </x:si>
   <x:si>
+    <x:t>1216029</x:t>
+  </x:si>
+  <x:si>
     <x:t>SENTBOX MARKETING</x:t>
   </x:si>
   <x:si>
@@ -521,6 +617,9 @@
     <x:t>61-11-2025-1251-543</x:t>
   </x:si>
   <x:si>
+    <x:t>1216036</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | January 2026</x:t>
   </x:si>
   <x:si>
@@ -533,6 +632,9 @@
     <x:t>61-1-2026-1270-352</x:t>
   </x:si>
   <x:si>
+    <x:t>1216094</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A Purok 5, Poblacion, Bayog, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -542,6 +644,9 @@
     <x:t>61-12-2025-1264-459</x:t>
   </x:si>
   <x:si>
+    <x:t>1216062</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier 9</x:t>
   </x:si>
   <x:si>
@@ -557,6 +662,9 @@
     <x:t>61-11-2025-1253-827</x:t>
   </x:si>
   <x:si>
+    <x:t>1216078</x:t>
+  </x:si>
+  <x:si>
     <x:t>NOEMA BALATUCAL</x:t>
   </x:si>
   <x:si>
@@ -569,6 +677,9 @@
     <x:t>61-1-2026-1283-474</x:t>
   </x:si>
   <x:si>
+    <x:t>1216091</x:t>
+  </x:si>
+  <x:si>
     <x:t>IX | February 2026</x:t>
   </x:si>
   <x:si>
@@ -584,6 +695,9 @@
     <x:t>61-2-2026-1313-983</x:t>
   </x:si>
   <x:si>
+    <x:t>1195989</x:t>
+  </x:si>
+  <x:si>
     <x:t>Fortunata Postigo</x:t>
   </x:si>
   <x:si>
@@ -596,6 +710,9 @@
     <x:t>61-2-2026-1330-585</x:t>
   </x:si>
   <x:si>
+    <x:t>1346991</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cyberzone, SM City Mindpro La Purisima, Zone III, Zamboanga City, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -620,6 +737,9 @@
     <x:t>61-3-2026-1384-689</x:t>
   </x:si>
   <x:si>
+    <x:t>1216179</x:t>
+  </x:si>
+  <x:si>
     <x:t>DES APPLIANCE PLAZA INC</x:t>
   </x:si>
   <x:si>
@@ -632,6 +752,9 @@
     <x:t>61-2-2026-1366-828</x:t>
   </x:si>
   <x:si>
+    <x:t>1217027</x:t>
+  </x:si>
+  <x:si>
     <x:t>COMPRO COMPUTER SHOP</x:t>
   </x:si>
   <x:si>
@@ -644,6 +767,9 @@
     <x:t>61-2-2026-1358-112</x:t>
   </x:si>
   <x:si>
+    <x:t>1216194</x:t>
+  </x:si>
+  <x:si>
     <x:t>HIGH-SPEED MOTORCYCLE PARTS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -656,6 +782,9 @@
     <x:t>61-2-2026-1355-880</x:t>
   </x:si>
   <x:si>
+    <x:t>1216190</x:t>
+  </x:si>
+  <x:si>
     <x:t>PCCP COMPUTER REPAIR SERVICES</x:t>
   </x:si>
   <x:si>
@@ -668,6 +797,9 @@
     <x:t>61-2-2026-1356-022</x:t>
   </x:si>
   <x:si>
+    <x:t>1216197</x:t>
+  </x:si>
+  <x:si>
     <x:t>PEARL'S ONLINE SHOP</x:t>
   </x:si>
   <x:si>
@@ -680,6 +812,9 @@
     <x:t>61-2-2026-1357-656</x:t>
   </x:si>
   <x:si>
+    <x:t>1216188</x:t>
+  </x:si>
+  <x:si>
     <x:t>SLIM BX ELECTRONICS AND TELECOMMUNICATION PARTS AND EQUIPMENT RETAILING</x:t>
   </x:si>
   <x:si>
@@ -692,6 +827,9 @@
     <x:t>61-2-2026-1360-023</x:t>
   </x:si>
   <x:si>
+    <x:t>1216189</x:t>
+  </x:si>
+  <x:si>
     <x:t>3D'S&amp;B CELLPHONE AND ACCESORIES</x:t>
   </x:si>
   <x:si>
@@ -704,6 +842,9 @@
     <x:t>61-3-2026-1377-766</x:t>
   </x:si>
   <x:si>
+    <x:t>1216198</x:t>
+  </x:si>
+  <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -716,6 +857,9 @@
     <x:t>61-1-2026-1294-762</x:t>
   </x:si>
   <x:si>
+    <x:t>1216183</x:t>
+  </x:si>
+  <x:si>
     <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
   </x:si>
   <x:si>
@@ -728,6 +872,9 @@
     <x:t>61-1-2026-1293-860</x:t>
   </x:si>
   <x:si>
+    <x:t>1216181</x:t>
+  </x:si>
+  <x:si>
     <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -737,6 +884,9 @@
     <x:t>61-1-2026-1292-941</x:t>
   </x:si>
   <x:si>
+    <x:t>1216180</x:t>
+  </x:si>
+  <x:si>
     <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -749,6 +899,9 @@
     <x:t>61-1-2026-1289-791</x:t>
   </x:si>
   <x:si>
+    <x:t>1216182</x:t>
+  </x:si>
+  <x:si>
     <x:t>AB-GADGETZ CELLPHONE STORE</x:t>
   </x:si>
   <x:si>
@@ -761,6 +914,9 @@
     <x:t>61-1-2026-1295-381</x:t>
   </x:si>
   <x:si>
+    <x:t>1216184</x:t>
+  </x:si>
+  <x:si>
     <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
   </x:si>
   <x:si>
@@ -773,6 +929,9 @@
     <x:t>61-2-2026-1359-531</x:t>
   </x:si>
   <x:si>
+    <x:t>1216168</x:t>
+  </x:si>
+  <x:si>
     <x:t>Service Center Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -785,6 +944,9 @@
     <x:t>61-2-2026-1374-436</x:t>
   </x:si>
   <x:si>
+    <x:t>1216195</x:t>
+  </x:si>
+  <x:si>
     <x:t>SABADO ST., SAN FRANCISCO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -794,6 +956,9 @@
     <x:t>61-2-2026-1373-524</x:t>
   </x:si>
   <x:si>
+    <x:t>1216196</x:t>
+  </x:si>
+  <x:si>
     <x:t>AILYN G. PANIS</x:t>
   </x:si>
   <x:si>
@@ -818,6 +983,9 @@
     <x:t>61-3-2026-1388-689</x:t>
   </x:si>
   <x:si>
+    <x:t>1216185</x:t>
+  </x:si>
+  <x:si>
     <x:t>JORELYN P. SOLES</x:t>
   </x:si>
   <x:si>
@@ -825,6 +993,9 @@
   </x:si>
   <x:si>
     <x:t>61-3-2026-1387-457</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216187</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -836,7 +1007,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -905,7 +1076,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -920,13 +1091,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -1163,7 +1327,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1222,13 +1386,10 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1240,14 +1401,8 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1295,6 +1450,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1304,6 +1463,10 @@
     </x:xf>
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1330,15 +1493,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1352,26 +1515,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -1670,7 +1813,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>191</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -1746,816 +1889,816 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>193</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>194</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46088.1798263889</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46088.179837963</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216179</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46088.1798280556</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46088.1798485995</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46093.2393865741</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46093.2393924884</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>197</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46077.2833680556</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46077.2833774074</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1217027</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46094.1366782407</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46094.1366842014</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>46076.2809953704</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>46076.2810185185</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1216194</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="B10" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46076.2810036343</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46076.2810195833</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46097.2411111111</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46097.2411206366</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>46076.245</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46076.2450115741</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1216190</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="B11" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46076.2450058565</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46076.2450229514</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46094.1710416667</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46094.1710418981</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>46076.2578009259</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>46076.2578240741</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1216197</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
+      <x:c r="B12" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46076.2578122338</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46076.2578276505</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="33">
-        <x:v>46097.2583912037</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L12" s="18">
+        <x:v>46097.2583940162</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>46076.2633564815</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>46076.2633680556</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1216188</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
+      <x:c r="B13" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46076.263358912</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46076.2633790625</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L13" s="33">
-        <x:v>46094.1562731481</x:v>
-      </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L13" s="18">
+        <x:v>46094.1562770949</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="29" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="D14" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="F14" s="29" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="G14" s="29" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="H14" s="31">
-        <x:v>46076.3755324074</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>46076.3755439815</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="n">
-        <x:v>1216189</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
+      <x:c r="B14" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46076.3755334722</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46076.3755506134</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="33">
-        <x:v>46094.1653935185</x:v>
-      </x:c>
-      <x:c r="M14" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L14" s="18">
+        <x:v>46094.1653946759</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="29" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="D15" s="30" t="s">
+      <x:c r="C15" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E15" s="29" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F15" s="29" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="G15" s="29" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="H15" s="31">
-        <x:v>46083.2965972222</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
+      <x:c r="E15" s="14" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46083.2966067014</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
         <x:v>46387</x:v>
       </x:c>
-      <x:c r="J15" s="30" t="n">
-        <x:v>1216198</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
+      <x:c r="J15" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L15" s="33">
-        <x:v>46098.2996296296</x:v>
-      </x:c>
-      <x:c r="M15" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L15" s="18">
+        <x:v>46098.2996351505</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="29" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="D16" s="30" t="s">
+      <x:c r="C16" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E16" s="29" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="F16" s="29" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="G16" s="29" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="H16" s="31">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
+      <x:c r="E16" s="14" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46046.1343687731</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
         <x:v>45917</x:v>
       </x:c>
-      <x:c r="J16" s="30" t="n">
-        <x:v>1216183</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
+      <x:c r="J16" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L16" s="33">
-        <x:v>46093.2878703704</x:v>
-      </x:c>
-      <x:c r="M16" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L16" s="18">
+        <x:v>46093.2878737037</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C17" s="29" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D17" s="30" t="s">
+      <x:c r="C17" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E17" s="29" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="F17" s="29" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G17" s="29" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H17" s="31">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I17" s="31">
+      <x:c r="E17" s="14" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46046.1309132176</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
         <x:v>46021</x:v>
       </x:c>
-      <x:c r="J17" s="30" t="n">
-        <x:v>1216181</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
+      <x:c r="J17" s="15" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L17" s="33">
-        <x:v>46093.273287037</x:v>
-      </x:c>
-      <x:c r="M17" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L17" s="18">
+        <x:v>46093.2732890162</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="D18" s="30" t="s">
+      <x:c r="C18" s="14" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E18" s="29" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F18" s="29" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G18" s="29" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H18" s="31">
-        <x:v>46046.1237615741</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
+      <x:c r="E18" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46046.1237709144</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J18" s="30" t="n">
-        <x:v>1216180</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
+      <x:c r="J18" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L18" s="33">
-        <x:v>46093.2636342593</x:v>
-      </x:c>
-      <x:c r="M18" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L18" s="18">
+        <x:v>46093.2636364931</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" s="29" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="D19" s="30" t="s">
+      <x:c r="C19" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E19" s="29" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="F19" s="29" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G19" s="29" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="H19" s="31">
-        <x:v>46046.1140856482</x:v>
-      </x:c>
-      <x:c r="I19" s="31">
+      <x:c r="E19" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46046.1140924306</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J19" s="30" t="n">
-        <x:v>1216182</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
+      <x:c r="J19" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L19" s="33">
-        <x:v>46093.2825231481</x:v>
-      </x:c>
-      <x:c r="M19" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L19" s="18">
+        <x:v>46093.2825289005</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="29" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D20" s="30" t="s">
+      <x:c r="C20" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E20" s="29" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F20" s="29" t="s">
+      <x:c r="E20" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46048.0974875347</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46093.2926065278</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46076.3189094676</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46092.1400343403</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G20" s="29" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H20" s="31">
-        <x:v>46048.0974768518</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J20" s="30" t="n">
-        <x:v>1216184</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L20" s="33">
-        <x:v>46093.2926041667</x:v>
-      </x:c>
-      <x:c r="M20" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="D21" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="29" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F21" s="29" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G21" s="29" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H21" s="31">
-        <x:v>46076.318900463</x:v>
-      </x:c>
-      <x:c r="I21" s="31">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J21" s="30" t="n">
-        <x:v>1216168</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L21" s="33">
-        <x:v>46092.1400231481</x:v>
-      </x:c>
-      <x:c r="M21" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="29" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D22" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E22" s="29" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="F22" s="29" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="G22" s="29" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H22" s="31">
-        <x:v>46079.2852546296</x:v>
-      </x:c>
-      <x:c r="I22" s="31">
-        <x:v>46079.2852662037</x:v>
-      </x:c>
-      <x:c r="J22" s="30" t="n">
-        <x:v>1216195</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
+      <x:c r="D22" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46079.2852568981</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46079.2852718981</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L22" s="33">
-        <x:v>46097.2459143518</x:v>
-      </x:c>
-      <x:c r="M22" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L22" s="18">
+        <x:v>46097.2459243171</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="29" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="D23" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E23" s="29" t="s">
+      <x:c r="B23" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="F23" s="29" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="G23" s="29" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="H23" s="31">
-        <x:v>46079.2747222222</x:v>
-      </x:c>
-      <x:c r="I23" s="31">
-        <x:v>46079.2747453704</x:v>
-      </x:c>
-      <x:c r="J23" s="30" t="n">
-        <x:v>1216196</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
+      <x:c r="D23" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46079.2747337153</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46079.2747495718</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L23" s="33">
-        <x:v>46097.2536342593</x:v>
-      </x:c>
-      <x:c r="M23" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L23" s="18">
+        <x:v>46097.2536368518</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C24" s="29" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="29" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F24" s="29" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G24" s="29" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H24" s="31">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I24" s="31">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J24" s="30" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
+      <x:c r="B24" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s"/>
+      <x:c r="E24" s="14" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46090.2854096643</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46090.2854287153</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L24" s="33">
-        <x:v>46094.0865740741</x:v>
-      </x:c>
-      <x:c r="M24" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L24" s="18">
+        <x:v>46094.0865837153</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C25" s="29" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="29" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F25" s="29" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G25" s="29" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H25" s="31">
-        <x:v>46090.2540972222</x:v>
-      </x:c>
-      <x:c r="I25" s="31">
-        <x:v>46090.2541203704</x:v>
-      </x:c>
-      <x:c r="J25" s="30" t="n">
-        <x:v>1216185</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
+      <x:c r="B25" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s"/>
+      <x:c r="E25" s="14" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46090.2541037731</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46090.2541222106</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L25" s="33">
-        <x:v>46094.0818981481</x:v>
-      </x:c>
-      <x:c r="M25" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L25" s="18">
+        <x:v>46094.0819034491</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C26" s="29" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="29" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F26" s="29" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G26" s="29" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H26" s="31">
-        <x:v>46090.2349189815</x:v>
-      </x:c>
-      <x:c r="I26" s="31">
-        <x:v>46090.2349305556</x:v>
-      </x:c>
-      <x:c r="J26" s="30" t="n">
-        <x:v>1216187</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
+      <x:c r="B26" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s"/>
+      <x:c r="E26" s="14" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46090.2349194444</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46090.2349374884</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L26" s="33">
-        <x:v>46094.0939351852</x:v>
-      </x:c>
-      <x:c r="M26" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L26" s="18">
+        <x:v>46094.093939213</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C29" s="18" t="s"/>
-      <x:c r="D29" s="18" t="s"/>
-      <x:c r="E29" s="19" t="s"/>
-      <x:c r="F29" s="19" t="s"/>
+      <x:c r="B29" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="s"/>
+      <x:c r="D29" s="20" t="s"/>
+      <x:c r="E29" s="21" t="s"/>
+      <x:c r="F29" s="21" t="s"/>
     </x:row>
     <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C30" s="21" t="s"/>
-      <x:c r="D30" s="21" t="s"/>
-      <x:c r="E30" s="21" t="s"/>
-      <x:c r="F30" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B30" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C30" s="23" t="s"/>
+      <x:c r="D30" s="23" t="s"/>
+      <x:c r="E30" s="23" t="s"/>
+      <x:c r="F30" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="23" t="s">
+      <x:c r="B31" s="25" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="25" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="25" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="25" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="28" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C31" s="24" t="s"/>
-      <x:c r="D31" s="24" t="s"/>
-      <x:c r="E31" s="24" t="s"/>
-      <x:c r="F31" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C32" s="24" t="s"/>
-      <x:c r="D32" s="24" t="s"/>
-      <x:c r="E32" s="24" t="s"/>
-      <x:c r="F32" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="23" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C33" s="24" t="s"/>
-      <x:c r="D33" s="24" t="s"/>
-      <x:c r="E33" s="24" t="s"/>
-      <x:c r="F33" s="25" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C34" s="24" t="s"/>
-      <x:c r="D34" s="24" t="s"/>
-      <x:c r="E34" s="24" t="s"/>
-      <x:c r="F34" s="25" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="23" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="C35" s="24" t="s"/>
-      <x:c r="D35" s="24" t="s"/>
-      <x:c r="E35" s="24" t="s"/>
-      <x:c r="F35" s="25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C36" s="24" t="s"/>
-      <x:c r="D36" s="24" t="s"/>
-      <x:c r="E36" s="24" t="s"/>
-      <x:c r="F36" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C37" s="27" t="s"/>
-      <x:c r="D37" s="27" t="s"/>
-      <x:c r="E37" s="27" t="s"/>
-      <x:c r="F37" s="28" t="n">
+      <x:c r="C37" s="29" t="s"/>
+      <x:c r="D37" s="29" t="s"/>
+      <x:c r="E37" s="29" t="s"/>
+      <x:c r="F37" s="30" t="n">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -3722,7 +3865,7 @@
       <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
@@ -3734,113 +3877,113 @@
       <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45860.0993981482</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="H8" s="16">
+        <x:v>45860.0994011343</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346409</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45860.1449537037</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45860.1449620718</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45861.1130539236</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45861.113062963</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45862.3035735301</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45861.1130439815</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45861.1130555556</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346412</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>930</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45862.3035648148</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
+      <x:c r="B12" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B13" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="B16" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -4943,7 +5086,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -5019,304 +5162,304 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45866.2802893519</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45866.2803009259</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215849</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45866.2802922106</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45866.2803013889</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45873.1184143519</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45873.1184145139</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45875.2238915046</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L9" s="18">
+        <x:v>45876.2433041204</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45880.121483588</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>45881.1619025579</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45873.2195533449</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45873.2195624074</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>45882.1150772338</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45875.2238888889</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="D12" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45875.3617282407</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215853</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45876.2432986111</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="J12" s="15" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45876.2230995023</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45880.1214814815</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1346457</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45881.1618981482</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D11" s="30" t="s"/>
-      <x:c r="E11" s="29" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>45873.2195486111</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45873.2195601852</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1195700</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>2790</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45882.1150694444</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
+      <x:c r="F13" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45875.2324767593</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>45876.2319890162</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>45875.361724537</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1215851</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45876.2230902778</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>45875.2324652778</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1215852</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>45876.2319791667</x:v>
-      </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="18" t="s"/>
-      <x:c r="D16" s="18" t="s"/>
-      <x:c r="E16" s="19" t="s"/>
-      <x:c r="F16" s="19" t="s"/>
+      <x:c r="B16" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="21" t="s"/>
-      <x:c r="F17" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B17" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="23" t="s">
+      <x:c r="B18" s="25" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="25" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="28" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -6415,7 +6558,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -6491,342 +6634,342 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45915.355787037</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45915.3557896528</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215901</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45918.2339583333</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45918.2339584606</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45903.3849652778</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45903.3849758912</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45916</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215886</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>3150</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45908.2848958333</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45908.2848985301</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45919.4023032407</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="E10" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45919.4023076505</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1215905</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45925.945150463</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45925.9451511111</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="29" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="29" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D11" s="30" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="29" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>45918.1053935185</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
+      <x:c r="E11" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45918.1054021528</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45900</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1215910</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45929.2194097222</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L11" s="18">
+        <x:v>45929.2194160764</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="29" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
+      <x:c r="C12" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>45908.2183449074</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
+      <x:c r="E12" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45908.2183496296</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
         <x:v>45918</x:v>
       </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1215894</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
+      <x:c r="J12" s="15" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45912.1906134259</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L12" s="18">
+        <x:v>45912.190615463</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="29" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C13" s="29" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D13" s="30" t="s">
+      <x:c r="C13" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E13" s="29" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>45922.1415393519</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
+      <x:c r="E13" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45922.1415441088</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1346550</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
+      <x:c r="J13" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="33">
-        <x:v>45922.1832523148</x:v>
-      </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>21</x:v>
+      <x:c r="L13" s="18">
+        <x:v>45922.1832596412</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="29" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F14" s="29" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G14" s="29" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H14" s="31">
-        <x:v>45919.473287037</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>45919.4732986111</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="n">
-        <x:v>1215906</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
+      <x:c r="B14" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45919.4732912847</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45919.4733016088</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L14" s="33">
-        <x:v>45926.2586111111</x:v>
-      </x:c>
-      <x:c r="M14" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L14" s="18">
+        <x:v>45926.2586175694</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="s"/>
-      <x:c r="D17" s="18" t="s"/>
-      <x:c r="E17" s="19" t="s"/>
-      <x:c r="F17" s="19" t="s"/>
+      <x:c r="B17" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="s"/>
+      <x:c r="D17" s="20" t="s"/>
+      <x:c r="E17" s="21" t="s"/>
+      <x:c r="F17" s="21" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="21" t="s"/>
-      <x:c r="F18" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B18" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="n">
+      <x:c r="B19" s="25" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="n">
+      <x:c r="B20" s="25" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="23" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C22" s="24" t="s"/>
-      <x:c r="D22" s="24" t="s"/>
-      <x:c r="E22" s="24" t="s"/>
-      <x:c r="F22" s="25" t="n">
+      <x:c r="B22" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="B23" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7924,7 +8067,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -8003,163 +8146,163 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45933.0884375</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45933.0884397222</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45932</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1215922</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45936.014837963</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45936.0148412269</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s"/>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s"/>
       <x:c r="E9" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45928.9304513889</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>45928.9304861111</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1215924</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45928.9304539583</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>45928.9304922454</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45938.0359375</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45938.035947419</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s"/>
-      <x:c r="E10" s="29" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45926.4563888889</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45926.4564351852</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1215917</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="B10" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45926.4563998264</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45926.4564372454</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45932.239537037</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45932.2395375463</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="B13" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B14" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="B16" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -9261,7 +9404,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>102</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -9337,512 +9480,512 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>103</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
       <x:c r="E8" s="14" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45951.1032638889</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>45951.103287037</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1346752</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45951.1032693866</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>45951.1032970718</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45971.0888194444</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45971.088825787</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>109</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45980.2160416667</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45980.216052338</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346786</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>45985.3594791667</x:v>
+      <x:c r="L9" s="18">
+        <x:v>45985.3594797917</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
+      <x:c r="B10" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45965.2736735764</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>45965.2736975579</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="18">
+        <x:v>45972.1539687153</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45965.2661516088</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>45972.1364239815</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45953.5328279861</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45966.0458205787</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45959.0699130787</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>45972.2719636111</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45958.0724435648</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45810</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>45973.0584535069</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45973.1309431481</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>45950</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>45985.2116720486</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>45971.2436290394</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>45608</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>45973.2287349769</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45965.2736689815</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
-        <x:v>45965.2736921296</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1216000</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45972.1539583333</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="D17" s="15" t="s"/>
+      <x:c r="E17" s="14" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="29" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>45965.2661458333</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1215999</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="33">
-        <x:v>45972.1364236111</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="29" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D12" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="29" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F12" s="29" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="G12" s="29" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H12" s="31">
-        <x:v>45953.5328240741</x:v>
-      </x:c>
-      <x:c r="I12" s="31">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="n">
-        <x:v>1215970</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="33">
-        <x:v>45966.0458101852</x:v>
-      </x:c>
-      <x:c r="M12" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="F13" s="29" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G13" s="29" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H13" s="31">
-        <x:v>45959.0699074074</x:v>
-      </x:c>
-      <x:c r="I13" s="31">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J13" s="30" t="n">
-        <x:v>1346761</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="33">
-        <x:v>45972.2719560185</x:v>
-      </x:c>
-      <x:c r="M13" s="29" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="29" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="29" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D14" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="29" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F14" s="29" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G14" s="29" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H14" s="31">
-        <x:v>45958.0724421296</x:v>
-      </x:c>
-      <x:c r="I14" s="31">
-        <x:v>45810</x:v>
-      </x:c>
-      <x:c r="J14" s="30" t="n">
-        <x:v>1216003</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="33">
-        <x:v>45973.0584490741</x:v>
-      </x:c>
-      <x:c r="M14" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="29" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C15" s="29" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D15" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="29" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F15" s="29" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G15" s="29" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H15" s="31">
-        <x:v>45973.1309375</x:v>
-      </x:c>
-      <x:c r="I15" s="31">
-        <x:v>45950</x:v>
-      </x:c>
-      <x:c r="J15" s="30" t="n">
-        <x:v>1216020</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L15" s="33">
-        <x:v>45985.2116666667</x:v>
-      </x:c>
-      <x:c r="M15" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D16" s="30" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="29" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F16" s="29" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G16" s="29" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H16" s="31">
-        <x:v>45971.2436226852</x:v>
-      </x:c>
-      <x:c r="I16" s="31">
-        <x:v>45608</x:v>
-      </x:c>
-      <x:c r="J16" s="30" t="n">
-        <x:v>1216004</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L16" s="33">
-        <x:v>45973.2287268518</x:v>
-      </x:c>
-      <x:c r="M16" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="29" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="F17" s="29" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="G17" s="29" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="H17" s="31">
-        <x:v>45954.4189930556</x:v>
-      </x:c>
-      <x:c r="I17" s="31">
-        <x:v>45954.4190277778</x:v>
-      </x:c>
-      <x:c r="J17" s="30" t="n">
-        <x:v>1215987</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
+      <x:c r="F17" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>45954.4190024884</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>45954.4190340741</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L17" s="33">
-        <x:v>45967.2850694444</x:v>
-      </x:c>
-      <x:c r="M17" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L17" s="18">
+        <x:v>45967.2850746528</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="29" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F18" s="29" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G18" s="29" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H18" s="31">
-        <x:v>45959.2592013889</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>45959.259224537</x:v>
-      </x:c>
-      <x:c r="J18" s="30" t="n">
-        <x:v>1216022</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
+      <x:c r="B18" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
+      <x:c r="E18" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>45959.2592067593</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>45959.2592354861</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L18" s="33">
-        <x:v>45986.1291898148</x:v>
-      </x:c>
-      <x:c r="M18" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L18" s="18">
+        <x:v>45986.1291977315</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C21" s="18" t="s"/>
-      <x:c r="D21" s="18" t="s"/>
-      <x:c r="E21" s="19" t="s"/>
-      <x:c r="F21" s="19" t="s"/>
+      <x:c r="B21" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C22" s="21" t="s"/>
-      <x:c r="D22" s="21" t="s"/>
-      <x:c r="E22" s="21" t="s"/>
-      <x:c r="F22" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B22" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C23" s="24" t="s"/>
-      <x:c r="D23" s="24" t="s"/>
-      <x:c r="E23" s="24" t="s"/>
-      <x:c r="F23" s="25" t="n">
+      <x:c r="B23" s="25" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C24" s="24" t="s"/>
-      <x:c r="D24" s="24" t="s"/>
-      <x:c r="E24" s="24" t="s"/>
-      <x:c r="F24" s="25" t="n">
+      <x:c r="B24" s="25" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="23" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C25" s="24" t="s"/>
-      <x:c r="D25" s="24" t="s"/>
-      <x:c r="E25" s="24" t="s"/>
-      <x:c r="F25" s="25" t="n">
+      <x:c r="B25" s="25" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="23" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C26" s="24" t="s"/>
-      <x:c r="D26" s="24" t="s"/>
-      <x:c r="E26" s="24" t="s"/>
-      <x:c r="F26" s="25" t="n">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="23" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C27" s="24" t="s"/>
-      <x:c r="D27" s="24" t="s"/>
-      <x:c r="E27" s="24" t="s"/>
-      <x:c r="F27" s="25" t="n">
+      <x:c r="B27" s="25" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C28" s="24" t="s"/>
-      <x:c r="D28" s="24" t="s"/>
-      <x:c r="E28" s="24" t="s"/>
-      <x:c r="F28" s="25" t="n">
+      <x:c r="B28" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="B29" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C29" s="29" t="s"/>
+      <x:c r="D29" s="29" t="s"/>
+      <x:c r="E29" s="29" t="s"/>
+      <x:c r="F29" s="30" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -10936,7 +11079,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>146</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -11015,37 +11158,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>148</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>149</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>45981.1374421296</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>45981.1374423611</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216030</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>45996.1054282407</x:v>
+      <x:c r="L8" s="18">
+        <x:v>45996.1054321181</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -11053,156 +11196,156 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>153</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>45994.1029050926</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>45994.1029113889</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>45169</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216035</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>12780</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46006.2230439815</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46006.2230459028</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45973.2824074074</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="E10" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45973.282415625</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1216029</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>45993.0810763889</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L10" s="18">
+        <x:v>45993.0810788889</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="29" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="29" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D11" s="30" t="s">
+      <x:c r="C11" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="29" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>45988.1651388889</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
+      <x:c r="E11" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45988.1651420255</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1216036</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="J11" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46006.2389583333</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46006.238966169</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="s"/>
-      <x:c r="D14" s="18" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="19" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12303,7 +12446,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>163</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -12382,37 +12525,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>164</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>165</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46033.3509837963</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46033.3509841319</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1216094</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46049.2368865741</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46049.2368941319</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -12420,165 +12563,165 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>167</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>168</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46010.1939351852</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46010.1939375579</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46029</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1216062</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46034.111087963</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46034.111096713</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>170</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="C10" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>45989.0397222222</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="E10" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45989.0397289236</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1216078</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46043.2235069444</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46043.2235160301</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="29" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="29" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D11" s="30" t="s"/>
-      <x:c r="E11" s="29" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
-        <x:v>46043.045474537</x:v>
-      </x:c>
-      <x:c r="I11" s="31">
-        <x:v>46043.0455092593</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="n">
-        <x:v>1216091</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="B11" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46043.0454792477</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46043.0455093056</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L11" s="33">
-        <x:v>46048.2516435185</x:v>
-      </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>38</x:v>
+      <x:c r="L11" s="18">
+        <x:v>46048.2516543634</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="s"/>
-      <x:c r="D14" s="18" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="19" t="s"/>
+      <x:c r="B14" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B15" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="n">
+      <x:c r="B17" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="B18" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -13679,7 +13822,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>179</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -13755,170 +13898,170 @@
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
-        <x:v>181</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F8" s="14" t="s">
-        <x:v>182</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G8" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46058.3038078704</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46058.3038087847</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
-        <x:v>1195989</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J8" s="15" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46066.3127777778</x:v>
+      <x:c r="L8" s="18">
+        <x:v>46066.3127838657</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
-        <x:v>184</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>185</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>186</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46066.3781828704</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46066.3781940972</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="J9" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="15">
-        <x:v>46077.0856712963</x:v>
+      <x:c r="L9" s="18">
+        <x:v>46077.0856746296</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="29" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
-        <x:v>46062.2741666667</x:v>
-      </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="E10" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46062.2741739236</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="n">
-        <x:v>1346991</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="15" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="33">
-        <x:v>46077.1029513889</x:v>
-      </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>21</x:v>
+      <x:c r="L10" s="18">
+        <x:v>46077.1029543634</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="B13" s="19" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
-        <x:v>29</x:v>
+      <x:c r="B14" s="22" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="B15" s="25" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -755,6 +755,21 @@
     <x:t>1217027</x:t>
   </x:si>
   <x:si>
+    <x:t>PMC EXPRESS HUB INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit no. 227, Robinson Pagadian Mall, F.S. Pajares Ave., Cor. P.L. Urro St., Cor Vincenzo, Sagun St.,, San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-II0618A-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1391-148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216201</x:t>
+  </x:si>
+  <x:si>
     <x:t>COMPRO COMPUTER SHOP</x:t>
   </x:si>
   <x:si>
@@ -863,6 +878,18 @@
     <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
   </x:si>
   <x:si>
+    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110615E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1292-941</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216180</x:t>
+  </x:si>
+  <x:si>
     <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -873,18 +900,6 @@
   </x:si>
   <x:si>
     <x:t>1216181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRR-110615E-22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1292-941</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216180</x:t>
   </x:si>
   <x:si>
     <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
@@ -1965,13 +1980,13 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
         <x:v>241</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
         <x:v>242</x:v>
@@ -1983,19 +1998,19 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46076.2810036343</x:v>
+        <x:v>46091.1989145023</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46076.2810195833</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>245</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>4030</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46097.2411206366</x:v>
+        <x:v>46106.1492534144</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>41</x:v>
@@ -2021,10 +2036,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46076.2450058565</x:v>
+        <x:v>46076.2810036343</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46076.2450229514</x:v>
+        <x:v>46076.2810195833</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>250</x:v>
@@ -2033,7 +2048,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46094.1710418981</x:v>
+        <x:v>46097.2411206366</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>41</x:v>
@@ -2059,10 +2074,10 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46076.2578122338</x:v>
+        <x:v>46076.2450058565</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46076.2578276505</x:v>
+        <x:v>46076.2450229514</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>255</x:v>
@@ -2071,7 +2086,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46097.2583940162</x:v>
+        <x:v>46094.1710418981</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>41</x:v>
@@ -2097,19 +2112,19 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46076.263358912</x:v>
+        <x:v>46076.2578122338</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46076.2633790625</x:v>
+        <x:v>46076.2578276505</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>260</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>4530</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46094.1562770949</x:v>
+        <x:v>46097.2583940162</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>41</x:v>
@@ -2135,19 +2150,19 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46076.3755334722</x:v>
+        <x:v>46076.263358912</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46076.3755506134</x:v>
+        <x:v>46076.2633790625</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>265</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46094.1653946759</x:v>
+        <x:v>46094.1562770949</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>41</x:v>
@@ -2155,13 +2170,13 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
         <x:v>266</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
         <x:v>267</x:v>
@@ -2173,19 +2188,19 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46083.2966067014</x:v>
+        <x:v>46076.3755334722</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46387</x:v>
+        <x:v>46076.3755506134</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>270</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46098.2996351505</x:v>
+        <x:v>46094.1653946759</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>41</x:v>
@@ -2211,10 +2226,10 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46046.1343687731</x:v>
+        <x:v>46083.2966067014</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>45917</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>275</x:v>
@@ -2223,7 +2238,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46093.2878737037</x:v>
+        <x:v>46098.2996351505</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>41</x:v>
@@ -2249,19 +2264,19 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46046.1309132176</x:v>
+        <x:v>46046.1343687731</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46021</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>280</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46093.2732890162</x:v>
+        <x:v>46093.2878737037</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>41</x:v>
@@ -2272,19 +2287,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>276</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="H18" s="16">
         <x:v>46046.1237709144</x:v>
@@ -2293,7 +2308,7 @@
         <x:v>45991</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3780</x:v>
@@ -2310,7 +2325,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>285</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>17</x:v>
@@ -2325,19 +2340,19 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46046.1140924306</x:v>
+        <x:v>46046.1309132176</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46024</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
         <x:v>289</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46093.2825289005</x:v>
+        <x:v>46093.2732890162</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>41</x:v>
@@ -2363,10 +2378,10 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46048.0974875347</x:v>
+        <x:v>46046.1140924306</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>294</x:v>
@@ -2375,7 +2390,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46093.2926065278</x:v>
+        <x:v>46093.2825289005</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>41</x:v>
@@ -2401,10 +2416,10 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46076.3189094676</x:v>
+        <x:v>46048.0974875347</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
         <x:v>299</x:v>
@@ -2413,7 +2428,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46092.1400343403</x:v>
+        <x:v>46093.2926065278</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>41</x:v>
@@ -2421,13 +2436,13 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B22" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
         <x:v>301</x:v>
@@ -2439,19 +2454,19 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46079.2852568981</x:v>
+        <x:v>46076.3189094676</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46079.2852718981</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
         <x:v>304</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>2130</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46097.2459243171</x:v>
+        <x:v>46092.1400343403</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>41</x:v>
@@ -2459,37 +2474,37 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>300</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>251</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46079.2747337153</x:v>
+        <x:v>46079.2852568981</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46079.2747495718</x:v>
+        <x:v>46079.2852718981</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46097.2536368518</x:v>
+        <x:v>46097.2459243171</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>41</x:v>
@@ -2497,12 +2512,14 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s"/>
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="E24" s="14" t="s">
         <x:v>310</x:v>
       </x:c>
@@ -2513,19 +2530,19 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46090.2854096643</x:v>
+        <x:v>46079.2747337153</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46090.2854287153</x:v>
+        <x:v>46079.2747495718</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
-        <x:v>426</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46094.0865837153</x:v>
+        <x:v>46097.2536368518</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>41</x:v>
@@ -2536,23 +2553,23 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s"/>
       <x:c r="E25" s="14" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46090.2541037731</x:v>
+        <x:v>46090.2854096643</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46090.2541222106</x:v>
+        <x:v>46090.2854287153</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
         <x:v>317</x:v>
@@ -2561,7 +2578,7 @@
         <x:v>426</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46094.0819034491</x:v>
+        <x:v>46094.0865837153</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>41</x:v>
@@ -2576,69 +2593,94 @@
       </x:c>
       <x:c r="D26" s="15" t="s"/>
       <x:c r="E26" s="14" t="s">
-        <x:v>314</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46090.2349194444</x:v>
+        <x:v>46090.2541037731</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46090.2349374884</x:v>
+        <x:v>46090.2541222106</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46094.093939213</x:v>
+        <x:v>46094.0819034491</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s"/>
+      <x:c r="E27" s="14" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46090.2349194444</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46090.2349374884</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46094.093939213</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="19" t="s">
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="19" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C29" s="20" t="s"/>
-      <x:c r="D29" s="20" t="s"/>
-      <x:c r="E29" s="21" t="s"/>
-      <x:c r="F29" s="21" t="s"/>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B30" s="22" t="s">
+      <x:c r="C30" s="20" t="s"/>
+      <x:c r="D30" s="20" t="s"/>
+      <x:c r="E30" s="21" t="s"/>
+      <x:c r="F30" s="21" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="22" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C30" s="23" t="s"/>
-      <x:c r="D30" s="23" t="s"/>
-      <x:c r="E30" s="23" t="s"/>
-      <x:c r="F30" s="24" t="s">
+      <x:c r="C31" s="23" t="s"/>
+      <x:c r="D31" s="23" t="s"/>
+      <x:c r="E31" s="23" t="s"/>
+      <x:c r="F31" s="24" t="s">
         <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="25" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="26" t="s"/>
       <x:c r="D32" s="26" t="s"/>
@@ -2649,60 +2691,70 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="25" t="s">
-        <x:v>131</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C33" s="26" t="s"/>
       <x:c r="D33" s="26" t="s"/>
       <x:c r="E33" s="26" t="s"/>
       <x:c r="F33" s="27" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="25" t="s">
-        <x:v>15</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C34" s="26" t="s"/>
       <x:c r="D34" s="26" t="s"/>
       <x:c r="E34" s="26" t="s"/>
       <x:c r="F34" s="27" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="25" t="s">
-        <x:v>300</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C35" s="26" t="s"/>
       <x:c r="D35" s="26" t="s"/>
       <x:c r="E35" s="26" t="s"/>
       <x:c r="F35" s="27" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="25" t="s">
-        <x:v>23</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C36" s="26" t="s"/>
       <x:c r="D36" s="26" t="s"/>
       <x:c r="E36" s="26" t="s"/>
       <x:c r="F36" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C37" s="26" t="s"/>
+      <x:c r="D37" s="26" t="s"/>
+      <x:c r="E37" s="26" t="s"/>
+      <x:c r="F37" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="28" t="s">
+    <x:row r="38" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B38" s="28" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C37" s="29" t="s"/>
-      <x:c r="D37" s="29" t="s"/>
-      <x:c r="E37" s="29" t="s"/>
-      <x:c r="F37" s="30" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C38" s="29" t="s"/>
+      <x:c r="D38" s="29" t="s"/>
+      <x:c r="E38" s="29" t="s"/>
+      <x:c r="F38" s="30" t="n">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3664,8 +3716,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B29:F29"/>
-    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B30:F30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
@@ -3673,6 +3724,7 @@
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -878,6 +878,18 @@
     <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
   </x:si>
   <x:si>
+    <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-110613A-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1293-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216181</x:t>
+  </x:si>
+  <x:si>
     <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -890,18 +902,6 @@
     <x:t>1216180</x:t>
   </x:si>
   <x:si>
-    <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-110613A-22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1293-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216181</x:t>
-  </x:si>
-  <x:si>
     <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -930,6 +930,42 @@
   </x:si>
   <x:si>
     <x:t>1216184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VETERANS VILLAGE, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0601G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1397-805</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sangali, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0630F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1398-278</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ayala, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0629F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1399-659</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1347138</x:t>
   </x:si>
   <x:si>
     <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
@@ -2302,19 +2338,19 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46046.1237709144</x:v>
+        <x:v>46046.1309132176</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
         <x:v>285</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46093.2636364931</x:v>
+        <x:v>46093.2732890162</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>41</x:v>
@@ -2340,19 +2376,19 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46046.1309132176</x:v>
+        <x:v>46046.1237709144</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46021</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
         <x:v>289</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46093.2732890162</x:v>
+        <x:v>46093.2636364931</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>41</x:v>
@@ -2439,146 +2475,148 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>300</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="H22" s="16">
+        <x:v>46094.3172049306</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46076.3189094676</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>304</x:v>
-      </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46092.1400343403</x:v>
+        <x:v>46107.1610127431</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B23" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="s">
+      <x:c r="H23" s="16">
+        <x:v>46094.3273162269</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46079.2852568981</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46079.2852718981</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>309</x:v>
-      </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46097.2459243171</x:v>
+        <x:v>46107.1513918519</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>305</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>256</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="s">
+      <x:c r="H24" s="16">
+        <x:v>46094.3289943287</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46079.2747337153</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46079.2747495718</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>313</x:v>
-      </x:c>
       <x:c r="K24" s="17" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46097.2536368518</x:v>
+        <x:v>46107.1436918634</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="s"/>
-      <x:c r="E25" s="14" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="s">
+      <x:c r="H25" s="16">
+        <x:v>46076.3189094676</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46090.2854096643</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46090.2854287153</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>317</x:v>
-      </x:c>
       <x:c r="K25" s="17" t="n">
-        <x:v>426</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46094.0865837153</x:v>
+        <x:v>46092.1400343403</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>41</x:v>
@@ -2586,35 +2624,37 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="s"/>
-      <x:c r="E26" s="14" t="s">
+      <x:c r="F26" s="14" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="H26" s="16">
+        <x:v>46079.2852568981</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46079.2852718981</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46090.2541037731</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46090.2541222106</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
-        <x:v>322</x:v>
-      </x:c>
       <x:c r="K26" s="17" t="n">
-        <x:v>426</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46094.0819034491</x:v>
+        <x:v>46097.2459243171</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>41</x:v>
@@ -2622,109 +2662,186 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="s"/>
-      <x:c r="E27" s="14" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="s">
+      <x:c r="H27" s="16">
+        <x:v>46079.2747337153</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46079.2747495718</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46090.2349194444</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46090.2349374884</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="s">
-        <x:v>326</x:v>
-      </x:c>
       <x:c r="K27" s="17" t="n">
-        <x:v>426</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46094.093939213</x:v>
+        <x:v>46097.2536368518</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="19" t="s">
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s"/>
+      <x:c r="E28" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46090.2854096643</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46090.2854287153</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46094.0865837153</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s"/>
+      <x:c r="E29" s="14" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46090.2541037731</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46090.2541222106</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46094.0819034491</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s"/>
+      <x:c r="E30" s="14" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46090.2349194444</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46090.2349374884</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46094.093939213</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="19" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C30" s="20" t="s"/>
-      <x:c r="D30" s="20" t="s"/>
-      <x:c r="E30" s="21" t="s"/>
-      <x:c r="F30" s="21" t="s"/>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="22" t="s">
+      <x:c r="C33" s="20" t="s"/>
+      <x:c r="D33" s="20" t="s"/>
+      <x:c r="E33" s="21" t="s"/>
+      <x:c r="F33" s="21" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="22" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C31" s="23" t="s"/>
-      <x:c r="D31" s="23" t="s"/>
-      <x:c r="E31" s="23" t="s"/>
-      <x:c r="F31" s="24" t="s">
+      <x:c r="C34" s="23" t="s"/>
+      <x:c r="D34" s="23" t="s"/>
+      <x:c r="E34" s="23" t="s"/>
+      <x:c r="F34" s="24" t="s">
         <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C32" s="26" t="s"/>
-      <x:c r="D32" s="26" t="s"/>
-      <x:c r="E32" s="26" t="s"/>
-      <x:c r="F32" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="25" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C33" s="26" t="s"/>
-      <x:c r="D33" s="26" t="s"/>
-      <x:c r="E33" s="26" t="s"/>
-      <x:c r="F33" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="25" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C34" s="26" t="s"/>
-      <x:c r="D34" s="26" t="s"/>
-      <x:c r="E34" s="26" t="s"/>
-      <x:c r="F34" s="27" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="25" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C35" s="26" t="s"/>
       <x:c r="D35" s="26" t="s"/>
       <x:c r="E35" s="26" t="s"/>
       <x:c r="F35" s="27" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="25" t="s">
-        <x:v>305</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C36" s="26" t="s"/>
       <x:c r="D36" s="26" t="s"/>
@@ -2735,29 +2852,59 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="25" t="s">
-        <x:v>23</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C37" s="26" t="s"/>
       <x:c r="D37" s="26" t="s"/>
       <x:c r="E37" s="26" t="s"/>
       <x:c r="F37" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="25" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C38" s="26" t="s"/>
+      <x:c r="D38" s="26" t="s"/>
+      <x:c r="E38" s="26" t="s"/>
+      <x:c r="F38" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="25" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="C39" s="26" t="s"/>
+      <x:c r="D39" s="26" t="s"/>
+      <x:c r="E39" s="26" t="s"/>
+      <x:c r="F39" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="25" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C40" s="26" t="s"/>
+      <x:c r="D40" s="26" t="s"/>
+      <x:c r="E40" s="26" t="s"/>
+      <x:c r="F40" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B38" s="28" t="s">
+    <x:row r="41" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B41" s="28" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C38" s="29" t="s"/>
-      <x:c r="D38" s="29" t="s"/>
-      <x:c r="E38" s="29" t="s"/>
-      <x:c r="F38" s="30" t="n">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C41" s="29" t="s"/>
+      <x:c r="D41" s="29" t="s"/>
+      <x:c r="E41" s="29" t="s"/>
+      <x:c r="F41" s="30" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3716,15 +3863,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B30:F30"/>
-    <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B33:F33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1897,7 +1897,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1937,7 +1937,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>34</x:v>
@@ -1976,7 +1976,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -2014,7 +2014,7 @@
         <x:v>222</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -2052,7 +2052,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
@@ -2090,7 +2090,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
@@ -2128,7 +2128,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
@@ -2166,7 +2166,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
@@ -2204,7 +2204,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
@@ -2242,7 +2242,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2280,7 +2280,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2318,7 +2318,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2356,7 +2356,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2394,7 +2394,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2432,7 +2432,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2470,7 +2470,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2508,7 +2508,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2546,7 +2546,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2584,7 +2584,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2622,7 +2622,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
         <x:v>317</x:v>
       </x:c>
@@ -2660,7 +2660,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
         <x:v>317</x:v>
       </x:c>
@@ -2698,7 +2698,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2734,7 +2734,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -2770,7 +2770,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -4016,7 +4016,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4056,7 +4056,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -4095,7 +4095,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -5318,7 +5318,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -5358,7 +5358,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>34</x:v>
@@ -5397,7 +5397,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -5435,7 +5435,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -5473,7 +5473,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
@@ -5509,7 +5509,7 @@
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -5547,7 +5547,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6790,7 +6790,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -6830,7 +6830,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>42</x:v>
@@ -6869,7 +6869,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
@@ -6907,7 +6907,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6945,7 +6945,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -6983,7 +6983,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7021,7 +7021,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -7059,7 +7059,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -8299,7 +8299,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -8339,7 +8339,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -8378,7 +8378,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -8414,7 +8414,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -9636,7 +9636,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -9676,7 +9676,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>121</x:v>
@@ -9713,7 +9713,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -9751,7 +9751,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
@@ -9789,7 +9789,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9827,7 +9827,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9865,7 +9865,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9903,7 +9903,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -9941,7 +9941,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>156</x:v>
       </x:c>
@@ -9979,7 +9979,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>156</x:v>
       </x:c>
@@ -10017,7 +10017,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -10053,7 +10053,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -11311,7 +11311,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -11351,7 +11351,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -11390,7 +11390,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11428,7 +11428,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -11466,7 +11466,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12678,7 +12678,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -12718,7 +12718,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -12757,7 +12757,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12795,7 +12795,7 @@
         <x:v>205</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -12833,7 +12833,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
@@ -14054,7 +14054,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -14094,7 +14094,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>42</x:v>
@@ -14133,7 +14133,7 @@
         <x:v>222</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -14171,7 +14171,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="330">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -38,9 +38,6 @@
     <x:t>PERMITS SUMMARY</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | July 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -131,9 +128,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | August 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -230,9 +224,6 @@
     <x:t>1215852</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | September 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>VALIANT ELECTRONICS SUPPLY</x:t>
   </x:si>
   <x:si>
@@ -344,9 +335,6 @@
     <x:t>1215906</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | October 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>EMCOR INC TIGUMA BRANCH</x:t>
   </x:si>
   <x:si>
@@ -392,9 +380,6 @@
     <x:t>1215917</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | November 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -557,9 +542,6 @@
     <x:t>1216022</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | December 2025</x:t>
-  </x:si>
-  <x:si>
     <x:t>AB GADGETS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -620,9 +602,6 @@
     <x:t>1216036</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | January 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>N/A N/A, Poblacion, San Pablo, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -680,9 +659,6 @@
     <x:t>1216091</x:t>
   </x:si>
   <x:si>
-    <x:t>IX | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>DES APPLIANCE PLAZA, INC.</x:t>
   </x:si>
   <x:si>
@@ -720,9 +696,6 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1317-596</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>MINZ CELLPHONE AND ACCESSORIES SHOP</x:t>
@@ -1378,7 +1351,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1393,6 +1366,9 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1453,7 +1429,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1489,6 +1465,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1863,20 +1843,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1899,1009 +1879,1009 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46088.1798280556</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46088.1798485995</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46093.2393924884</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46077.2833774074</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46097</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46094.1366842014</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46088.1798280556</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46088.1798485995</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="H10" s="17">
+        <x:v>46091.1989145023</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46106.1492534144</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46076.2810036343</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46076.2810195833</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46097.2411206366</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46076.2450058565</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46076.2450229514</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46094.1710418981</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46076.2578122338</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46076.2578276505</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46097.2583940162</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46076.263358912</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46076.2633790625</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46093.2393924884</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="L14" s="19">
+        <x:v>46094.1562770949</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46076.3755334722</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46076.3755506134</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46094.1653946759</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46083.2966067014</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46387</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46098.2996351505</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46046.1343687731</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>45917</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46093.2878737037</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46046.1309132176</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46021</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46093.2732890162</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46046.1237709144</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46093.2636364931</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46046.1140924306</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46093.2825289005</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H21" s="17">
+        <x:v>46048.0974875347</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J21" s="16" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46093.2926065278</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H22" s="17">
+        <x:v>46094.3172049306</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J22" s="16" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46107.1610127431</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H23" s="17">
+        <x:v>46094.3273162269</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J23" s="16" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46107.1513918519</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="H24" s="17">
+        <x:v>46094.3289943287</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="J24" s="16" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46107.1436918634</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="H25" s="17">
+        <x:v>46076.3189094676</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J25" s="16" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46092.1400343403</x:v>
+      </x:c>
+      <x:c r="M25" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="15" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46077.2833774074</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46097</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46094.1366842014</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46091.1989145023</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46101</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46106.1492534144</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="D26" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="H26" s="17">
+        <x:v>46079.2852568981</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>46079.2852718981</x:v>
+      </x:c>
+      <x:c r="J26" s="16" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46097.2459243171</x:v>
+      </x:c>
+      <x:c r="M26" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="15" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46076.2810036343</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46076.2810195833</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46097.2411206366</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46076.2450058565</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46076.2450229514</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>46094.1710418981</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46076.2578122338</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46076.2578276505</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>46097.2583940162</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46076.263358912</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46076.2633790625</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>46094.1562770949</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46076.3755334722</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46076.3755506134</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>46094.1653946759</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46083.2966067014</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46387</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>46098.2996351505</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46046.1343687731</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>45917</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>46093.2878737037</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46046.1309132176</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46021</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>46093.2732890162</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46046.1237709144</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>46093.2636364931</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46046.1140924306</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>46093.2825289005</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46048.0974875347</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>46093.2926065278</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46094.3172049306</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>46107.1610127431</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
+      <x:c r="D27" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="H27" s="17">
+        <x:v>46079.2747337153</x:v>
+      </x:c>
+      <x:c r="I27" s="17">
+        <x:v>46079.2747495718</x:v>
+      </x:c>
+      <x:c r="J27" s="16" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46097.2536368518</x:v>
+      </x:c>
+      <x:c r="M27" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46094.3273162269</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>46107.1513918519</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
+      <x:c r="C28" s="15" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="s"/>
+      <x:c r="E28" s="15" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="H28" s="17">
+        <x:v>46090.2854096643</x:v>
+      </x:c>
+      <x:c r="I28" s="17">
+        <x:v>46090.2854287153</x:v>
+      </x:c>
+      <x:c r="J28" s="16" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46094.0865837153</x:v>
+      </x:c>
+      <x:c r="M28" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46094.3289943287</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L24" s="18">
-        <x:v>46107.1436918634</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
+      <x:c r="C29" s="15" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="s"/>
+      <x:c r="E29" s="15" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="H29" s="17">
+        <x:v>46090.2541037731</x:v>
+      </x:c>
+      <x:c r="I29" s="17">
+        <x:v>46090.2541222106</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L29" s="19">
+        <x:v>46094.0819034491</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46076.3189094676</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L25" s="18">
-        <x:v>46092.1400343403</x:v>
-      </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46079.2852568981</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46079.2852718981</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="K26" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L26" s="18">
-        <x:v>46097.2459243171</x:v>
-      </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
+      <x:c r="C30" s="15" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="s"/>
+      <x:c r="E30" s="15" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
-        <x:v>46079.2747337153</x:v>
-      </x:c>
-      <x:c r="I27" s="16">
-        <x:v>46079.2747495718</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="K27" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L27" s="18">
-        <x:v>46097.2536368518</x:v>
-      </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s"/>
-      <x:c r="E28" s="14" t="s">
+      <x:c r="F30" s="15" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="F28" s="14" t="s">
+      <x:c r="G30" s="15" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="G28" s="14" t="s">
+      <x:c r="H30" s="17">
+        <x:v>46090.2349194444</x:v>
+      </x:c>
+      <x:c r="I30" s="17">
+        <x:v>46090.2349374884</x:v>
+      </x:c>
+      <x:c r="J30" s="16" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="H28" s="16">
-        <x:v>46090.2854096643</x:v>
-      </x:c>
-      <x:c r="I28" s="16">
-        <x:v>46090.2854287153</x:v>
-      </x:c>
-      <x:c r="J28" s="15" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="K28" s="17" t="n">
+      <x:c r="K30" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L28" s="18">
-        <x:v>46094.0865837153</x:v>
-      </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s"/>
-      <x:c r="E29" s="14" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
-        <x:v>46090.2541037731</x:v>
-      </x:c>
-      <x:c r="I29" s="16">
-        <x:v>46090.2541222106</x:v>
-      </x:c>
-      <x:c r="J29" s="15" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="K29" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L29" s="18">
-        <x:v>46094.0819034491</x:v>
-      </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s"/>
-      <x:c r="E30" s="14" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
-        <x:v>46090.2349194444</x:v>
-      </x:c>
-      <x:c r="I30" s="16">
-        <x:v>46090.2349374884</x:v>
-      </x:c>
-      <x:c r="J30" s="15" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="K30" s="17" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L30" s="18">
+      <x:c r="L30" s="19">
         <x:v>46094.093939213</x:v>
       </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>41</x:v>
+      <x:c r="M30" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="19" t="s">
+      <x:c r="B33" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C33" s="21" t="s"/>
+      <x:c r="D33" s="21" t="s"/>
+      <x:c r="E33" s="22" t="s"/>
+      <x:c r="F33" s="22" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C33" s="20" t="s"/>
-      <x:c r="D33" s="20" t="s"/>
-      <x:c r="E33" s="21" t="s"/>
-      <x:c r="F33" s="21" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="22" t="s">
+      <x:c r="C34" s="24" t="s"/>
+      <x:c r="D34" s="24" t="s"/>
+      <x:c r="E34" s="24" t="s"/>
+      <x:c r="F34" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C34" s="23" t="s"/>
-      <x:c r="D34" s="23" t="s"/>
-      <x:c r="E34" s="23" t="s"/>
-      <x:c r="F34" s="24" t="s">
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="26" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C37" s="27" t="s"/>
+      <x:c r="D37" s="27" t="s"/>
+      <x:c r="E37" s="27" t="s"/>
+      <x:c r="F37" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C38" s="27" t="s"/>
+      <x:c r="D38" s="27" t="s"/>
+      <x:c r="E38" s="27" t="s"/>
+      <x:c r="F38" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="26" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="C39" s="27" t="s"/>
+      <x:c r="D39" s="27" t="s"/>
+      <x:c r="E39" s="27" t="s"/>
+      <x:c r="F39" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C40" s="27" t="s"/>
+      <x:c r="D40" s="27" t="s"/>
+      <x:c r="E40" s="27" t="s"/>
+      <x:c r="F40" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B41" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C35" s="26" t="s"/>
-      <x:c r="D35" s="26" t="s"/>
-      <x:c r="E35" s="26" t="s"/>
-      <x:c r="F35" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="25" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C36" s="26" t="s"/>
-      <x:c r="D36" s="26" t="s"/>
-      <x:c r="E36" s="26" t="s"/>
-      <x:c r="F36" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="25" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C37" s="26" t="s"/>
-      <x:c r="D37" s="26" t="s"/>
-      <x:c r="E37" s="26" t="s"/>
-      <x:c r="F37" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C38" s="26" t="s"/>
-      <x:c r="D38" s="26" t="s"/>
-      <x:c r="E38" s="26" t="s"/>
-      <x:c r="F38" s="27" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="25" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="C39" s="26" t="s"/>
-      <x:c r="D39" s="26" t="s"/>
-      <x:c r="E39" s="26" t="s"/>
-      <x:c r="F39" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C40" s="26" t="s"/>
-      <x:c r="D40" s="26" t="s"/>
-      <x:c r="E40" s="26" t="s"/>
-      <x:c r="F40" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B41" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C41" s="29" t="s"/>
-      <x:c r="D41" s="29" t="s"/>
-      <x:c r="E41" s="29" t="s"/>
-      <x:c r="F41" s="30" t="n">
+      <x:c r="C41" s="30" t="s"/>
+      <x:c r="D41" s="30" t="s"/>
+      <x:c r="E41" s="30" t="s"/>
+      <x:c r="F41" s="31" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>
@@ -3982,20 +3962,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45839</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4018,171 +3998,171 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45860.0994011343</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45860.0994011343</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45860.1449620718</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45860.1449620718</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="C9" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45861.1130539236</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45861.113062963</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45861.1130539236</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45861.113062963</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="L9" s="18">
+      <x:c r="L9" s="19">
         <x:v>45862.3035735301</x:v>
       </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C12" s="20" t="s"/>
-      <x:c r="D12" s="20" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="21" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="22" t="s">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C13" s="23" t="s"/>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="23" t="s"/>
-      <x:c r="F13" s="24" t="s">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="s"/>
-      <x:c r="D14" s="26" t="s"/>
-      <x:c r="E14" s="26" t="s"/>
-      <x:c r="F14" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="30" t="n">
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -5284,20 +5264,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45870</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5320,345 +5300,345 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45866.2802922106</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45866.2803013889</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45873.1184145139</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45866.2802922106</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45866.2803013889</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45873.1184145139</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="C9" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45875.2238915046</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45921</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>4030</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45876.2433041204</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45875.2238915046</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45880.121483588</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45882</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45881.1619025579</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45873.2195533449</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45873.2195624074</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45882.1150772338</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45875.3617282407</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>4030</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45876.2433041204</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
+      <x:c r="J12" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45876.2230995023</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45880.121483588</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45882</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45881.1619025579</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45873.2195533449</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45873.2195624074</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>2790</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45882.1150772338</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45875.3617282407</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45921</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="H13" s="17">
+        <x:v>45875.2324767593</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45903</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45876.2230995023</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45875.2324767593</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45903</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45876.2319890162</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>41</x:v>
+      <x:c r="M13" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="19" t="s">
+      <x:c r="B16" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="s"/>
-      <x:c r="D16" s="20" t="s"/>
-      <x:c r="E16" s="21" t="s"/>
-      <x:c r="F16" s="21" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="s">
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="25" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -6756,20 +6736,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45901</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6792,383 +6772,383 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="H8" s="17">
+        <x:v>45915.3557896528</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45918.2339584606</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="C9" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45915.3557896528</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="D9" s="16" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45918.2339584606</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
+      <x:c r="E9" s="15" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45903.3849758912</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45916</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>3150</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45908.2848985301</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45903.3849758912</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45916</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>3150</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45908.2848985301</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45919.4023076505</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45926</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45925.9451511111</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45919.4023076505</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45926</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="G11" s="15" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45918.1054021528</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45900</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45929.2194160764</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45908.2183496296</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45918</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45925.9451511111</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45918.1054021528</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45900</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45929.2194160764</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="L12" s="19">
+        <x:v>45912.190615463</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45908.2183496296</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45918</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="G13" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>45922.1415441088</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45920</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45912.190615463</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="L13" s="19">
+        <x:v>45922.1832596412</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="15" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45922.1415441088</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45920</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
+      <x:c r="F14" s="15" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>45922.1832596412</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="H14" s="17">
+        <x:v>45919.4732912847</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45919.4733016088</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45919.4732912847</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45919.4733016088</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="19">
         <x:v>45926.2586175694</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>41</x:v>
+      <x:c r="M14" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="19" t="s">
+      <x:c r="B17" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="22" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C17" s="20" t="s"/>
-      <x:c r="D17" s="20" t="s"/>
-      <x:c r="E17" s="21" t="s"/>
-      <x:c r="F17" s="21" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="22" t="s">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C18" s="23" t="s"/>
-      <x:c r="D18" s="23" t="s"/>
-      <x:c r="E18" s="23" t="s"/>
-      <x:c r="F18" s="24" t="s">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="25" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="s"/>
-      <x:c r="D19" s="26" t="s"/>
-      <x:c r="E19" s="26" t="s"/>
-      <x:c r="F19" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="30" t="n">
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8265,20 +8245,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45931</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8301,207 +8281,207 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>45933.0884397222</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45932</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45936.0148412269</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="D9" s="16" t="s"/>
+      <x:c r="E9" s="15" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45933.0884397222</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45932</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45936.0148412269</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45928.9304539583</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45928.9304922454</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45938.035947419</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45928.9304539583</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45928.9304922454</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="H10" s="17">
+        <x:v>45926.4563998264</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45926.4564372454</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45938.035947419</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45926.4563998264</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45926.4564372454</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45932.2395375463</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>41</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
+      <x:c r="B13" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -9602,20 +9582,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45962</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9638,553 +9618,553 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>45951.1032693866</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45951.1032970718</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="K8" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45971.088825787</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45980.216052338</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45979</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45951.1032693866</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45951.1032970718</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>45985.3594797917</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="C10" s="15" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45971.088825787</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45965.2736735764</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45965.2736975579</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45972.1539687153</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>45965.2661516088</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>45972.1364239815</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>45953.5328279861</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>45966.0458205787</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>45959.0699130787</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45972.2719636111</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>45958.0724435648</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>45810</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>45973.0584535069</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>45973.1309431481</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>45950</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>45985.2116720486</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>45971.2436290394</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>45608</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>45973.2287349769</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45980.216052338</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45979</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45985.3594797917</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
+      <x:c r="C17" s="15" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s"/>
+      <x:c r="E17" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>45954.4190024884</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>45954.4190340741</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>45967.2850746528</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45965.2736735764</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45965.2736975579</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45972.1539687153</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45965.2661516088</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45972.1364239815</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45953.5328279861</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45966.0458205787</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45959.0699130787</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>45972.2719636111</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45958.0724435648</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45810</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>45973.0584535069</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45973.1309431481</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>45950</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>45985.2116720486</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="C18" s="15" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="H16" s="16">
-        <x:v>45971.2436290394</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>45608</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
+      <x:c r="D18" s="16" t="s"/>
+      <x:c r="E18" s="15" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>1950</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>45973.2287349769</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s"/>
-      <x:c r="E17" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="F18" s="15" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="G18" s="15" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>45954.4190024884</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>45954.4190340741</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
+      <x:c r="H18" s="17">
+        <x:v>45959.2592067593</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>45959.2592354861</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>1986</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>45967.2850746528</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s"/>
-      <x:c r="E18" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>45959.2592067593</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>45959.2592354861</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K18" s="18" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L18" s="19">
         <x:v>45986.1291977315</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>41</x:v>
+      <x:c r="M18" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="19" t="s">
+      <x:c r="B21" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C21" s="21" t="s"/>
+      <x:c r="D21" s="21" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="22" t="s"/>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C21" s="20" t="s"/>
-      <x:c r="D21" s="20" t="s"/>
-      <x:c r="E21" s="21" t="s"/>
-      <x:c r="F21" s="21" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="22" t="s">
+      <x:c r="C22" s="24" t="s"/>
+      <x:c r="D22" s="24" t="s"/>
+      <x:c r="E22" s="24" t="s"/>
+      <x:c r="F22" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C22" s="23" t="s"/>
-      <x:c r="D22" s="23" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="24" t="s">
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B29" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="25" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="25" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="C27" s="26" t="s"/>
-      <x:c r="D27" s="26" t="s"/>
-      <x:c r="E27" s="26" t="s"/>
-      <x:c r="F27" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
+      <x:c r="C29" s="30" t="s"/>
+      <x:c r="D29" s="30" t="s"/>
+      <x:c r="E29" s="30" t="s"/>
+      <x:c r="F29" s="31" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -11277,20 +11257,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>45992</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11313,238 +11293,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>45981.1374423611</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>45996.1054321181</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F9" s="15" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>45994.1029113889</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>45169</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45981.1374423611</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>12780</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46006.2230459028</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>45973.282415625</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45996.1054321181</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45994.1029113889</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45169</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="L10" s="19">
+        <x:v>45993.0810788889</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>12780</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46006.2230459028</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>45988.1651420255</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45974</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45973.282415625</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45993.0810788889</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45988.1651420255</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45974</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>46006.238966169</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>41</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+      <x:c r="B14" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -12644,20 +12624,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -12680,247 +12660,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46033.3509841319</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46049.2368941319</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46010.1939375579</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46029</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46034.111096713</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46033.3509841319</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46049.2368941319</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H10" s="17">
+        <x:v>45989.0397289236</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45597</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46010.1939375579</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46029</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
+      <x:c r="K10" s="18" t="n">
+        <x:v>8280</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46043.2235160301</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46034.111096713</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>205</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="H11" s="17">
+        <x:v>46043.0454792477</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46043.0455093056</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45989.0397289236</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45597</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>8280</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46043.2235160301</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46043.0454792477</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46043.0455093056</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>46048.2516543634</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>41</x:v>
+      <x:c r="M11" s="15" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
+      <x:c r="B14" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -14020,20 +14000,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -14056,211 +14036,211 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46058.3038087847</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46055</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46066.3127838657</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46066.3781940972</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46081</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="K9" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46077.0856746296</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>46058.3038087847</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>46055</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="H10" s="17">
+        <x:v>46062.2741739236</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46075</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="18">
-        <x:v>46066.3127838657</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46066.3781940972</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46081</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>46077.0856746296</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46062.2741739236</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46075</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>46077.1029543634</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="19" t="s">
+      <x:c r="B13" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="21" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="s">
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="25" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C15" s="26" t="s"/>
-      <x:c r="D15" s="26" t="s"/>
-      <x:c r="E15" s="26" t="s"/>
-      <x:c r="F15" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="30" t="n">
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -15,6 +15,7 @@
     <x:sheet name="January 2026" sheetId="13" r:id="rId13"/>
     <x:sheet name="February 2026" sheetId="14" r:id="rId14"/>
     <x:sheet name="March 2026" sheetId="15" r:id="rId15"/>
+    <x:sheet name="April 2026" sheetId="16" r:id="rId16"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="330">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1020,6 +1021,33 @@
   </x:si>
   <x:si>
     <x:t>1216187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yoho Building Purok tambis, Sanito, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-07290-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1402-161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quezon avenue, poblacion, Sindangan, Zamboanga Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-07286-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1401-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216209</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3852,6 +3880,1299 @@
     <x:mergeCell ref="B39:E39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46097.2931531944</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46097.2931710069</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46119.1505964699</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46097.2826708912</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46097.2826882292</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46119.1491368056</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1048,6 +1048,21 @@
   </x:si>
   <x:si>
     <x:t>1216209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JVR bldg. Rizal avenue, San francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0716-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1296-085</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216221</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4141,52 +4156,99 @@
         <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46049.1592238657</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45939</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46120.3467831597</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5164,15 +5226,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1021,6 +1021,21 @@
   </x:si>
   <x:si>
     <x:t>1216187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZZ GADGETS AND ACCESORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Central Hypermarket Rizal Avenue, Blancia, Molave, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIX-07277-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1400-190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216222</x:t>
   </x:si>
   <x:si>
     <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
@@ -4082,7 +4097,7 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="15" t="s">
-        <x:v>126</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
         <x:v>330</x:v>
@@ -4100,19 +4115,19 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46097.2931531944</x:v>
+        <x:v>46097.2573180208</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46097.2931710069</x:v>
+        <x:v>46097.2573345602</x:v>
       </x:c>
       <x:c r="J8" s="16" t="s">
         <x:v>334</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>3530</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46119.1505964699</x:v>
+        <x:v>46125.2485400116</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>39</x:v>
@@ -4123,34 +4138,34 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>330</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
-        <x:v>335</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F9" s="15" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>337</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46097.2826708912</x:v>
+        <x:v>46097.2931531944</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46097.2826882292</x:v>
+        <x:v>46097.2931710069</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
-        <x:v>338</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46119.1491368056</x:v>
+        <x:v>46119.1505964699</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>39</x:v>
@@ -4158,13 +4173,13 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="15" t="s">
-        <x:v>14</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>339</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E10" s="15" t="s">
         <x:v>340</x:v>
@@ -4176,60 +4191,87 @@
         <x:v>342</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46049.1592238657</x:v>
+        <x:v>46097.2826708912</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>45939</x:v>
+        <x:v>46097.2826882292</x:v>
       </x:c>
       <x:c r="J10" s="16" t="s">
         <x:v>343</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46120.3467831597</x:v>
+        <x:v>46119.1491368056</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46049.1592238657</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45939</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46120.3467831597</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="20" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="22" t="s"/>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="23" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="s">
         <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="26" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="27" t="s"/>
       <x:c r="D16" s="27" t="s"/>
@@ -4238,19 +4280,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B19" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
@@ -5226,16 +5288,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-permit_cache_ServiceTracking-IX-202501-202612.xlsx.xlsx
@@ -1089,7 +1089,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1129,14 +1129,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1409,7 +1401,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1420,16 +1412,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1441,53 +1430,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1522,87 +1511,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1904,17 +1889,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1937,1009 +1922,1009 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46088.1798280556</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46088.1798485995</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46093.2393924884</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46077.2833774074</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46097</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46094.1366842014</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46091.1989145023</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>4030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46106.1492534144</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46076.2810036343</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46076.2810195833</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46097.2411206366</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46076.2450058565</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46076.2450229514</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46094.1710418981</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46076.2578122338</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46076.2578276505</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46097.2583940162</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46076.263358912</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46076.2633790625</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46094.1562770949</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46076.3755334722</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46076.3755506134</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46094.1653946759</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46083.2966067014</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46387</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46098.2996351505</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46046.1343687731</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>45917</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46093.2878737037</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46046.1309132176</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46021</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46093.2732890162</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46046.1237709144</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46093.2636364931</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46046.1140924306</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46093.2825289005</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46048.0974875347</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46093.2926065278</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46094.3172049306</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46107.1610127431</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="14" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>46094.3273162269</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>46107.1513918519</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>46094.3289943287</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>46112</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>46107.1436918634</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="15" t="s">
+      <x:c r="B25" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="s">
+      <x:c r="C25" s="14" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="s">
+      <x:c r="D25" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="s">
+      <x:c r="E25" s="14" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="s">
+      <x:c r="F25" s="14" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="G25" s="15" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="H25" s="17">
+      <x:c r="H25" s="16">
         <x:v>46076.3189094676</x:v>
       </x:c>
-      <x:c r="I25" s="17">
+      <x:c r="I25" s="16">
         <x:v>46074</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="s">
+      <x:c r="J25" s="15" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="K25" s="18" t="n">
+      <x:c r="K25" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="18">
         <x:v>46092.1400343403</x:v>
       </x:c>
-      <x:c r="M25" s="15" t="s">
+      <x:c r="M25" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="15" t="s">
+      <x:c r="B26" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="s">
+      <x:c r="C26" s="14" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="s">
+      <x:c r="D26" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="s">
+      <x:c r="E26" s="14" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="s">
+      <x:c r="F26" s="14" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="G26" s="15" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="H26" s="17">
+      <x:c r="H26" s="16">
         <x:v>46079.2852568981</x:v>
       </x:c>
-      <x:c r="I26" s="17">
+      <x:c r="I26" s="16">
         <x:v>46079.2852718981</x:v>
       </x:c>
-      <x:c r="J26" s="16" t="s">
+      <x:c r="J26" s="15" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="K26" s="18" t="n">
+      <x:c r="K26" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L26" s="19">
+      <x:c r="L26" s="18">
         <x:v>46097.2459243171</x:v>
       </x:c>
-      <x:c r="M26" s="15" t="s">
+      <x:c r="M26" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="15" t="s">
+      <x:c r="B27" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="s">
+      <x:c r="C27" s="14" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D27" s="16" t="s">
+      <x:c r="D27" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="s">
+      <x:c r="E27" s="14" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="s">
+      <x:c r="F27" s="14" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="G27" s="15" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="H27" s="17">
+      <x:c r="H27" s="16">
         <x:v>46079.2747337153</x:v>
       </x:c>
-      <x:c r="I27" s="17">
+      <x:c r="I27" s="16">
         <x:v>46079.2747495718</x:v>
       </x:c>
-      <x:c r="J27" s="16" t="s">
+      <x:c r="J27" s="15" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="K27" s="18" t="n">
+      <x:c r="K27" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L27" s="19">
+      <x:c r="L27" s="18">
         <x:v>46097.2536368518</x:v>
       </x:c>
-      <x:c r="M27" s="15" t="s">
+      <x:c r="M27" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="15" t="s">
+      <x:c r="B28" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="s">
+      <x:c r="C28" s="14" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="D28" s="16" t="s"/>
-      <x:c r="E28" s="15" t="s">
+      <x:c r="D28" s="15" t="s"/>
+      <x:c r="E28" s="14" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="s">
+      <x:c r="F28" s="14" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="G28" s="15" t="s">
+      <x:c r="G28" s="14" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="H28" s="17">
+      <x:c r="H28" s="16">
         <x:v>46090.2854096643</x:v>
       </x:c>
-      <x:c r="I28" s="17">
+      <x:c r="I28" s="16">
         <x:v>46090.2854287153</x:v>
       </x:c>
-      <x:c r="J28" s="16" t="s">
+      <x:c r="J28" s="15" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="K28" s="18" t="n">
+      <x:c r="K28" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L28" s="19">
+      <x:c r="L28" s="18">
         <x:v>46094.0865837153</x:v>
       </x:c>
-      <x:c r="M28" s="15" t="s">
+      <x:c r="M28" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="15" t="s">
+      <x:c r="B29" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="s">
+      <x:c r="C29" s="14" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="D29" s="16" t="s"/>
-      <x:c r="E29" s="15" t="s">
+      <x:c r="D29" s="15" t="s"/>
+      <x:c r="E29" s="14" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="s">
+      <x:c r="F29" s="14" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="G29" s="15" t="s">
+      <x:c r="G29" s="14" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="H29" s="17">
+      <x:c r="H29" s="16">
         <x:v>46090.2541037731</x:v>
       </x:c>
-      <x:c r="I29" s="17">
+      <x:c r="I29" s="16">
         <x:v>46090.2541222106</x:v>
       </x:c>
-      <x:c r="J29" s="16" t="s">
+      <x:c r="J29" s="15" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="K29" s="18" t="n">
+      <x:c r="K29" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L29" s="19">
+      <x:c r="L29" s="18">
         <x:v>46094.0819034491</x:v>
       </x:c>
-      <x:c r="M29" s="15" t="s">
+      <x:c r="M29" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="15" t="s">
+      <x:c r="B30" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="s">
+      <x:c r="C30" s="14" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="D30" s="16" t="s"/>
-      <x:c r="E30" s="15" t="s">
+      <x:c r="D30" s="15" t="s"/>
+      <x:c r="E30" s="14" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="s">
+      <x:c r="F30" s="14" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="G30" s="15" t="s">
+      <x:c r="G30" s="14" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="H30" s="17">
+      <x:c r="H30" s="16">
         <x:v>46090.2349194444</x:v>
       </x:c>
-      <x:c r="I30" s="17">
+      <x:c r="I30" s="16">
         <x:v>46090.2349374884</x:v>
       </x:c>
-      <x:c r="J30" s="16" t="s">
+      <x:c r="J30" s="15" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="K30" s="18" t="n">
+      <x:c r="K30" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L30" s="19">
+      <x:c r="L30" s="18">
         <x:v>46094.093939213</x:v>
       </x:c>
-      <x:c r="M30" s="15" t="s">
+      <x:c r="M30" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="20" t="s">
+      <x:c r="B33" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C33" s="21" t="s"/>
-      <x:c r="D33" s="21" t="s"/>
-      <x:c r="E33" s="22" t="s"/>
-      <x:c r="F33" s="22" t="s"/>
+      <x:c r="C33" s="20" t="s"/>
+      <x:c r="D33" s="20" t="s"/>
+      <x:c r="E33" s="21" t="s"/>
+      <x:c r="F33" s="21" t="s"/>
     </x:row>
     <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="23" t="s">
+      <x:c r="B34" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C34" s="24" t="s"/>
-      <x:c r="D34" s="24" t="s"/>
-      <x:c r="E34" s="24" t="s"/>
-      <x:c r="F34" s="25" t="s">
+      <x:c r="C34" s="23" t="s"/>
+      <x:c r="D34" s="23" t="s"/>
+      <x:c r="E34" s="23" t="s"/>
+      <x:c r="F34" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
+      <x:c r="B35" s="25" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
+      <x:c r="B36" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="26" t="s">
+      <x:c r="B37" s="25" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C37" s="27" t="s"/>
-      <x:c r="D37" s="27" t="s"/>
-      <x:c r="E37" s="27" t="s"/>
-      <x:c r="F37" s="28" t="n">
+      <x:c r="C37" s="26" t="s"/>
+      <x:c r="D37" s="26" t="s"/>
+      <x:c r="E37" s="26" t="s"/>
+      <x:c r="F37" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="26" t="s">
+      <x:c r="B38" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C38" s="27" t="s"/>
-      <x:c r="D38" s="27" t="s"/>
-      <x:c r="E38" s="27" t="s"/>
-      <x:c r="F38" s="28" t="n">
+      <x:c r="C38" s="26" t="s"/>
+      <x:c r="D38" s="26" t="s"/>
+      <x:c r="E38" s="26" t="s"/>
+      <x:c r="F38" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="26" t="s">
+      <x:c r="B39" s="25" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="C39" s="27" t="s"/>
-      <x:c r="D39" s="27" t="s"/>
-      <x:c r="E39" s="27" t="s"/>
-      <x:c r="F39" s="28" t="n">
+      <x:c r="C39" s="26" t="s"/>
+      <x:c r="D39" s="26" t="s"/>
+      <x:c r="E39" s="26" t="s"/>
+      <x:c r="F39" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="26" t="s">
+      <x:c r="B40" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C40" s="27" t="s"/>
-      <x:c r="D40" s="27" t="s"/>
-      <x:c r="E40" s="27" t="s"/>
-      <x:c r="F40" s="28" t="n">
+      <x:c r="C40" s="26" t="s"/>
+      <x:c r="D40" s="26" t="s"/>
+      <x:c r="E40" s="26" t="s"/>
+      <x:c r="F40" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B41" s="29" t="s">
+      <x:c r="B41" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C41" s="30" t="s"/>
-      <x:c r="D41" s="30" t="s"/>
-      <x:c r="E41" s="30" t="s"/>
-      <x:c r="F41" s="31" t="n">
+      <x:c r="C41" s="29" t="s"/>
+      <x:c r="D41" s="29" t="s"/>
+      <x:c r="E41" s="29" t="s"/>
+      <x:c r="F41" s="30" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>
@@ -4023,17 +4008,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4056,260 +4041,260 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46097.2573180208</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46097.2573345602</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46125.2485400116</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46097.2931531944</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46097.2931710069</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46119.1505964699</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46097.2826708912</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46097.2826882292</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46119.1491368056</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46049.1592238657</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45939</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46120.3467831597</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B19" s="29" t="s">
+      <x:c r="B19" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s"/>
-      <x:c r="D19" s="30" t="s"/>
-      <x:c r="E19" s="30" t="s"/>
-      <x:c r="F19" s="31" t="n">
+      <x:c r="C19" s="29" t="s"/>
+      <x:c r="D19" s="29" t="s"/>
+      <x:c r="E19" s="29" t="s"/>
+      <x:c r="F19" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -5412,17 +5397,17 @@
       <x:c r="B5" s="12">
         <x:v>45839</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5445,171 +5430,171 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45860.0994011343</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45853</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45860.1449620718</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45861.1130539236</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45861.113062963</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>930</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45862.3035735301</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="29" t="s"/>
+      <x:c r="D16" s="29" t="s"/>
+      <x:c r="E16" s="29" t="s"/>
+      <x:c r="F16" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -6714,17 +6699,17 @@
       <x:c r="B5" s="12">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -6747,345 +6732,345 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45866.2802922106</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45866.2803013889</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45873.1184145139</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45875.2238915046</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>4030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45876.2433041204</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45880.121483588</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45882</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45881.1619025579</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45873.2195533449</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45873.2195624074</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>2790</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45882.1150772338</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45875.3617282407</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45921</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45876.2230995023</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45875.2324767593</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45903</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45876.2319890162</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="29" t="s">
+      <x:c r="B22" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -8186,17 +8171,17 @@
       <x:c r="B5" s="12">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -8219,383 +8204,383 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45915.3557896528</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45918.2339584606</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45903.3849758912</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45916</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3150</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45908.2848985301</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45919.4023076505</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45925.9451511111</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45918.1054021528</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45900</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45929.2194160764</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45908.2183496296</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45918</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45912.190615463</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45922.1415441088</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45920</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45922.1832596412</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45919.4732912847</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45919.4733016088</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45926.2586175694</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
+      <x:c r="B17" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
+      <x:c r="C17" s="20" t="s"/>
+      <x:c r="D17" s="20" t="s"/>
+      <x:c r="E17" s="21" t="s"/>
+      <x:c r="F17" s="21" t="s"/>
     </x:row>
     <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
+      <x:c r="C18" s="23" t="s"/>
+      <x:c r="D18" s="23" t="s"/>
+      <x:c r="E18" s="23" t="s"/>
+      <x:c r="F18" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+      <x:c r="B23" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -9695,17 +9680,17 @@
       <x:c r="B5" s="12">
         <x:v>45931</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9728,207 +9713,207 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45933.0884397222</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45932</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45936.0148412269</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45928.9304539583</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45928.9304922454</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45938.035947419</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45926.4563998264</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45926.4564372454</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45932.2395375463</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -11032,17 +11017,17 @@
       <x:c r="B5" s="12">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11065,553 +11050,553 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45951.1032693866</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45951.1032970718</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45971.088825787</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45980.216052338</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45979</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45985.3594797917</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45965.2736735764</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45965.2736975579</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45972.1539687153</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45965.2661516088</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45972.1364239815</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45953.5328279861</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45966.0458205787</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45959.0699130787</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45972.2719636111</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45958.0724435648</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45810</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45973.0584535069</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45973.1309431481</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>45950</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45985.2116720486</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>45971.2436290394</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>45608</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>45973.2287349769</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s"/>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="D17" s="15" t="s"/>
+      <x:c r="E17" s="14" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>45954.4190024884</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>45954.4190340741</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>45967.2850746528</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s"/>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="D18" s="15" t="s"/>
+      <x:c r="E18" s="14" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>45959.2592067593</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>45959.2592354861</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>45986.1291977315</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="20" t="s">
+      <x:c r="B21" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C21" s="21" t="s"/>
-      <x:c r="D21" s="21" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="22" t="s"/>
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
     </x:row>
     <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="23" t="s">
+      <x:c r="B22" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C22" s="24" t="s"/>
-      <x:c r="D22" s="24" t="s"/>
-      <x:c r="E22" s="24" t="s"/>
-      <x:c r="F22" s="25" t="s">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
+      <x:c r="B27" s="25" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
+      <x:c r="B28" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="29" t="s">
+      <x:c r="B29" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C29" s="30" t="s"/>
-      <x:c r="D29" s="30" t="s"/>
-      <x:c r="E29" s="30" t="s"/>
-      <x:c r="F29" s="31" t="n">
+      <x:c r="C29" s="29" t="s"/>
+      <x:c r="D29" s="29" t="s"/>
+      <x:c r="E29" s="29" t="s"/>
+      <x:c r="F29" s="30" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -12707,17 +12692,17 @@
       <x:c r="B5" s="12">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -12740,238 +12725,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45981.1374423611</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45996.1054321181</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45994.1029113889</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45169</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>12780</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46006.2230459028</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45973.282415625</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45993.0810788889</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45988.1651420255</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46006.238966169</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -14074,17 +14059,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -14107,247 +14092,247 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46033.3509841319</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46049.2368941319</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46010.1939375579</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46029</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46034.111096713</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45989.0397289236</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46043.2235160301</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46043.0454792477</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46043.0455093056</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46048.2516543634</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+      <x:c r="B14" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="22" t="s"/>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="s">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="29" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s"/>
-      <x:c r="D18" s="30" t="s"/>
-      <x:c r="E18" s="30" t="s"/>
-      <x:c r="F18" s="31" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -15450,17 +15435,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -15483,211 +15468,211 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46058.3038087847</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46055</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46066.3127838657</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46066.3781940972</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46081</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46077.0856746296</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46062.2741739236</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46075</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46077.1029543634</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+      <x:c r="B17" s="28" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
+      <x:c r="C17" s="29" t="s"/>
+      <x:c r="D17" s="29" t="s"/>
+      <x:c r="E17" s="29" t="s"/>
+      <x:c r="F17" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
